--- a/output/Gym_Maliyet_BoQ.xlsx
+++ b/output/Gym_Maliyet_BoQ.xlsx
@@ -383,12 +383,12 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -401,11 +401,11 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -808,7 +808,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rev A · 13 Eylül 2026 · Eylül 2026 piyasa mertebesi · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
+          <t>Rev B · 13 Eylül 2026 · Eylül 2026 piyasa mertebesi · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev A · 13 Eylül 2026 · Fiyat referansı: Eylül 2026 piyasa mertebesi · Net iç alan 103.78 m²</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev B · 13 Eylül 2026 · Fiyat referansı: Eylül 2026 piyasa mertebesi · Net iç alan 103.78 m²</t>
         </is>
       </c>
     </row>
@@ -3684,16 +3684,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3733,15 +3734,20 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
+          <t>Yükseklik (m)</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
           <t>Adet</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Footprint (m²)</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Marka / model (işveren dolduracak)</t>
         </is>
@@ -3755,7 +3761,7 @@
       </c>
       <c r="B4" s="59" t="inlineStr">
         <is>
-          <t>TRIMODE ARENA — 4 katmanlı altıgen rig</t>
+          <t>TRIMODE ARENA — altıgen ring, 4 sıra halat</t>
         </is>
       </c>
       <c r="C4" s="60" t="inlineStr">
@@ -3769,12 +3775,15 @@
         </is>
       </c>
       <c r="E4" s="61" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="F4" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="61" t="n">
         <v>10.6</v>
       </c>
-      <c r="G4" s="63" t="n"/>
+      <c r="H4" s="63" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="64" t="inlineStr">
@@ -3784,7 +3793,7 @@
       </c>
       <c r="B5" s="65" t="inlineStr">
         <is>
-          <t>Çok fonksiyonlu istasyon</t>
+          <t>Çok fonksiyonlu kuvvet istasyonu (ağırlık takozlu)</t>
         </is>
       </c>
       <c r="C5" s="66" t="n">
@@ -3794,12 +3803,15 @@
         <v>62</v>
       </c>
       <c r="E5" s="67" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="F5" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="67" t="n">
         <v>1.51</v>
       </c>
-      <c r="G5" s="63" t="n"/>
+      <c r="H5" s="63" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="58" t="inlineStr">
@@ -3819,12 +3831,15 @@
         <v>232</v>
       </c>
       <c r="E6" s="61" t="n">
-        <v>1</v>
+        <v>2.15</v>
       </c>
       <c r="F6" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="61" t="n">
         <v>4.06</v>
       </c>
-      <c r="G6" s="63" t="n"/>
+      <c r="H6" s="63" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="64" t="inlineStr">
@@ -3834,7 +3849,7 @@
       </c>
       <c r="B7" s="65" t="inlineStr">
         <is>
-          <t>Sehpa / dambıl rafı</t>
+          <t>Dambıl rafı / sehpa</t>
         </is>
       </c>
       <c r="C7" s="66" t="n">
@@ -3844,12 +3859,15 @@
         <v>39</v>
       </c>
       <c r="E7" s="67" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F7" s="68" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="68" t="n">
+      <c r="G7" s="67" t="n">
         <v>1.21</v>
       </c>
-      <c r="G7" s="63" t="n"/>
+      <c r="H7" s="63" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="58" t="inlineStr">
@@ -3859,7 +3877,7 @@
       </c>
       <c r="B8" s="59" t="inlineStr">
         <is>
-          <t>Kardiyo — kompakt</t>
+          <t>Kardiyo — kondisyon bisikleti</t>
         </is>
       </c>
       <c r="C8" s="60" t="n">
@@ -3869,12 +3887,15 @@
         <v>150</v>
       </c>
       <c r="E8" s="61" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="F8" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="61" t="n">
         <v>1.26</v>
       </c>
-      <c r="G8" s="63" t="n"/>
+      <c r="H8" s="63" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="64" t="inlineStr">
@@ -3884,7 +3905,7 @@
       </c>
       <c r="B9" s="65" t="inlineStr">
         <is>
-          <t>Koşu bandı / kürek</t>
+          <t>Koşu bandı</t>
         </is>
       </c>
       <c r="C9" s="66" t="n">
@@ -3894,12 +3915,15 @@
         <v>74</v>
       </c>
       <c r="E9" s="67" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F9" s="68" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="68" t="n">
+      <c r="G9" s="67" t="n">
         <v>3.63</v>
       </c>
-      <c r="G9" s="63" t="n"/>
+      <c r="H9" s="63" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="17" t="n"/>
@@ -3910,15 +3934,16 @@
       </c>
       <c r="C10" s="17" t="n"/>
       <c r="D10" s="17" t="n"/>
-      <c r="E10" s="19">
-        <f>SUM(E4:E9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="69">
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="19">
         <f>SUM(F4:F9)</f>
         <v/>
       </c>
-      <c r="G10" s="17" t="n"/>
+      <c r="G10" s="69">
+        <f>SUM(G4:G9)</f>
+        <v/>
+      </c>
+      <c r="H10" s="17" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="30" t="inlineStr">
@@ -3926,7 +3951,7 @@
           <t>Salon brüt alanı</t>
         </is>
       </c>
-      <c r="F12" s="62" t="n">
+      <c r="G12" s="61" t="n">
         <v>87.05</v>
       </c>
     </row>
@@ -3936,15 +3961,15 @@
           <t>Serbest sirkülasyon / çalışma alanı</t>
         </is>
       </c>
-      <c r="F13" s="62">
-        <f>87.05-F10</f>
+      <c r="G13" s="61">
+        <f>87.05-G10</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4000,7 +4025,7 @@
           <t>Salon alanı</t>
         </is>
       </c>
-      <c r="B4" s="62" t="n">
+      <c r="B4" s="61" t="n">
         <v>87.05</v>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -4020,7 +4045,7 @@
           <t>Erkek soyunma bloğu</t>
         </is>
       </c>
-      <c r="B5" s="68" t="n">
+      <c r="B5" s="67" t="n">
         <v>8.24</v>
       </c>
       <c r="C5" s="15" t="inlineStr">
@@ -4040,7 +4065,7 @@
           <t>Kadın soyunma bloğu</t>
         </is>
       </c>
-      <c r="B6" s="62" t="n">
+      <c r="B6" s="61" t="n">
         <v>8.49</v>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -4060,7 +4085,7 @@
           <t>Net iç kullanım alanı</t>
         </is>
       </c>
-      <c r="B7" s="68" t="n">
+      <c r="B7" s="67" t="n">
         <v>103.78</v>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -4080,7 +4105,7 @@
           <t>Ön bahçe</t>
         </is>
       </c>
-      <c r="B8" s="62" t="n">
+      <c r="B8" s="61" t="n">
         <v>24.39</v>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -4100,7 +4125,7 @@
           <t>Arka bahçe</t>
         </is>
       </c>
-      <c r="B9" s="68" t="n">
+      <c r="B9" s="67" t="n">
         <v>32.82</v>
       </c>
       <c r="C9" s="15" t="inlineStr">
@@ -4120,7 +4145,7 @@
           <t>Salon dış çevre uzunluğu</t>
         </is>
       </c>
-      <c r="B10" s="62" t="n">
+      <c r="B10" s="61" t="n">
         <v>46.15</v>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -4140,7 +4165,7 @@
           <t>Islak hacim blok çevresi</t>
         </is>
       </c>
-      <c r="B11" s="68" t="n">
+      <c r="B11" s="67" t="n">
         <v>25.32</v>
       </c>
       <c r="C11" s="15" t="inlineStr">
@@ -4160,7 +4185,7 @@
           <t>Boyanacak / sıvalanacak duvar</t>
         </is>
       </c>
-      <c r="B12" s="62" t="n">
+      <c r="B12" s="61" t="n">
         <v>129.3</v>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -4180,7 +4205,7 @@
           <t>Islak hacim duvar fayansı</t>
         </is>
       </c>
-      <c r="B13" s="68" t="n">
+      <c r="B13" s="67" t="n">
         <v>55.7</v>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -4200,7 +4225,7 @@
           <t>Yeni alçıpan bölme</t>
         </is>
       </c>
-      <c r="B14" s="62" t="n">
+      <c r="B14" s="61" t="n">
         <v>44.6</v>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -4220,7 +4245,7 @@
           <t>Armatür adedi</t>
         </is>
       </c>
-      <c r="B15" s="68" t="n">
+      <c r="B15" s="67" t="n">
         <v>15</v>
       </c>
       <c r="C15" s="15" t="inlineStr">
@@ -4240,7 +4265,7 @@
           <t>Klima adedi</t>
         </is>
       </c>
-      <c r="B16" s="62" t="n">
+      <c r="B16" s="61" t="n">
         <v>3</v>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -4260,7 +4285,7 @@
           <t>Taze hava debisi</t>
         </is>
       </c>
-      <c r="B17" s="68" t="n">
+      <c r="B17" s="67" t="n">
         <v>1000</v>
       </c>
       <c r="C17" s="15" t="inlineStr">
@@ -4280,7 +4305,7 @@
           <t>Kurulu güç</t>
         </is>
       </c>
-      <c r="B18" s="62" t="n">
+      <c r="B18" s="61" t="n">
         <v>16.3</v>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -4300,7 +4325,7 @@
           <t>Şantiye genel gideri</t>
         </is>
       </c>
-      <c r="B19" s="68" t="n">
+      <c r="B19" s="67" t="n">
         <v>0.09</v>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -4320,7 +4345,7 @@
           <t>Beklenmedik pay</t>
         </is>
       </c>
-      <c r="B20" s="62" t="n">
+      <c r="B20" s="61" t="n">
         <v>0.15</v>
       </c>
       <c r="C20" s="10" t="inlineStr">

--- a/output/Gym_Maliyet_BoQ.xlsx
+++ b/output/Gym_Maliyet_BoQ.xlsx
@@ -13,7 +13,7 @@
     <sheet name="4 · Varsayımlar" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2 · Detay metraj'!$A$3:$K$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2 · Detay metraj'!$A$3:$K$109</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -808,7 +808,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rev B · 13 Eylül 2026 · Eylül 2026 piyasa mertebesi · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
+          <t>Rev C · 13 Eylül 2026 · Eylül 2026 piyasa mertebesi · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
         </is>
       </c>
     </row>
@@ -935,19 +935,19 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>'2 · Detay metraj'!G12+'2 · Detay metraj'!G13+'2 · Detay metraj'!G14+'2 · Detay metraj'!G15+'2 · Detay metraj'!G16+'2 · Detay metraj'!G17+'2 · Detay metraj'!G18+'2 · Detay metraj'!G19+'2 · Detay metraj'!G20</f>
+        <f>'2 · Detay metraj'!G12+'2 · Detay metraj'!G13+'2 · Detay metraj'!G14+'2 · Detay metraj'!G15+'2 · Detay metraj'!G16+'2 · Detay metraj'!G17+'2 · Detay metraj'!G18</f>
         <v/>
       </c>
       <c r="C9" s="9">
-        <f>'2 · Detay metraj'!H12+'2 · Detay metraj'!H13+'2 · Detay metraj'!H14+'2 · Detay metraj'!H15+'2 · Detay metraj'!H16+'2 · Detay metraj'!H17+'2 · Detay metraj'!H18+'2 · Detay metraj'!H19+'2 · Detay metraj'!H20</f>
+        <f>'2 · Detay metraj'!H12+'2 · Detay metraj'!H13+'2 · Detay metraj'!H14+'2 · Detay metraj'!H15+'2 · Detay metraj'!H16+'2 · Detay metraj'!H17+'2 · Detay metraj'!H18</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>'2 · Detay metraj'!I12+'2 · Detay metraj'!I13+'2 · Detay metraj'!I14+'2 · Detay metraj'!I15+'2 · Detay metraj'!I16+'2 · Detay metraj'!I17+'2 · Detay metraj'!I18+'2 · Detay metraj'!I19+'2 · Detay metraj'!I20</f>
+        <f>'2 · Detay metraj'!I12+'2 · Detay metraj'!I13+'2 · Detay metraj'!I14+'2 · Detay metraj'!I15+'2 · Detay metraj'!I16+'2 · Detay metraj'!I17+'2 · Detay metraj'!I18</f>
         <v/>
       </c>
       <c r="E9" s="10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" s="11">
         <f>IFERROR((C9+D9)/2/(($C$17+$D$17)/2),0)</f>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B10" s="13">
-        <f>'2 · Detay metraj'!G21+'2 · Detay metraj'!G22+'2 · Detay metraj'!G23+'2 · Detay metraj'!G24+'2 · Detay metraj'!G25</f>
+        <f>'2 · Detay metraj'!G19+'2 · Detay metraj'!G20+'2 · Detay metraj'!G21+'2 · Detay metraj'!G22+'2 · Detay metraj'!G23</f>
         <v/>
       </c>
       <c r="C10" s="14">
-        <f>'2 · Detay metraj'!H21+'2 · Detay metraj'!H22+'2 · Detay metraj'!H23+'2 · Detay metraj'!H24+'2 · Detay metraj'!H25</f>
+        <f>'2 · Detay metraj'!H19+'2 · Detay metraj'!H20+'2 · Detay metraj'!H21+'2 · Detay metraj'!H22+'2 · Detay metraj'!H23</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>'2 · Detay metraj'!I21+'2 · Detay metraj'!I22+'2 · Detay metraj'!I23+'2 · Detay metraj'!I24+'2 · Detay metraj'!I25</f>
+        <f>'2 · Detay metraj'!I19+'2 · Detay metraj'!I20+'2 · Detay metraj'!I21+'2 · Detay metraj'!I22+'2 · Detay metraj'!I23</f>
         <v/>
       </c>
       <c r="E10" s="15" t="n">
@@ -987,19 +987,19 @@
         </is>
       </c>
       <c r="B11" s="8">
-        <f>'2 · Detay metraj'!G26+'2 · Detay metraj'!G27+'2 · Detay metraj'!G28+'2 · Detay metraj'!G29+'2 · Detay metraj'!G30+'2 · Detay metraj'!G31</f>
+        <f>'2 · Detay metraj'!G74+'2 · Detay metraj'!G75+'2 · Detay metraj'!G76+'2 · Detay metraj'!G77+'2 · Detay metraj'!G78+'2 · Detay metraj'!G79+'2 · Detay metraj'!G80+'2 · Detay metraj'!G81+'2 · Detay metraj'!G82+'2 · Detay metraj'!G83+'2 · Detay metraj'!G84+'2 · Detay metraj'!G85+'2 · Detay metraj'!G86+'2 · Detay metraj'!G87+'2 · Detay metraj'!G88+'2 · Detay metraj'!G89+'2 · Detay metraj'!G90+'2 · Detay metraj'!G91+'2 · Detay metraj'!G92+'2 · Detay metraj'!G93+'2 · Detay metraj'!G94+'2 · Detay metraj'!G95+'2 · Detay metraj'!G96+'2 · Detay metraj'!G97+'2 · Detay metraj'!G98+'2 · Detay metraj'!G99+'2 · Detay metraj'!G100+'2 · Detay metraj'!G101+'2 · Detay metraj'!G102+'2 · Detay metraj'!G103+'2 · Detay metraj'!G104+'2 · Detay metraj'!G105+'2 · Detay metraj'!G106+'2 · Detay metraj'!G107+'2 · Detay metraj'!G108+'2 · Detay metraj'!G109</f>
         <v/>
       </c>
       <c r="C11" s="9">
-        <f>'2 · Detay metraj'!H26+'2 · Detay metraj'!H27+'2 · Detay metraj'!H28+'2 · Detay metraj'!H29+'2 · Detay metraj'!H30+'2 · Detay metraj'!H31</f>
+        <f>'2 · Detay metraj'!H74+'2 · Detay metraj'!H75+'2 · Detay metraj'!H76+'2 · Detay metraj'!H77+'2 · Detay metraj'!H78+'2 · Detay metraj'!H79+'2 · Detay metraj'!H80+'2 · Detay metraj'!H81+'2 · Detay metraj'!H82+'2 · Detay metraj'!H83+'2 · Detay metraj'!H84+'2 · Detay metraj'!H85+'2 · Detay metraj'!H86+'2 · Detay metraj'!H87+'2 · Detay metraj'!H88+'2 · Detay metraj'!H89+'2 · Detay metraj'!H90+'2 · Detay metraj'!H91+'2 · Detay metraj'!H92+'2 · Detay metraj'!H93+'2 · Detay metraj'!H94+'2 · Detay metraj'!H95+'2 · Detay metraj'!H96+'2 · Detay metraj'!H97+'2 · Detay metraj'!H98+'2 · Detay metraj'!H99+'2 · Detay metraj'!H100+'2 · Detay metraj'!H101+'2 · Detay metraj'!H102+'2 · Detay metraj'!H103+'2 · Detay metraj'!H104+'2 · Detay metraj'!H105+'2 · Detay metraj'!H106+'2 · Detay metraj'!H107+'2 · Detay metraj'!H108+'2 · Detay metraj'!H109</f>
         <v/>
       </c>
       <c r="D11" s="9">
-        <f>'2 · Detay metraj'!I26+'2 · Detay metraj'!I27+'2 · Detay metraj'!I28+'2 · Detay metraj'!I29+'2 · Detay metraj'!I30+'2 · Detay metraj'!I31</f>
+        <f>'2 · Detay metraj'!I74+'2 · Detay metraj'!I75+'2 · Detay metraj'!I76+'2 · Detay metraj'!I77+'2 · Detay metraj'!I78+'2 · Detay metraj'!I79+'2 · Detay metraj'!I80+'2 · Detay metraj'!I81+'2 · Detay metraj'!I82+'2 · Detay metraj'!I83+'2 · Detay metraj'!I84+'2 · Detay metraj'!I85+'2 · Detay metraj'!I86+'2 · Detay metraj'!I87+'2 · Detay metraj'!I88+'2 · Detay metraj'!I89+'2 · Detay metraj'!I90+'2 · Detay metraj'!I91+'2 · Detay metraj'!I92+'2 · Detay metraj'!I93+'2 · Detay metraj'!I94+'2 · Detay metraj'!I95+'2 · Detay metraj'!I96+'2 · Detay metraj'!I97+'2 · Detay metraj'!I98+'2 · Detay metraj'!I99+'2 · Detay metraj'!I100+'2 · Detay metraj'!I101+'2 · Detay metraj'!I102+'2 · Detay metraj'!I103+'2 · Detay metraj'!I104+'2 · Detay metraj'!I105+'2 · Detay metraj'!I106+'2 · Detay metraj'!I107+'2 · Detay metraj'!I108+'2 · Detay metraj'!I109</f>
         <v/>
       </c>
       <c r="E11" s="10" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="F11" s="11">
         <f>IFERROR((C11+D11)/2/(($C$17+$D$17)/2),0)</f>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="B12" s="13">
-        <f>'2 · Detay metraj'!G32+'2 · Detay metraj'!G33+'2 · Detay metraj'!G34+'2 · Detay metraj'!G35</f>
+        <f>'2 · Detay metraj'!G37+'2 · Detay metraj'!G38+'2 · Detay metraj'!G39+'2 · Detay metraj'!G40+'2 · Detay metraj'!G41+'2 · Detay metraj'!G42+'2 · Detay metraj'!G43+'2 · Detay metraj'!G44+'2 · Detay metraj'!G45+'2 · Detay metraj'!G46+'2 · Detay metraj'!G47+'2 · Detay metraj'!G48+'2 · Detay metraj'!G49+'2 · Detay metraj'!G50+'2 · Detay metraj'!G51+'2 · Detay metraj'!G52+'2 · Detay metraj'!G53+'2 · Detay metraj'!G54+'2 · Detay metraj'!G55+'2 · Detay metraj'!G56+'2 · Detay metraj'!G57+'2 · Detay metraj'!G58+'2 · Detay metraj'!G59+'2 · Detay metraj'!G60+'2 · Detay metraj'!G61+'2 · Detay metraj'!G62+'2 · Detay metraj'!G63+'2 · Detay metraj'!G64+'2 · Detay metraj'!G65+'2 · Detay metraj'!G66+'2 · Detay metraj'!G67+'2 · Detay metraj'!G68+'2 · Detay metraj'!G69+'2 · Detay metraj'!G70+'2 · Detay metraj'!G71+'2 · Detay metraj'!G72+'2 · Detay metraj'!G73</f>
         <v/>
       </c>
       <c r="C12" s="14">
-        <f>'2 · Detay metraj'!H32+'2 · Detay metraj'!H33+'2 · Detay metraj'!H34+'2 · Detay metraj'!H35</f>
+        <f>'2 · Detay metraj'!H37+'2 · Detay metraj'!H38+'2 · Detay metraj'!H39+'2 · Detay metraj'!H40+'2 · Detay metraj'!H41+'2 · Detay metraj'!H42+'2 · Detay metraj'!H43+'2 · Detay metraj'!H44+'2 · Detay metraj'!H45+'2 · Detay metraj'!H46+'2 · Detay metraj'!H47+'2 · Detay metraj'!H48+'2 · Detay metraj'!H49+'2 · Detay metraj'!H50+'2 · Detay metraj'!H51+'2 · Detay metraj'!H52+'2 · Detay metraj'!H53+'2 · Detay metraj'!H54+'2 · Detay metraj'!H55+'2 · Detay metraj'!H56+'2 · Detay metraj'!H57+'2 · Detay metraj'!H58+'2 · Detay metraj'!H59+'2 · Detay metraj'!H60+'2 · Detay metraj'!H61+'2 · Detay metraj'!H62+'2 · Detay metraj'!H63+'2 · Detay metraj'!H64+'2 · Detay metraj'!H65+'2 · Detay metraj'!H66+'2 · Detay metraj'!H67+'2 · Detay metraj'!H68+'2 · Detay metraj'!H69+'2 · Detay metraj'!H70+'2 · Detay metraj'!H71+'2 · Detay metraj'!H72+'2 · Detay metraj'!H73</f>
         <v/>
       </c>
       <c r="D12" s="14">
-        <f>'2 · Detay metraj'!I32+'2 · Detay metraj'!I33+'2 · Detay metraj'!I34+'2 · Detay metraj'!I35</f>
+        <f>'2 · Detay metraj'!I37+'2 · Detay metraj'!I38+'2 · Detay metraj'!I39+'2 · Detay metraj'!I40+'2 · Detay metraj'!I41+'2 · Detay metraj'!I42+'2 · Detay metraj'!I43+'2 · Detay metraj'!I44+'2 · Detay metraj'!I45+'2 · Detay metraj'!I46+'2 · Detay metraj'!I47+'2 · Detay metraj'!I48+'2 · Detay metraj'!I49+'2 · Detay metraj'!I50+'2 · Detay metraj'!I51+'2 · Detay metraj'!I52+'2 · Detay metraj'!I53+'2 · Detay metraj'!I54+'2 · Detay metraj'!I55+'2 · Detay metraj'!I56+'2 · Detay metraj'!I57+'2 · Detay metraj'!I58+'2 · Detay metraj'!I59+'2 · Detay metraj'!I60+'2 · Detay metraj'!I61+'2 · Detay metraj'!I62+'2 · Detay metraj'!I63+'2 · Detay metraj'!I64+'2 · Detay metraj'!I65+'2 · Detay metraj'!I66+'2 · Detay metraj'!I67+'2 · Detay metraj'!I68+'2 · Detay metraj'!I69+'2 · Detay metraj'!I70+'2 · Detay metraj'!I71+'2 · Detay metraj'!I72+'2 · Detay metraj'!I73</f>
         <v/>
       </c>
       <c r="E12" s="15" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F12" s="16">
         <f>IFERROR((C12+D12)/2/(($C$17+$D$17)/2),0)</f>
@@ -1039,15 +1039,15 @@
         </is>
       </c>
       <c r="B13" s="8">
-        <f>'2 · Detay metraj'!G36+'2 · Detay metraj'!G37+'2 · Detay metraj'!G38+'2 · Detay metraj'!G39</f>
+        <f>'2 · Detay metraj'!G24+'2 · Detay metraj'!G25+'2 · Detay metraj'!G26+'2 · Detay metraj'!G27</f>
         <v/>
       </c>
       <c r="C13" s="9">
-        <f>'2 · Detay metraj'!H36+'2 · Detay metraj'!H37+'2 · Detay metraj'!H38+'2 · Detay metraj'!H39</f>
+        <f>'2 · Detay metraj'!H24+'2 · Detay metraj'!H25+'2 · Detay metraj'!H26+'2 · Detay metraj'!H27</f>
         <v/>
       </c>
       <c r="D13" s="9">
-        <f>'2 · Detay metraj'!I36+'2 · Detay metraj'!I37+'2 · Detay metraj'!I38+'2 · Detay metraj'!I39</f>
+        <f>'2 · Detay metraj'!I24+'2 · Detay metraj'!I25+'2 · Detay metraj'!I26+'2 · Detay metraj'!I27</f>
         <v/>
       </c>
       <c r="E13" s="10" t="n">
@@ -1065,15 +1065,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>'2 · Detay metraj'!G40+'2 · Detay metraj'!G41+'2 · Detay metraj'!G42</f>
+        <f>'2 · Detay metraj'!G28+'2 · Detay metraj'!G29+'2 · Detay metraj'!G30</f>
         <v/>
       </c>
       <c r="C14" s="14">
-        <f>'2 · Detay metraj'!H40+'2 · Detay metraj'!H41+'2 · Detay metraj'!H42</f>
+        <f>'2 · Detay metraj'!H28+'2 · Detay metraj'!H29+'2 · Detay metraj'!H30</f>
         <v/>
       </c>
       <c r="D14" s="14">
-        <f>'2 · Detay metraj'!I40+'2 · Detay metraj'!I41+'2 · Detay metraj'!I42</f>
+        <f>'2 · Detay metraj'!I28+'2 · Detay metraj'!I29+'2 · Detay metraj'!I30</f>
         <v/>
       </c>
       <c r="E14" s="15" t="n">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="B15" s="8">
-        <f>'2 · Detay metraj'!G43+'2 · Detay metraj'!G44+'2 · Detay metraj'!G45+'2 · Detay metraj'!G46+'2 · Detay metraj'!G47</f>
+        <f>'2 · Detay metraj'!G31+'2 · Detay metraj'!G32+'2 · Detay metraj'!G33+'2 · Detay metraj'!G34</f>
         <v/>
       </c>
       <c r="C15" s="9">
-        <f>'2 · Detay metraj'!H43+'2 · Detay metraj'!H44+'2 · Detay metraj'!H45+'2 · Detay metraj'!H46+'2 · Detay metraj'!H47</f>
+        <f>'2 · Detay metraj'!H31+'2 · Detay metraj'!H32+'2 · Detay metraj'!H33+'2 · Detay metraj'!H34</f>
         <v/>
       </c>
       <c r="D15" s="9">
-        <f>'2 · Detay metraj'!I43+'2 · Detay metraj'!I44+'2 · Detay metraj'!I45+'2 · Detay metraj'!I46+'2 · Detay metraj'!I47</f>
+        <f>'2 · Detay metraj'!I31+'2 · Detay metraj'!I32+'2 · Detay metraj'!I33+'2 · Detay metraj'!I34</f>
         <v/>
       </c>
       <c r="E15" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15" s="11">
         <f>IFERROR((C15+D15)/2/(($C$17+$D$17)/2),0)</f>
@@ -1117,15 +1117,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>'2 · Detay metraj'!G48+'2 · Detay metraj'!G49</f>
+        <f>'2 · Detay metraj'!G35+'2 · Detay metraj'!G36</f>
         <v/>
       </c>
       <c r="C16" s="14">
-        <f>'2 · Detay metraj'!H48+'2 · Detay metraj'!H49</f>
+        <f>'2 · Detay metraj'!H35+'2 · Detay metraj'!H36</f>
         <v/>
       </c>
       <c r="D16" s="14">
-        <f>'2 · Detay metraj'!I48+'2 · Detay metraj'!I49</f>
+        <f>'2 · Detay metraj'!I35+'2 · Detay metraj'!I36</f>
         <v/>
       </c>
       <c r="E16" s="15" t="n">
@@ -1155,7 +1155,7 @@
         <v/>
       </c>
       <c r="E17" s="19" t="n">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="F17" s="20" t="n">
         <v>1</v>
@@ -1430,7 +1430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1456,7 +1456,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev B · 13 Eylül 2026 · Fiyat referansı: Eylül 2026 piyasa mertebesi · Net iç alan 103.78 m²</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev C · 13 Eylül 2026 · Fiyat referansı: Eylül 2026 piyasa mertebesi · Net iç alan 103.78 m²</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
     <row r="12">
       <c r="A12" s="34" t="inlineStr">
         <is>
-          <t>03.01</t>
+          <t>03.02</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1899,16 +1899,16 @@
       </c>
       <c r="C12" s="35" t="inlineStr">
         <is>
-          <t>Pis su + temiz su tesisatı yenileme (2 duş + 2 WC + lavabo)</t>
+          <t>Su yalıtımı — çift bileşenli, dönüş 30 cm</t>
         </is>
       </c>
       <c r="D12" s="36" t="inlineStr">
         <is>
-          <t>götürü</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E12" s="37" t="n">
-        <v>1</v>
+        <v>24.3</v>
       </c>
       <c r="F12" s="29" t="n"/>
       <c r="G12" s="38">
@@ -1916,11 +1916,11 @@
         <v/>
       </c>
       <c r="H12" s="39">
-        <f>85000*K12</f>
+        <f>11664*K12</f>
         <v/>
       </c>
       <c r="I12" s="39">
-        <f>150000*K12</f>
+        <f>18954*K12</f>
         <v/>
       </c>
       <c r="J12" s="40" t="inlineStr">
@@ -1935,7 +1935,7 @@
     <row r="13">
       <c r="A13" s="41" t="inlineStr">
         <is>
-          <t>03.02</t>
+          <t>03.03</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="C13" s="42" t="inlineStr">
         <is>
-          <t>Su yalıtımı — çift bileşenli, dönüş 30 cm</t>
+          <t>Zemin seramiği R11 kaymaz (malzeme + işçilik)</t>
         </is>
       </c>
       <c r="D13" s="43" t="inlineStr">
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="E13" s="44" t="n">
-        <v>24.3</v>
+        <v>16.73</v>
       </c>
       <c r="F13" s="29" t="n"/>
       <c r="G13" s="45">
@@ -1962,11 +1962,11 @@
         <v/>
       </c>
       <c r="H13" s="46">
-        <f>11664*K13</f>
+        <f>12548*K13</f>
         <v/>
       </c>
       <c r="I13" s="46">
-        <f>18954*K13</f>
+        <f>20076*K13</f>
         <v/>
       </c>
       <c r="J13" s="47" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="14">
       <c r="A14" s="34" t="inlineStr">
         <is>
-          <t>03.03</t>
+          <t>03.04</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="C14" s="35" t="inlineStr">
         <is>
-          <t>Zemin seramiği R11 kaymaz (malzeme + işçilik)</t>
+          <t>Duvar fayansı h=2,20 m (malzeme + işçilik)</t>
         </is>
       </c>
       <c r="D14" s="36" t="inlineStr">
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="37" t="n">
-        <v>16.73</v>
+        <v>55.7</v>
       </c>
       <c r="F14" s="29" t="n"/>
       <c r="G14" s="38">
@@ -2008,11 +2008,11 @@
         <v/>
       </c>
       <c r="H14" s="39">
-        <f>12548*K14</f>
+        <f>47345*K14</f>
         <v/>
       </c>
       <c r="I14" s="39">
-        <f>20076*K14</f>
+        <f>75195*K14</f>
         <v/>
       </c>
       <c r="J14" s="40" t="inlineStr">
@@ -2027,7 +2027,7 @@
     <row r="15">
       <c r="A15" s="41" t="inlineStr">
         <is>
-          <t>03.04</t>
+          <t>03.05</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -2037,16 +2037,16 @@
       </c>
       <c r="C15" s="42" t="inlineStr">
         <is>
-          <t>Duvar fayansı h=2,20 m (malzeme + işçilik)</t>
+          <t>Vitrifiye seti — 2 klozet, 2 lavabo, armatürler</t>
         </is>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>takım</t>
         </is>
       </c>
       <c r="E15" s="44" t="n">
-        <v>55.7</v>
+        <v>2</v>
       </c>
       <c r="F15" s="29" t="n"/>
       <c r="G15" s="45">
@@ -2054,11 +2054,11 @@
         <v/>
       </c>
       <c r="H15" s="46">
-        <f>47345*K15</f>
+        <f>24000*K15</f>
         <v/>
       </c>
       <c r="I15" s="46">
-        <f>75195*K15</f>
+        <f>44000*K15</f>
         <v/>
       </c>
       <c r="J15" s="47" t="inlineStr">
@@ -2073,7 +2073,7 @@
     <row r="16">
       <c r="A16" s="34" t="inlineStr">
         <is>
-          <t>03.05</t>
+          <t>03.06</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
-          <t>Vitrifiye seti — 2 klozet, 2 lavabo, armatürler</t>
+          <t>Duş teknesi + cam duşakabin (2 adet)</t>
         </is>
       </c>
       <c r="D16" s="36" t="inlineStr">
         <is>
-          <t>takım</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E16" s="37" t="n">
@@ -2100,11 +2100,11 @@
         <v/>
       </c>
       <c r="H16" s="39">
-        <f>24000*K16</f>
+        <f>32000*K16</f>
         <v/>
       </c>
       <c r="I16" s="39">
-        <f>44000*K16</f>
+        <f>60000*K16</f>
         <v/>
       </c>
       <c r="J16" s="40" t="inlineStr">
@@ -2117,195 +2117,196 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="41" t="inlineStr">
-        <is>
-          <t>03.06</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="A17" s="48" t="inlineStr">
+        <is>
+          <t>03.08</t>
+        </is>
+      </c>
+      <c r="B17" s="49" t="inlineStr">
         <is>
           <t>ISLAK HACİM</t>
         </is>
       </c>
-      <c r="C17" s="42" t="inlineStr">
-        <is>
-          <t>Duş teknesi + cam duşakabin (2 adet)</t>
-        </is>
-      </c>
-      <c r="D17" s="43" t="inlineStr">
-        <is>
-          <t>adet</t>
-        </is>
-      </c>
-      <c r="E17" s="44" t="n">
-        <v>2</v>
+      <c r="C17" s="50" t="inlineStr">
+        <is>
+          <t>SEÇENEK A — ıslak hacim zemini 15–20 cm yükseltme (hafif dolgu + şap + basamak/rampa)</t>
+        </is>
+      </c>
+      <c r="D17" s="51" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E17" s="52" t="n">
+        <v>16.73</v>
       </c>
       <c r="F17" s="29" t="n"/>
-      <c r="G17" s="45">
+      <c r="G17" s="53">
         <f>E17*F17*K17</f>
         <v/>
       </c>
-      <c r="H17" s="46">
-        <f>32000*K17</f>
-        <v/>
-      </c>
-      <c r="I17" s="46">
-        <f>60000*K17</f>
-        <v/>
-      </c>
-      <c r="J17" s="47" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="K17" s="47" t="n">
-        <v>1</v>
+      <c r="H17" s="54">
+        <f>14220*K17</f>
+        <v/>
+      </c>
+      <c r="I17" s="54">
+        <f>23422*K17</f>
+        <v/>
+      </c>
+      <c r="J17" s="55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K17" s="55">
+        <f>IF('1 · Özet'!$E$4="A",1,0)</f>
+        <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
-        <is>
-          <t>03.07</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="A18" s="48" t="inlineStr">
+        <is>
+          <t>03.09</t>
+        </is>
+      </c>
+      <c r="B18" s="49" t="inlineStr">
         <is>
           <t>ISLAK HACİM</t>
         </is>
       </c>
-      <c r="C18" s="35" t="inlineStr">
-        <is>
-          <t>Sıcak su — elektrikli ani ısıtıcı 2×6 kW + hat</t>
-        </is>
-      </c>
-      <c r="D18" s="36" t="inlineStr">
+      <c r="C18" s="50" t="inlineStr">
+        <is>
+          <t>SEÇENEK B — öğütücülü gri su / atık su pompası (2 ünite + hat)</t>
+        </is>
+      </c>
+      <c r="D18" s="51" t="inlineStr">
         <is>
           <t>takım</t>
         </is>
       </c>
-      <c r="E18" s="37" t="n">
+      <c r="E18" s="52" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="29" t="n"/>
-      <c r="G18" s="38">
+      <c r="G18" s="53">
         <f>E18*F18*K18</f>
         <v/>
       </c>
-      <c r="H18" s="39">
-        <f>28000*K18</f>
-        <v/>
-      </c>
-      <c r="I18" s="39">
-        <f>52000*K18</f>
-        <v/>
-      </c>
-      <c r="J18" s="40" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="K18" s="40" t="n">
-        <v>1</v>
+      <c r="H18" s="54">
+        <f>72000*K18</f>
+        <v/>
+      </c>
+      <c r="I18" s="54">
+        <f>128000*K18</f>
+        <v/>
+      </c>
+      <c r="J18" s="55" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K18" s="55">
+        <f>IF('1 · Özet'!$E$4="B",1,0)</f>
+        <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="48" t="inlineStr">
-        <is>
-          <t>03.08</t>
-        </is>
-      </c>
-      <c r="B19" s="49" t="inlineStr">
-        <is>
-          <t>ISLAK HACİM</t>
-        </is>
-      </c>
-      <c r="C19" s="50" t="inlineStr">
-        <is>
-          <t>SEÇENEK A — ıslak hacim zemini 15–20 cm yükseltme (hafif dolgu + şap + basamak/rampa)</t>
-        </is>
-      </c>
-      <c r="D19" s="51" t="inlineStr">
+      <c r="A19" s="41" t="inlineStr">
+        <is>
+          <t>04.01</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>ZEMİN</t>
+        </is>
+      </c>
+      <c r="C19" s="42" t="inlineStr">
+        <is>
+          <t>Kauçuk karo 40 mm — arena / serbest ağırlık</t>
+        </is>
+      </c>
+      <c r="D19" s="43" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E19" s="52" t="n">
-        <v>16.73</v>
+      <c r="E19" s="44" t="n">
+        <v>31.76</v>
       </c>
       <c r="F19" s="29" t="n"/>
-      <c r="G19" s="53">
+      <c r="G19" s="45">
         <f>E19*F19*K19</f>
         <v/>
       </c>
-      <c r="H19" s="54">
-        <f>14220*K19</f>
-        <v/>
-      </c>
-      <c r="I19" s="54">
-        <f>23422*K19</f>
-        <v/>
-      </c>
-      <c r="J19" s="55" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K19" s="55">
-        <f>IF('1 · Özet'!$E$4="A",1,0)</f>
-        <v/>
+      <c r="H19" s="46">
+        <f>36524*K19</f>
+        <v/>
+      </c>
+      <c r="I19" s="46">
+        <f>57168*K19</f>
+        <v/>
+      </c>
+      <c r="J19" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K19" s="47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="48" t="inlineStr">
-        <is>
-          <t>03.09</t>
-        </is>
-      </c>
-      <c r="B20" s="49" t="inlineStr">
-        <is>
-          <t>ISLAK HACİM</t>
-        </is>
-      </c>
-      <c r="C20" s="50" t="inlineStr">
-        <is>
-          <t>SEÇENEK B — öğütücülü gri su / atık su pompası (2 ünite + hat)</t>
-        </is>
-      </c>
-      <c r="D20" s="51" t="inlineStr">
-        <is>
-          <t>takım</t>
-        </is>
-      </c>
-      <c r="E20" s="52" t="n">
-        <v>1</v>
+      <c r="A20" s="34" t="inlineStr">
+        <is>
+          <t>04.02</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>ZEMİN</t>
+        </is>
+      </c>
+      <c r="C20" s="35" t="inlineStr">
+        <is>
+          <t>Titreşim matı 10 mm (arena altı — üst katta konut varsayımı)</t>
+        </is>
+      </c>
+      <c r="D20" s="36" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E20" s="37" t="n">
+        <v>31.76</v>
       </c>
       <c r="F20" s="29" t="n"/>
-      <c r="G20" s="53">
+      <c r="G20" s="38">
         <f>E20*F20*K20</f>
         <v/>
       </c>
-      <c r="H20" s="54">
-        <f>72000*K20</f>
-        <v/>
-      </c>
-      <c r="I20" s="54">
-        <f>128000*K20</f>
-        <v/>
-      </c>
-      <c r="J20" s="55" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K20" s="55">
-        <f>IF('1 · Özet'!$E$4="B",1,0)</f>
+      <c r="H20" s="39">
+        <f>9528*K20</f>
+        <v/>
+      </c>
+      <c r="I20" s="39">
+        <f>16515*K20</f>
+        <v/>
+      </c>
+      <c r="J20" s="40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" s="40">
+        <f>IF('1 · Özet'!$B$4="ÖNERİLEN",1,0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="41" t="inlineStr">
         <is>
-          <t>04.01</t>
+          <t>04.03</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -2315,7 +2316,7 @@
       </c>
       <c r="C21" s="42" t="inlineStr">
         <is>
-          <t>Kauçuk karo 40 mm — arena / serbest ağırlık</t>
+          <t>Kauçuk karo 20 mm — fonksiyonel / kardiyo</t>
         </is>
       </c>
       <c r="D21" s="43" t="inlineStr">
@@ -2324,7 +2325,7 @@
         </is>
       </c>
       <c r="E21" s="44" t="n">
-        <v>31.76</v>
+        <v>22.31</v>
       </c>
       <c r="F21" s="29" t="n"/>
       <c r="G21" s="45">
@@ -2332,11 +2333,11 @@
         <v/>
       </c>
       <c r="H21" s="46">
-        <f>36524*K21</f>
+        <f>15617*K21</f>
         <v/>
       </c>
       <c r="I21" s="46">
-        <f>57168*K21</f>
+        <f>25656*K21</f>
         <v/>
       </c>
       <c r="J21" s="47" t="inlineStr">
@@ -2351,7 +2352,7 @@
     <row r="22">
       <c r="A22" s="34" t="inlineStr">
         <is>
-          <t>04.02</t>
+          <t>04.04</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2361,7 +2362,7 @@
       </c>
       <c r="C22" s="35" t="inlineStr">
         <is>
-          <t>Titreşim matı 10 mm (arena altı — üst katta konut varsayımı)</t>
+          <t>LVT / laminat parke — dinlenme + giriş / banko</t>
         </is>
       </c>
       <c r="D22" s="36" t="inlineStr">
@@ -2370,7 +2371,7 @@
         </is>
       </c>
       <c r="E22" s="37" t="n">
-        <v>31.76</v>
+        <v>32.98</v>
       </c>
       <c r="F22" s="29" t="n"/>
       <c r="G22" s="38">
@@ -2378,27 +2379,26 @@
         <v/>
       </c>
       <c r="H22" s="39">
-        <f>9528*K22</f>
+        <f>18139*K22</f>
         <v/>
       </c>
       <c r="I22" s="39">
-        <f>16515*K22</f>
+        <f>31331*K22</f>
         <v/>
       </c>
       <c r="J22" s="40" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K22" s="40">
-        <f>IF('1 · Özet'!$B$4="ÖNERİLEN",1,0)</f>
-        <v/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K22" s="40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="41" t="inlineStr">
         <is>
-          <t>04.03</t>
+          <t>04.05</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -2408,16 +2408,16 @@
       </c>
       <c r="C23" s="42" t="inlineStr">
         <is>
-          <t>Kauçuk karo 20 mm — fonksiyonel / kardiyo</t>
+          <t>Süpürgelik, geçiş profilleri, eşikler</t>
         </is>
       </c>
       <c r="D23" s="43" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E23" s="44" t="n">
-        <v>22.31</v>
+        <v>71.5</v>
       </c>
       <c r="F23" s="29" t="n"/>
       <c r="G23" s="45">
@@ -2425,11 +2425,11 @@
         <v/>
       </c>
       <c r="H23" s="46">
-        <f>15617*K23</f>
+        <f>11440*K23</f>
         <v/>
       </c>
       <c r="I23" s="46">
-        <f>25656*K23</f>
+        <f>20735*K23</f>
         <v/>
       </c>
       <c r="J23" s="47" t="inlineStr">
@@ -2444,17 +2444,17 @@
     <row r="24">
       <c r="A24" s="34" t="inlineStr">
         <is>
-          <t>04.04</t>
+          <t>07.01</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ZEMİN</t>
+          <t>BOYA · DEKOR</t>
         </is>
       </c>
       <c r="C24" s="35" t="inlineStr">
         <is>
-          <t>LVT / laminat parke — dinlenme + giriş / banko</t>
+          <t>Silinebilir mat duvar boyası (astar + 2 kat)</t>
         </is>
       </c>
       <c r="D24" s="36" t="inlineStr">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="E24" s="37" t="n">
-        <v>32.98</v>
+        <v>129.3</v>
       </c>
       <c r="F24" s="29" t="n"/>
       <c r="G24" s="38">
@@ -2471,11 +2471,11 @@
         <v/>
       </c>
       <c r="H24" s="39">
-        <f>18139*K24</f>
+        <f>19395*K24</f>
         <v/>
       </c>
       <c r="I24" s="39">
-        <f>31331*K24</f>
+        <f>36204*K24</f>
         <v/>
       </c>
       <c r="J24" s="40" t="inlineStr">
@@ -2490,26 +2490,26 @@
     <row r="25">
       <c r="A25" s="41" t="inlineStr">
         <is>
-          <t>04.05</t>
+          <t>07.02</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>ZEMİN</t>
+          <t>BOYA · DEKOR</t>
         </is>
       </c>
       <c r="C25" s="42" t="inlineStr">
         <is>
-          <t>Süpürgelik, geçiş profilleri, eşikler</t>
+          <t>Tavan boyası / açık tavan siyah boya (endüstriyel)</t>
         </is>
       </c>
       <c r="D25" s="43" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E25" s="44" t="n">
-        <v>71.5</v>
+        <v>103.78</v>
       </c>
       <c r="F25" s="29" t="n"/>
       <c r="G25" s="45">
@@ -2517,11 +2517,11 @@
         <v/>
       </c>
       <c r="H25" s="46">
-        <f>11440*K25</f>
+        <f>18680*K25</f>
         <v/>
       </c>
       <c r="I25" s="46">
-        <f>20735*K25</f>
+        <f>32172*K25</f>
         <v/>
       </c>
       <c r="J25" s="47" t="inlineStr">
@@ -2536,26 +2536,26 @@
     <row r="26">
       <c r="A26" s="34" t="inlineStr">
         <is>
-          <t>05.01</t>
+          <t>07.03</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ELEKTRİK</t>
+          <t>BOYA · DEKOR</t>
         </is>
       </c>
       <c r="C26" s="35" t="inlineStr">
         <is>
-          <t>Ana pano yenileme + kaçak akım + kompanzasyonsuz dağıtım</t>
+          <t>Ayna — arena ve fonksiyonel alan (6 mm, montaj dahil)</t>
         </is>
       </c>
       <c r="D26" s="36" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E26" s="37" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F26" s="29" t="n"/>
       <c r="G26" s="38">
@@ -2563,45 +2563,46 @@
         <v/>
       </c>
       <c r="H26" s="39">
-        <f>55000*K26</f>
+        <f>16100*K26</f>
         <v/>
       </c>
       <c r="I26" s="39">
-        <f>105000*K26</f>
+        <f>27300*K26</f>
         <v/>
       </c>
       <c r="J26" s="40" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="K26" s="40" t="n">
-        <v>1</v>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" s="40">
+        <f>IF('1 · Özet'!$B$4="ÖNERİLEN",1,0)</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="41" t="inlineStr">
         <is>
-          <t>05.02</t>
+          <t>07.04</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>ELEKTRİK</t>
+          <t>BOYA · DEKOR</t>
         </is>
       </c>
       <c r="C27" s="42" t="inlineStr">
         <is>
-          <t>Priz / anahtar / kuvvet noktası (sıva altı, komple)</t>
+          <t>Duvar grafiği / marka uygulaması</t>
         </is>
       </c>
       <c r="D27" s="43" t="inlineStr">
         <is>
-          <t>nokta</t>
+          <t>götürü</t>
         </is>
       </c>
       <c r="E27" s="44" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="F27" s="29" t="n"/>
       <c r="G27" s="45">
@@ -2609,45 +2610,46 @@
         <v/>
       </c>
       <c r="H27" s="46">
-        <f>60800*K27</f>
+        <f>28000*K27</f>
         <v/>
       </c>
       <c r="I27" s="46">
-        <f>102400*K27</f>
+        <f>60000*K27</f>
         <v/>
       </c>
       <c r="J27" s="47" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="K27" s="47" t="n">
-        <v>1</v>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" s="47">
+        <f>IF('1 · Özet'!$B$4="ÖNERİLEN",1,0)</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="34" t="inlineStr">
         <is>
-          <t>05.03</t>
+          <t>08.01</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ELEKTRİK</t>
+          <t>MARANGOZ</t>
         </is>
       </c>
       <c r="C28" s="35" t="inlineStr">
         <is>
-          <t>Lineer LED armatür 40 W / 4400 lm (montaj dahil)</t>
+          <t>Resepsiyon bankosu — 2,40 m, kompakt lamine tezgâh</t>
         </is>
       </c>
       <c r="D28" s="36" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E28" s="37" t="n">
-        <v>15</v>
+        <v>2.4</v>
       </c>
       <c r="F28" s="29" t="n"/>
       <c r="G28" s="38">
@@ -2655,11 +2657,11 @@
         <v/>
       </c>
       <c r="H28" s="39">
-        <f>21000*K28</f>
+        <f>26400*K28</f>
         <v/>
       </c>
       <c r="I28" s="39">
-        <f>39000*K28</f>
+        <f>45600*K28</f>
         <v/>
       </c>
       <c r="J28" s="40" t="inlineStr">
@@ -2674,26 +2676,26 @@
     <row r="29">
       <c r="A29" s="41" t="inlineStr">
         <is>
-          <t>05.06</t>
+          <t>08.02</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>ELEKTRİK</t>
+          <t>MARANGOZ</t>
         </is>
       </c>
       <c r="C29" s="42" t="inlineStr">
         <is>
-          <t>IP44 downlight 18 W / 1800 lm — ıslak hacim ve soyunma</t>
+          <t>Soyunma dolabı / askılık — 24 göz (2 blok)</t>
         </is>
       </c>
       <c r="D29" s="43" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>göz</t>
         </is>
       </c>
       <c r="E29" s="44" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F29" s="29" t="n"/>
       <c r="G29" s="45">
@@ -2701,11 +2703,11 @@
         <v/>
       </c>
       <c r="H29" s="46">
-        <f>5100*K29</f>
+        <f>57600*K29</f>
         <v/>
       </c>
       <c r="I29" s="46">
-        <f>9300*K29</f>
+        <f>100800*K29</f>
         <v/>
       </c>
       <c r="J29" s="47" t="inlineStr">
@@ -2720,26 +2722,26 @@
     <row r="30">
       <c r="A30" s="34" t="inlineStr">
         <is>
-          <t>05.04</t>
+          <t>08.03</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ELEKTRİK</t>
+          <t>MARANGOZ</t>
         </is>
       </c>
       <c r="C30" s="35" t="inlineStr">
         <is>
-          <t>Acil aydınlatma + yönlendirme armatürü</t>
+          <t>Oturma bankı (soyunma) + dinlenme mobilyası</t>
         </is>
       </c>
       <c r="D30" s="36" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>götürü</t>
         </is>
       </c>
       <c r="E30" s="37" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F30" s="29" t="n"/>
       <c r="G30" s="38">
@@ -2747,45 +2749,46 @@
         <v/>
       </c>
       <c r="H30" s="39">
-        <f>9200*K30</f>
+        <f>34000*K30</f>
         <v/>
       </c>
       <c r="I30" s="39">
-        <f>16800*K30</f>
+        <f>66000*K30</f>
         <v/>
       </c>
       <c r="J30" s="40" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="K30" s="40" t="n">
-        <v>1</v>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" s="40">
+        <f>IF('1 · Özet'!$B$4="ÖNERİLEN",1,0)</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="41" t="inlineStr">
         <is>
-          <t>05.05</t>
+          <t>09.01</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>ELEKTRİK</t>
+          <t>YANGIN · GÜVENLİK</t>
         </is>
       </c>
       <c r="C31" s="42" t="inlineStr">
         <is>
-          <t>Zayıf akım — ağ, ses sistemi, CCTV, geçiş kontrol altyapısı</t>
+          <t>6 kg KKT yangın söndürücü + dolap + montaj</t>
         </is>
       </c>
       <c r="D31" s="43" t="inlineStr">
         <is>
-          <t>götürü</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E31" s="44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F31" s="29" t="n"/>
       <c r="G31" s="45">
@@ -2793,46 +2796,45 @@
         <v/>
       </c>
       <c r="H31" s="46">
-        <f>55000*K31</f>
+        <f>12800*K31</f>
         <v/>
       </c>
       <c r="I31" s="46">
-        <f>110000*K31</f>
+        <f>21600*K31</f>
         <v/>
       </c>
       <c r="J31" s="47" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K31" s="47">
-        <f>IF('1 · Özet'!$B$4="ÖNERİLEN",1,0)</f>
-        <v/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K31" s="47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="34" t="inlineStr">
         <is>
-          <t>06.01</t>
+          <t>09.03</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MEKANİK</t>
+          <t>YANGIN · GÜVENLİK</t>
         </is>
       </c>
       <c r="C32" s="35" t="inlineStr">
         <is>
-          <t>Split klima 24.000 BTU inverter + montaj</t>
+          <t>Keskin köşe / kolon darbe hafifletici kaplama</t>
         </is>
       </c>
       <c r="D32" s="36" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E32" s="37" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F32" s="29" t="n"/>
       <c r="G32" s="38">
@@ -2840,11 +2842,11 @@
         <v/>
       </c>
       <c r="H32" s="39">
-        <f>96000*K32</f>
+        <f>15300*K32</f>
         <v/>
       </c>
       <c r="I32" s="39">
-        <f>156000*K32</f>
+        <f>27000*K32</f>
         <v/>
       </c>
       <c r="J32" s="40" t="inlineStr">
@@ -2859,22 +2861,22 @@
     <row r="33">
       <c r="A33" s="41" t="inlineStr">
         <is>
-          <t>06.02</t>
+          <t>09.04</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>MEKANİK</t>
+          <t>YANGIN · GÜVENLİK</t>
         </is>
       </c>
       <c r="C33" s="42" t="inlineStr">
         <is>
-          <t>Taze hava + egzoz seti 1000 m³/h (kanal, fan, menfez, susturucu)</t>
+          <t>Engelli erişimi — rampa, tutamak, kapı genişliği düzenlemesi</t>
         </is>
       </c>
       <c r="D33" s="43" t="inlineStr">
         <is>
-          <t>takım</t>
+          <t>götürü</t>
         </is>
       </c>
       <c r="E33" s="44" t="n">
@@ -2886,11 +2888,11 @@
         <v/>
       </c>
       <c r="H33" s="46">
+        <f>30000*K33</f>
+        <v/>
+      </c>
+      <c r="I33" s="46">
         <f>65000*K33</f>
-        <v/>
-      </c>
-      <c r="I33" s="46">
-        <f>120000*K33</f>
         <v/>
       </c>
       <c r="J33" s="47" t="inlineStr">
@@ -2905,17 +2907,17 @@
     <row r="34">
       <c r="A34" s="34" t="inlineStr">
         <is>
-          <t>06.03</t>
+          <t>09.05</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MEKANİK</t>
+          <t>YANGIN · GÜVENLİK</t>
         </is>
       </c>
       <c r="C34" s="35" t="inlineStr">
         <is>
-          <t>Islak hacim egzozu 240 m³/h (2 duş + 2 WC)</t>
+          <t>İlk yardım dolabı, AED, acil çıkış donanımı</t>
         </is>
       </c>
       <c r="D34" s="36" t="inlineStr">
@@ -2932,11 +2934,11 @@
         <v/>
       </c>
       <c r="H34" s="39">
-        <f>18000*K34</f>
+        <f>24000*K34</f>
         <v/>
       </c>
       <c r="I34" s="39">
-        <f>32000*K34</f>
+        <f>45000*K34</f>
         <v/>
       </c>
       <c r="J34" s="40" t="inlineStr">
@@ -2951,17 +2953,17 @@
     <row r="35">
       <c r="A35" s="41" t="inlineStr">
         <is>
-          <t>06.04</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>MEKANİK</t>
+          <t>TABELA · DIŞ</t>
         </is>
       </c>
       <c r="C35" s="42" t="inlineStr">
         <is>
-          <t>Sıhhi tesisat gider hatları, süzgeçler, havalandırma bacası</t>
+          <t>Işıklı kutu harf tabela + cephe folyo</t>
         </is>
       </c>
       <c r="D35" s="43" t="inlineStr">
@@ -2978,45 +2980,46 @@
         <v/>
       </c>
       <c r="H35" s="46">
-        <f>25000*K35</f>
+        <f>48000*K35</f>
         <v/>
       </c>
       <c r="I35" s="46">
-        <f>45000*K35</f>
+        <f>95000*K35</f>
         <v/>
       </c>
       <c r="J35" s="47" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="K35" s="47" t="n">
-        <v>1</v>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" s="47">
+        <f>IF('1 · Özet'!$B$4="ÖNERİLEN",1,0)</f>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="34" t="inlineStr">
         <is>
-          <t>07.01</t>
+          <t>10.02</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>BOYA · DEKOR</t>
+          <t>TABELA · DIŞ</t>
         </is>
       </c>
       <c r="C36" s="35" t="inlineStr">
         <is>
-          <t>Silinebilir mat duvar boyası (astar + 2 kat)</t>
+          <t>Cephe doğrama temizlik / bakım, giriş kapısı revizyonu</t>
         </is>
       </c>
       <c r="D36" s="36" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>götürü</t>
         </is>
       </c>
       <c r="E36" s="37" t="n">
-        <v>129.3</v>
+        <v>1</v>
       </c>
       <c r="F36" s="29" t="n"/>
       <c r="G36" s="38">
@@ -3024,11 +3027,11 @@
         <v/>
       </c>
       <c r="H36" s="39">
-        <f>19395*K36</f>
+        <f>26000*K36</f>
         <v/>
       </c>
       <c r="I36" s="39">
-        <f>36204*K36</f>
+        <f>50000*K36</f>
         <v/>
       </c>
       <c r="J36" s="40" t="inlineStr">
@@ -3043,26 +3046,26 @@
     <row r="37">
       <c r="A37" s="41" t="inlineStr">
         <is>
-          <t>07.02</t>
+          <t>06.01</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>BOYA · DEKOR</t>
+          <t>MEKANİK</t>
         </is>
       </c>
       <c r="C37" s="42" t="inlineStr">
         <is>
-          <t>Tavan boyası / açık tavan siyah boya (endüstriyel)</t>
+          <t>Kanal tipi taze hava fanı — 1.000 m³/h / 250 Pa, hız kontrollü</t>
         </is>
       </c>
       <c r="D37" s="43" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E37" s="44" t="n">
-        <v>103.78</v>
+        <v>1</v>
       </c>
       <c r="F37" s="29" t="n"/>
       <c r="G37" s="45">
@@ -3070,11 +3073,11 @@
         <v/>
       </c>
       <c r="H37" s="46">
-        <f>18680*K37</f>
+        <f>18500*K37</f>
         <v/>
       </c>
       <c r="I37" s="46">
-        <f>32172*K37</f>
+        <f>31000*K37</f>
         <v/>
       </c>
       <c r="J37" s="47" t="inlineStr">
@@ -3089,26 +3092,26 @@
     <row r="38">
       <c r="A38" s="34" t="inlineStr">
         <is>
-          <t>07.03</t>
+          <t>06.02</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>BOYA · DEKOR</t>
+          <t>MEKANİK</t>
         </is>
       </c>
       <c r="C38" s="35" t="inlineStr">
         <is>
-          <t>Ayna — arena ve fonksiyonel alan (6 mm, montaj dahil)</t>
+          <t>Kanal tipi egzoz fanı — 760 m³/h / 200 Pa</t>
         </is>
       </c>
       <c r="D38" s="36" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E38" s="37" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F38" s="29" t="n"/>
       <c r="G38" s="38">
@@ -3116,42 +3119,41 @@
         <v/>
       </c>
       <c r="H38" s="39">
-        <f>16100*K38</f>
+        <f>14500*K38</f>
         <v/>
       </c>
       <c r="I38" s="39">
-        <f>27300*K38</f>
+        <f>24000*K38</f>
         <v/>
       </c>
       <c r="J38" s="40" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K38" s="40">
-        <f>IF('1 · Özet'!$B$4="ÖNERİLEN",1,0)</f>
-        <v/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K38" s="40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="41" t="inlineStr">
         <is>
-          <t>07.04</t>
+          <t>06.03</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>BOYA · DEKOR</t>
+          <t>MEKANİK</t>
         </is>
       </c>
       <c r="C39" s="42" t="inlineStr">
         <is>
-          <t>Duvar grafiği / marka uygulaması</t>
+          <t>Islak hacim egzoz fanı — 240 m³/h, sessiz tip, nem sensörlü</t>
         </is>
       </c>
       <c r="D39" s="43" t="inlineStr">
         <is>
-          <t>götürü</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E39" s="44" t="n">
@@ -3163,37 +3165,36 @@
         <v/>
       </c>
       <c r="H39" s="46">
-        <f>28000*K39</f>
+        <f>6500*K39</f>
         <v/>
       </c>
       <c r="I39" s="46">
-        <f>60000*K39</f>
+        <f>11500*K39</f>
         <v/>
       </c>
       <c r="J39" s="47" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K39" s="47">
-        <f>IF('1 · Özet'!$B$4="ÖNERİLEN",1,0)</f>
-        <v/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K39" s="47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="34" t="inlineStr">
         <is>
-          <t>08.01</t>
+          <t>06.04</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MARANGOZ</t>
+          <t>MEKANİK</t>
         </is>
       </c>
       <c r="C40" s="35" t="inlineStr">
         <is>
-          <t>Resepsiyon bankosu — 2,40 m, kompakt lamine tezgâh</t>
+          <t>Galvaniz dikdörtgen kanal 500×150 — besleme ana hattı</t>
         </is>
       </c>
       <c r="D40" s="36" t="inlineStr">
@@ -3202,7 +3203,7 @@
         </is>
       </c>
       <c r="E40" s="37" t="n">
-        <v>2.4</v>
+        <v>10.3</v>
       </c>
       <c r="F40" s="29" t="n"/>
       <c r="G40" s="38">
@@ -3210,11 +3211,11 @@
         <v/>
       </c>
       <c r="H40" s="39">
-        <f>26400*K40</f>
+        <f>13905*K40</f>
         <v/>
       </c>
       <c r="I40" s="39">
-        <f>45600*K40</f>
+        <f>22660*K40</f>
         <v/>
       </c>
       <c r="J40" s="40" t="inlineStr">
@@ -3229,26 +3230,26 @@
     <row r="41">
       <c r="A41" s="41" t="inlineStr">
         <is>
-          <t>08.02</t>
+          <t>06.05</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>MARANGOZ</t>
+          <t>MEKANİK</t>
         </is>
       </c>
       <c r="C41" s="42" t="inlineStr">
         <is>
-          <t>Soyunma dolabı / askılık — 24 göz (2 blok)</t>
+          <t>Galvaniz dikdörtgen kanal 400×150 — egzoz ana hattı</t>
         </is>
       </c>
       <c r="D41" s="43" t="inlineStr">
         <is>
-          <t>göz</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E41" s="44" t="n">
-        <v>24</v>
+        <v>9.1</v>
       </c>
       <c r="F41" s="29" t="n"/>
       <c r="G41" s="45">
@@ -3256,11 +3257,11 @@
         <v/>
       </c>
       <c r="H41" s="46">
-        <f>57600*K41</f>
+        <f>10465*K41</f>
         <v/>
       </c>
       <c r="I41" s="46">
-        <f>100800*K41</f>
+        <f>17290*K41</f>
         <v/>
       </c>
       <c r="J41" s="47" t="inlineStr">
@@ -3275,26 +3276,26 @@
     <row r="42">
       <c r="A42" s="34" t="inlineStr">
         <is>
-          <t>08.03</t>
+          <t>06.06</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>MARANGOZ</t>
+          <t>MEKANİK</t>
         </is>
       </c>
       <c r="C42" s="35" t="inlineStr">
         <is>
-          <t>Oturma bankı (soyunma) + dinlenme mobilyası</t>
+          <t>Spiro kanal Ø200 — menfez branşmanları</t>
         </is>
       </c>
       <c r="D42" s="36" t="inlineStr">
         <is>
-          <t>götürü</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E42" s="37" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F42" s="29" t="n"/>
       <c r="G42" s="38">
@@ -3302,46 +3303,45 @@
         <v/>
       </c>
       <c r="H42" s="39">
-        <f>34000*K42</f>
+        <f>4960*K42</f>
         <v/>
       </c>
       <c r="I42" s="39">
-        <f>66000*K42</f>
+        <f>8400*K42</f>
         <v/>
       </c>
       <c r="J42" s="40" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K42" s="40">
-        <f>IF('1 · Özet'!$B$4="ÖNERİLEN",1,0)</f>
-        <v/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K42" s="40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="41" t="inlineStr">
         <is>
-          <t>09.01</t>
+          <t>06.06b</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>YANGIN · GÜVENLİK</t>
+          <t>MEKANİK</t>
         </is>
       </c>
       <c r="C43" s="42" t="inlineStr">
         <is>
-          <t>6 kg KKT yangın söndürücü + dolap + montaj</t>
+          <t>Spiro kanal Ø125 — ıslak hacim valf branşmanları</t>
         </is>
       </c>
       <c r="D43" s="43" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E43" s="44" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="F43" s="29" t="n"/>
       <c r="G43" s="45">
@@ -3349,11 +3349,11 @@
         <v/>
       </c>
       <c r="H43" s="46">
-        <f>12800*K43</f>
+        <f>1932*K43</f>
         <v/>
       </c>
       <c r="I43" s="46">
-        <f>21600*K43</f>
+        <f>3312*K43</f>
         <v/>
       </c>
       <c r="J43" s="47" t="inlineStr">
@@ -3368,26 +3368,26 @@
     <row r="44">
       <c r="A44" s="34" t="inlineStr">
         <is>
-          <t>09.02</t>
+          <t>06.07</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>YANGIN · GÜVENLİK</t>
+          <t>MEKANİK</t>
         </is>
       </c>
       <c r="C44" s="35" t="inlineStr">
         <is>
-          <t>Yangın algılama (duman dedektörü + siren + panel)</t>
+          <t>Spiro kanal Ø160 — ıslak hacim egzoz hattı</t>
         </is>
       </c>
       <c r="D44" s="36" t="inlineStr">
         <is>
-          <t>götürü</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E44" s="37" t="n">
-        <v>1</v>
+        <v>7.4</v>
       </c>
       <c r="F44" s="29" t="n"/>
       <c r="G44" s="38">
@@ -3395,11 +3395,11 @@
         <v/>
       </c>
       <c r="H44" s="39">
-        <f>32000*K44</f>
+        <f>3996*K44</f>
         <v/>
       </c>
       <c r="I44" s="39">
-        <f>65000*K44</f>
+        <f>6660*K44</f>
         <v/>
       </c>
       <c r="J44" s="40" t="inlineStr">
@@ -3414,26 +3414,26 @@
     <row r="45">
       <c r="A45" s="41" t="inlineStr">
         <is>
-          <t>09.03</t>
+          <t>06.08</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>YANGIN · GÜVENLİK</t>
+          <t>MEKANİK</t>
         </is>
       </c>
       <c r="C45" s="42" t="inlineStr">
         <is>
-          <t>Keskin köşe / kolon darbe hafifletici kaplama</t>
+          <t>Çift sıra ayarlı besleme menfezi 300×150 + plenum</t>
         </is>
       </c>
       <c r="D45" s="43" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E45" s="44" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F45" s="29" t="n"/>
       <c r="G45" s="45">
@@ -3441,11 +3441,11 @@
         <v/>
       </c>
       <c r="H45" s="46">
-        <f>15300*K45</f>
+        <f>9600*K45</f>
         <v/>
       </c>
       <c r="I45" s="46">
-        <f>27000*K45</f>
+        <f>15600*K45</f>
         <v/>
       </c>
       <c r="J45" s="47" t="inlineStr">
@@ -3460,26 +3460,26 @@
     <row r="46">
       <c r="A46" s="34" t="inlineStr">
         <is>
-          <t>09.04</t>
+          <t>06.09</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>YANGIN · GÜVENLİK</t>
+          <t>MEKANİK</t>
         </is>
       </c>
       <c r="C46" s="35" t="inlineStr">
         <is>
-          <t>Engelli erişimi — rampa, tutamak, kapı genişliği düzenlemesi</t>
+          <t>Egzoz menfezi 300×150 + plenum</t>
         </is>
       </c>
       <c r="D46" s="36" t="inlineStr">
         <is>
-          <t>götürü</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E46" s="37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F46" s="29" t="n"/>
       <c r="G46" s="38">
@@ -3487,11 +3487,11 @@
         <v/>
       </c>
       <c r="H46" s="39">
-        <f>30000*K46</f>
+        <f>6300*K46</f>
         <v/>
       </c>
       <c r="I46" s="39">
-        <f>65000*K46</f>
+        <f>10200*K46</f>
         <v/>
       </c>
       <c r="J46" s="40" t="inlineStr">
@@ -3506,26 +3506,26 @@
     <row r="47">
       <c r="A47" s="41" t="inlineStr">
         <is>
-          <t>09.05</t>
+          <t>06.10</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>YANGIN · GÜVENLİK</t>
+          <t>MEKANİK</t>
         </is>
       </c>
       <c r="C47" s="42" t="inlineStr">
         <is>
-          <t>İlk yardım dolabı, AED, acil çıkış donanımı</t>
+          <t>Tavan egzoz valfi Ø160 (duş / WC)</t>
         </is>
       </c>
       <c r="D47" s="43" t="inlineStr">
         <is>
-          <t>takım</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E47" s="44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F47" s="29" t="n"/>
       <c r="G47" s="45">
@@ -3533,11 +3533,11 @@
         <v/>
       </c>
       <c r="H47" s="46">
-        <f>24000*K47</f>
+        <f>3800*K47</f>
         <v/>
       </c>
       <c r="I47" s="46">
-        <f>45000*K47</f>
+        <f>6400*K47</f>
         <v/>
       </c>
       <c r="J47" s="47" t="inlineStr">
@@ -3552,26 +3552,26 @@
     <row r="48">
       <c r="A48" s="34" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>06.11</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>TABELA · DIŞ</t>
+          <t>MEKANİK</t>
         </is>
       </c>
       <c r="C48" s="35" t="inlineStr">
         <is>
-          <t>Işıklı kutu harf tabela + cephe folyo</t>
+          <t>Debi ayar damperi (branşman başı)</t>
         </is>
       </c>
       <c r="D48" s="36" t="inlineStr">
         <is>
-          <t>götürü</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E48" s="37" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F48" s="29" t="n"/>
       <c r="G48" s="38">
@@ -3579,46 +3579,45 @@
         <v/>
       </c>
       <c r="H48" s="39">
-        <f>48000*K48</f>
+        <f>8050*K48</f>
         <v/>
       </c>
       <c r="I48" s="39">
-        <f>95000*K48</f>
+        <f>13300*K48</f>
         <v/>
       </c>
       <c r="J48" s="40" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K48" s="40">
-        <f>IF('1 · Özet'!$B$4="ÖNERİLEN",1,0)</f>
-        <v/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K48" s="40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="41" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>06.12</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>TABELA · DIŞ</t>
+          <t>MEKANİK</t>
         </is>
       </c>
       <c r="C49" s="42" t="inlineStr">
         <is>
-          <t>Cephe doğrama temizlik / bakım, giriş kapısı revizyonu</t>
+          <t>Kanal susturucusu 1.000 mm — besleme ve egzoz</t>
         </is>
       </c>
       <c r="D49" s="43" t="inlineStr">
         <is>
-          <t>götürü</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E49" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" s="29" t="n"/>
       <c r="G49" s="45">
@@ -3626,11 +3625,11 @@
         <v/>
       </c>
       <c r="H49" s="46">
-        <f>26000*K49</f>
+        <f>13600*K49</f>
         <v/>
       </c>
       <c r="I49" s="46">
-        <f>50000*K49</f>
+        <f>23000*K49</f>
         <v/>
       </c>
       <c r="J49" s="47" t="inlineStr">
@@ -3642,34 +3641,2796 @@
         <v>1</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="34" t="inlineStr">
+        <is>
+          <t>06.13</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C50" s="35" t="inlineStr">
+        <is>
+          <t>Dış hava / egzoz panjuru + kuş teli</t>
+        </is>
+      </c>
+      <c r="D50" s="36" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E50" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" s="29" t="n"/>
+      <c r="G50" s="38">
+        <f>E50*F50*K50</f>
+        <v/>
+      </c>
+      <c r="H50" s="39">
+        <f>9600*K50</f>
+        <v/>
+      </c>
+      <c r="I50" s="39">
+        <f>16200*K50</f>
+        <v/>
+      </c>
+      <c r="J50" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K50" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="51">
-      <c r="A51" s="56" t="n"/>
-      <c r="B51" s="56" t="n"/>
-      <c r="C51" s="57" t="inlineStr">
+      <c r="A51" s="41" t="inlineStr">
+        <is>
+          <t>06.14</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C51" s="42" t="inlineStr">
+        <is>
+          <t>Kanal izolasyonu — 19 mm elastomerik kauçuk</t>
+        </is>
+      </c>
+      <c r="D51" s="43" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E51" s="44" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="F51" s="29" t="n"/>
+      <c r="G51" s="45">
+        <f>E51*F51*K51</f>
+        <v/>
+      </c>
+      <c r="H51" s="46">
+        <f>19656*K51</f>
+        <v/>
+      </c>
+      <c r="I51" s="46">
+        <f>32760*K51</f>
+        <v/>
+      </c>
+      <c r="J51" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K51" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="34" t="inlineStr">
+        <is>
+          <t>06.15</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C52" s="35" t="inlineStr">
+        <is>
+          <t>Kanal askı, taşıyıcı ve titreşim takozu</t>
+        </is>
+      </c>
+      <c r="D52" s="36" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E52" s="37" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F52" s="29" t="n"/>
+      <c r="G52" s="38">
+        <f>E52*F52*K52</f>
+        <v/>
+      </c>
+      <c r="H52" s="39">
+        <f>8576*K52</f>
+        <v/>
+      </c>
+      <c r="I52" s="39">
+        <f>14472*K52</f>
+        <v/>
+      </c>
+      <c r="J52" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K52" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="41" t="inlineStr">
+        <is>
+          <t>06.16</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C53" s="42" t="inlineStr">
+        <is>
+          <t>Hava debisi ölçümü, balanslama ve test raporu</t>
+        </is>
+      </c>
+      <c r="D53" s="43" t="inlineStr">
+        <is>
+          <t>götürü</t>
+        </is>
+      </c>
+      <c r="E53" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="29" t="n"/>
+      <c r="G53" s="45">
+        <f>E53*F53*K53</f>
+        <v/>
+      </c>
+      <c r="H53" s="46">
+        <f>12000*K53</f>
+        <v/>
+      </c>
+      <c r="I53" s="46">
+        <f>22000*K53</f>
+        <v/>
+      </c>
+      <c r="J53" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K53" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="48" t="inlineStr">
+        <is>
+          <t>06.17</t>
+        </is>
+      </c>
+      <c r="B54" s="49" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C54" s="50" t="inlineStr">
+        <is>
+          <t>SEÇENEK — ısı geri kazanımlı taze hava ünitesi 1.000 m³/h (%75 verim)</t>
+        </is>
+      </c>
+      <c r="D54" s="51" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E54" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="29" t="n"/>
+      <c r="G54" s="53">
+        <f>E54*F54*K54</f>
+        <v/>
+      </c>
+      <c r="H54" s="54">
+        <f>95000*K54</f>
+        <v/>
+      </c>
+      <c r="I54" s="54">
+        <f>165000*K54</f>
+        <v/>
+      </c>
+      <c r="J54" s="55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K54" s="55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="41" t="inlineStr">
+        <is>
+          <t>06.20</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C55" s="42" t="inlineStr">
+        <is>
+          <t>Duvar tipi inverter split klima 24.000 BTU (iç + dış ünite)</t>
+        </is>
+      </c>
+      <c r="D55" s="43" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E55" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="29" t="n"/>
+      <c r="G55" s="45">
+        <f>E55*F55*K55</f>
+        <v/>
+      </c>
+      <c r="H55" s="46">
+        <f>34000*K55</f>
+        <v/>
+      </c>
+      <c r="I55" s="46">
+        <f>55000*K55</f>
+        <v/>
+      </c>
+      <c r="J55" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K55" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="34" t="inlineStr">
+        <is>
+          <t>06.21</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C56" s="35" t="inlineStr">
+        <is>
+          <t>Duvar tipi inverter split klima 18.000 BTU (iç + dış ünite)</t>
+        </is>
+      </c>
+      <c r="D56" s="36" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E56" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="29" t="n"/>
+      <c r="G56" s="38">
+        <f>E56*F56*K56</f>
+        <v/>
+      </c>
+      <c r="H56" s="39">
+        <f>27000*K56</f>
+        <v/>
+      </c>
+      <c r="I56" s="39">
+        <f>44000*K56</f>
+        <v/>
+      </c>
+      <c r="J56" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K56" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="41" t="inlineStr">
+        <is>
+          <t>06.22</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C57" s="42" t="inlineStr">
+        <is>
+          <t>Duvar tipi inverter split klima 12.000 BTU (iç + dış ünite)</t>
+        </is>
+      </c>
+      <c r="D57" s="43" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E57" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" s="29" t="n"/>
+      <c r="G57" s="45">
+        <f>E57*F57*K57</f>
+        <v/>
+      </c>
+      <c r="H57" s="46">
+        <f>39000*K57</f>
+        <v/>
+      </c>
+      <c r="I57" s="46">
+        <f>64000*K57</f>
+        <v/>
+      </c>
+      <c r="J57" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K57" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="34" t="inlineStr">
+        <is>
+          <t>06.23</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C58" s="35" t="inlineStr">
+        <is>
+          <t>Bakır boru seti (1/4"–5/8") + izolasyon + bağlantı kablosu</t>
+        </is>
+      </c>
+      <c r="D58" s="36" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E58" s="37" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="F58" s="29" t="n"/>
+      <c r="G58" s="38">
+        <f>E58*F58*K58</f>
+        <v/>
+      </c>
+      <c r="H58" s="39">
+        <f>36850*K58</f>
+        <v/>
+      </c>
+      <c r="I58" s="39">
+        <f>61975*K58</f>
+        <v/>
+      </c>
+      <c r="J58" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K58" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="41" t="inlineStr">
+        <is>
+          <t>06.24</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C59" s="42" t="inlineStr">
+        <is>
+          <t>Dış ünite galvaniz montaj konsolu ve titreşim takozu</t>
+        </is>
+      </c>
+      <c r="D59" s="43" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E59" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="F59" s="29" t="n"/>
+      <c r="G59" s="45">
+        <f>E59*F59*K59</f>
+        <v/>
+      </c>
+      <c r="H59" s="46">
+        <f>15200*K59</f>
+        <v/>
+      </c>
+      <c r="I59" s="46">
+        <f>24800*K59</f>
+        <v/>
+      </c>
+      <c r="J59" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K59" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="34" t="inlineStr">
+        <is>
+          <t>06.25</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C60" s="35" t="inlineStr">
+        <is>
+          <t>Drenaj hattı PPRC Ø25 + izolasyon</t>
+        </is>
+      </c>
+      <c r="D60" s="36" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E60" s="37" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="F60" s="29" t="n"/>
+      <c r="G60" s="38">
+        <f>E60*F60*K60</f>
+        <v/>
+      </c>
+      <c r="H60" s="39">
+        <f>13272*K60</f>
+        <v/>
+      </c>
+      <c r="I60" s="39">
+        <f>22752*K60</f>
+        <v/>
+      </c>
+      <c r="J60" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K60" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="41" t="inlineStr">
+        <is>
+          <t>06.26</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C61" s="42" t="inlineStr">
+        <is>
+          <t>Vakum, gaz şarjı, devreye alma ve test</t>
+        </is>
+      </c>
+      <c r="D61" s="43" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E61" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="F61" s="29" t="n"/>
+      <c r="G61" s="45">
+        <f>E61*F61*K61</f>
+        <v/>
+      </c>
+      <c r="H61" s="46">
+        <f>12800*K61</f>
+        <v/>
+      </c>
+      <c r="I61" s="46">
+        <f>21600*K61</f>
+        <v/>
+      </c>
+      <c r="J61" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K61" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="34" t="inlineStr">
+        <is>
+          <t>06.30</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C62" s="35" t="inlineStr">
+        <is>
+          <t>PPRC temiz su borusu Ø25 (ek parça ve montaj dahil)</t>
+        </is>
+      </c>
+      <c r="D62" s="36" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E62" s="37" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F62" s="29" t="n"/>
+      <c r="G62" s="38">
+        <f>E62*F62*K62</f>
+        <v/>
+      </c>
+      <c r="H62" s="39">
+        <f>4278*K62</f>
+        <v/>
+      </c>
+      <c r="I62" s="39">
+        <f>7245*K62</f>
+        <v/>
+      </c>
+      <c r="J62" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K62" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="41" t="inlineStr">
+        <is>
+          <t>06.31</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C63" s="42" t="inlineStr">
+        <is>
+          <t>PPRC temiz su borusu Ø20 (ek parça ve montaj dahil)</t>
+        </is>
+      </c>
+      <c r="D63" s="43" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E63" s="44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F63" s="29" t="n"/>
+      <c r="G63" s="45">
+        <f>E63*F63*K63</f>
+        <v/>
+      </c>
+      <c r="H63" s="46">
+        <f>1612*K63</f>
+        <v/>
+      </c>
+      <c r="I63" s="46">
+        <f>2728*K63</f>
+        <v/>
+      </c>
+      <c r="J63" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K63" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="34" t="inlineStr">
+        <is>
+          <t>06.32</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C64" s="35" t="inlineStr">
+        <is>
+          <t>PPRC sıcak su hattı Ø20 + boru izolasyonu</t>
+        </is>
+      </c>
+      <c r="D64" s="36" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E64" s="37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F64" s="29" t="n"/>
+      <c r="G64" s="38">
+        <f>E64*F64*K64</f>
+        <v/>
+      </c>
+      <c r="H64" s="39">
+        <f>2856*K64</f>
+        <v/>
+      </c>
+      <c r="I64" s="39">
+        <f>4830*K64</f>
+        <v/>
+      </c>
+      <c r="J64" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K64" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="41" t="inlineStr">
+        <is>
+          <t>06.33</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C65" s="42" t="inlineStr">
+        <is>
+          <t>PVC pis su borusu Ø100 (%2 eğimli, askılı)</t>
+        </is>
+      </c>
+      <c r="D65" s="43" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E65" s="44" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F65" s="29" t="n"/>
+      <c r="G65" s="45">
+        <f>E65*F65*K65</f>
+        <v/>
+      </c>
+      <c r="H65" s="46">
+        <f>5772*K65</f>
+        <v/>
+      </c>
+      <c r="I65" s="46">
+        <f>9620*K65</f>
+        <v/>
+      </c>
+      <c r="J65" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K65" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="34" t="inlineStr">
+        <is>
+          <t>06.34</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C66" s="35" t="inlineStr">
+        <is>
+          <t>PVC pis su borusu Ø70</t>
+        </is>
+      </c>
+      <c r="D66" s="36" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E66" s="37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F66" s="29" t="n"/>
+      <c r="G66" s="38">
+        <f>E66*F66*K66</f>
+        <v/>
+      </c>
+      <c r="H66" s="39">
+        <f>168*K66</f>
+        <v/>
+      </c>
+      <c r="I66" s="39">
+        <f>285*K66</f>
+        <v/>
+      </c>
+      <c r="J66" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K66" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="41" t="inlineStr">
+        <is>
+          <t>06.35</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C67" s="42" t="inlineStr">
+        <is>
+          <t>PVC pis su borusu Ø50</t>
+        </is>
+      </c>
+      <c r="D67" s="43" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E67" s="44" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F67" s="29" t="n"/>
+      <c r="G67" s="45">
+        <f>E67*F67*K67</f>
+        <v/>
+      </c>
+      <c r="H67" s="46">
+        <f>1849*K67</f>
+        <v/>
+      </c>
+      <c r="I67" s="46">
+        <f>3182*K67</f>
+        <v/>
+      </c>
+      <c r="J67" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K67" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="34" t="inlineStr">
+        <is>
+          <t>06.36</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C68" s="35" t="inlineStr">
+        <is>
+          <t>Pis su havalandırma bacası Ø70 — çatı kotuna kadar</t>
+        </is>
+      </c>
+      <c r="D68" s="36" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E68" s="37" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F68" s="29" t="n"/>
+      <c r="G68" s="38">
+        <f>E68*F68*K68</f>
+        <v/>
+      </c>
+      <c r="H68" s="39">
+        <f>5890*K68</f>
+        <v/>
+      </c>
+      <c r="I68" s="39">
+        <f>9975*K68</f>
+        <v/>
+      </c>
+      <c r="J68" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K68" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="41" t="inlineStr">
+        <is>
+          <t>06.37</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C69" s="42" t="inlineStr">
+        <is>
+          <t>Paslanmaz sifonlu yer süzgeci 15×15</t>
+        </is>
+      </c>
+      <c r="D69" s="43" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E69" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" s="29" t="n"/>
+      <c r="G69" s="45">
+        <f>E69*F69*K69</f>
+        <v/>
+      </c>
+      <c r="H69" s="46">
+        <f>5800*K69</f>
+        <v/>
+      </c>
+      <c r="I69" s="46">
+        <f>9600*K69</f>
+        <v/>
+      </c>
+      <c r="J69" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K69" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="34" t="inlineStr">
+        <is>
+          <t>06.38</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C70" s="35" t="inlineStr">
+        <is>
+          <t>Küresel vana Ø25 / Ø20 (kolon ve branşman kesme)</t>
+        </is>
+      </c>
+      <c r="D70" s="36" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E70" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="F70" s="29" t="n"/>
+      <c r="G70" s="38">
+        <f>E70*F70*K70</f>
+        <v/>
+      </c>
+      <c r="H70" s="39">
+        <f>6240*K70</f>
+        <v/>
+      </c>
+      <c r="I70" s="39">
+        <f>10400*K70</f>
+        <v/>
+      </c>
+      <c r="J70" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K70" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="41" t="inlineStr">
+        <is>
+          <t>06.39</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C71" s="42" t="inlineStr">
+        <is>
+          <t>Sayaç sonrası ana kesme vanası + pislik tutucu filtre</t>
+        </is>
+      </c>
+      <c r="D71" s="43" t="inlineStr">
+        <is>
+          <t>takım</t>
+        </is>
+      </c>
+      <c r="E71" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="29" t="n"/>
+      <c r="G71" s="45">
+        <f>E71*F71*K71</f>
+        <v/>
+      </c>
+      <c r="H71" s="46">
+        <f>6500*K71</f>
+        <v/>
+      </c>
+      <c r="I71" s="46">
+        <f>11000*K71</f>
+        <v/>
+      </c>
+      <c r="J71" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K71" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="34" t="inlineStr">
+        <is>
+          <t>06.40</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C72" s="35" t="inlineStr">
+        <is>
+          <t>Elektrikli ani su ısıtıcı 6 kW (blok başına)</t>
+        </is>
+      </c>
+      <c r="D72" s="36" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E72" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" s="29" t="n"/>
+      <c r="G72" s="38">
+        <f>E72*F72*K72</f>
+        <v/>
+      </c>
+      <c r="H72" s="39">
+        <f>19600*K72</f>
+        <v/>
+      </c>
+      <c r="I72" s="39">
+        <f>34000*K72</f>
+        <v/>
+      </c>
+      <c r="J72" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K72" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="41" t="inlineStr">
+        <is>
+          <t>06.41</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>MEKANİK</t>
+        </is>
+      </c>
+      <c r="C73" s="42" t="inlineStr">
+        <is>
+          <t>Tesisat basınç testi, dezenfeksiyon ve teslim raporu</t>
+        </is>
+      </c>
+      <c r="D73" s="43" t="inlineStr">
+        <is>
+          <t>götürü</t>
+        </is>
+      </c>
+      <c r="E73" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="29" t="n"/>
+      <c r="G73" s="45">
+        <f>E73*F73*K73</f>
+        <v/>
+      </c>
+      <c r="H73" s="46">
+        <f>9500*K73</f>
+        <v/>
+      </c>
+      <c r="I73" s="46">
+        <f>17000*K73</f>
+        <v/>
+      </c>
+      <c r="J73" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K73" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="34" t="inlineStr">
+        <is>
+          <t>05.01</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C74" s="35" t="inlineStr">
+        <is>
+          <t>Ana dağıtım panosu — sıva üstü metal, 36 modül, montajlı</t>
+        </is>
+      </c>
+      <c r="D74" s="36" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E74" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="29" t="n"/>
+      <c r="G74" s="38">
+        <f>E74*F74*K74</f>
+        <v/>
+      </c>
+      <c r="H74" s="39">
+        <f>22000*K74</f>
+        <v/>
+      </c>
+      <c r="I74" s="39">
+        <f>37000*K74</f>
+        <v/>
+      </c>
+      <c r="J74" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K74" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="41" t="inlineStr">
+        <is>
+          <t>05.02</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C75" s="42" t="inlineStr">
+        <is>
+          <t>Ana kesici 3×40 A, C eğrisi</t>
+        </is>
+      </c>
+      <c r="D75" s="43" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E75" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="29" t="n"/>
+      <c r="G75" s="45">
+        <f>E75*F75*K75</f>
+        <v/>
+      </c>
+      <c r="H75" s="46">
+        <f>3200*K75</f>
+        <v/>
+      </c>
+      <c r="I75" s="46">
+        <f>5400*K75</f>
+        <v/>
+      </c>
+      <c r="J75" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K75" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="34" t="inlineStr">
+        <is>
+          <t>05.03</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C76" s="35" t="inlineStr">
+        <is>
+          <t>Kaçak akım rölesi 4×40 A / 30 mA (genel + ıslak hacim ayrı)</t>
+        </is>
+      </c>
+      <c r="D76" s="36" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E76" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F76" s="29" t="n"/>
+      <c r="G76" s="38">
+        <f>E76*F76*K76</f>
+        <v/>
+      </c>
+      <c r="H76" s="39">
+        <f>8400*K76</f>
+        <v/>
+      </c>
+      <c r="I76" s="39">
+        <f>14000*K76</f>
+        <v/>
+      </c>
+      <c r="J76" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K76" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="41" t="inlineStr">
+        <is>
+          <t>05.04</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C77" s="42" t="inlineStr">
+        <is>
+          <t>Otomatik sigorta (1×6 / 1×10 / 1×16 / 1×32 A)</t>
+        </is>
+      </c>
+      <c r="D77" s="43" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E77" s="44" t="n">
+        <v>21</v>
+      </c>
+      <c r="F77" s="29" t="n"/>
+      <c r="G77" s="45">
+        <f>E77*F77*K77</f>
+        <v/>
+      </c>
+      <c r="H77" s="46">
+        <f>13020*K77</f>
+        <v/>
+      </c>
+      <c r="I77" s="46">
+        <f>22050*K77</f>
+        <v/>
+      </c>
+      <c r="J77" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K77" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="34" t="inlineStr">
+        <is>
+          <t>05.05</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C78" s="35" t="inlineStr">
+        <is>
+          <t>Parafudr Tip 2 (aşırı gerilim koruma)</t>
+        </is>
+      </c>
+      <c r="D78" s="36" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E78" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="29" t="n"/>
+      <c r="G78" s="38">
+        <f>E78*F78*K78</f>
+        <v/>
+      </c>
+      <c r="H78" s="39">
+        <f>6800*K78</f>
+        <v/>
+      </c>
+      <c r="I78" s="39">
+        <f>11500*K78</f>
+        <v/>
+      </c>
+      <c r="J78" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K78" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="41" t="inlineStr">
+        <is>
+          <t>05.06</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C79" s="42" t="inlineStr">
+        <is>
+          <t>NYY kolon hattı 5×10 mm² — sayaçtan panoya</t>
+        </is>
+      </c>
+      <c r="D79" s="43" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E79" s="44" t="n">
+        <v>22</v>
+      </c>
+      <c r="F79" s="29" t="n"/>
+      <c r="G79" s="45">
+        <f>E79*F79*K79</f>
+        <v/>
+      </c>
+      <c r="H79" s="46">
+        <f>17160*K79</f>
+        <v/>
+      </c>
+      <c r="I79" s="46">
+        <f>28600*K79</f>
+        <v/>
+      </c>
+      <c r="J79" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K79" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="34" t="inlineStr">
+        <is>
+          <t>05.07</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C80" s="35" t="inlineStr">
+        <is>
+          <t>Pano etiketleme, tek hat şeması çerçevesi ve fonksiyon testi</t>
+        </is>
+      </c>
+      <c r="D80" s="36" t="inlineStr">
+        <is>
+          <t>götürü</t>
+        </is>
+      </c>
+      <c r="E80" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="29" t="n"/>
+      <c r="G80" s="38">
+        <f>E80*F80*K80</f>
+        <v/>
+      </c>
+      <c r="H80" s="39">
+        <f>6500*K80</f>
+        <v/>
+      </c>
+      <c r="I80" s="39">
+        <f>11000*K80</f>
+        <v/>
+      </c>
+      <c r="J80" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K80" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="41" t="inlineStr">
+        <is>
+          <t>05.10</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C81" s="42" t="inlineStr">
+        <is>
+          <t>Lineer LED armatür 40 W / 4400 lm, 1.200 mm (montaj dahil)</t>
+        </is>
+      </c>
+      <c r="D81" s="43" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E81" s="44" t="n">
+        <v>15</v>
+      </c>
+      <c r="F81" s="29" t="n"/>
+      <c r="G81" s="45">
+        <f>E81*F81*K81</f>
+        <v/>
+      </c>
+      <c r="H81" s="46">
+        <f>21000*K81</f>
+        <v/>
+      </c>
+      <c r="I81" s="46">
+        <f>39000*K81</f>
+        <v/>
+      </c>
+      <c r="J81" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K81" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="34" t="inlineStr">
+        <is>
+          <t>05.11</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C82" s="35" t="inlineStr">
+        <is>
+          <t>IP44 downlight 18 W / 1800 lm — ıslak hacim ve soyunma</t>
+        </is>
+      </c>
+      <c r="D82" s="36" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E82" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F82" s="29" t="n"/>
+      <c r="G82" s="38">
+        <f>E82*F82*K82</f>
+        <v/>
+      </c>
+      <c r="H82" s="39">
+        <f>5100*K82</f>
+        <v/>
+      </c>
+      <c r="I82" s="39">
+        <f>9300*K82</f>
+        <v/>
+      </c>
+      <c r="J82" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K82" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="41" t="inlineStr">
+        <is>
+          <t>05.12</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C83" s="42" t="inlineStr">
+        <is>
+          <t>Acil aydınlatma armatürü — 3 saat bataryalı</t>
+        </is>
+      </c>
+      <c r="D83" s="43" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E83" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="F83" s="29" t="n"/>
+      <c r="G83" s="45">
+        <f>E83*F83*K83</f>
+        <v/>
+      </c>
+      <c r="H83" s="46">
+        <f>6250*K83</f>
+        <v/>
+      </c>
+      <c r="I83" s="46">
+        <f>11000*K83</f>
+        <v/>
+      </c>
+      <c r="J83" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K83" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="34" t="inlineStr">
+        <is>
+          <t>05.13</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C84" s="35" t="inlineStr">
+        <is>
+          <t>Acil çıkış yönlendirme armatürü</t>
+        </is>
+      </c>
+      <c r="D84" s="36" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E84" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F84" s="29" t="n"/>
+      <c r="G84" s="38">
+        <f>E84*F84*K84</f>
+        <v/>
+      </c>
+      <c r="H84" s="39">
+        <f>3450*K84</f>
+        <v/>
+      </c>
+      <c r="I84" s="39">
+        <f>5850*K84</f>
+        <v/>
+      </c>
+      <c r="J84" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K84" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="41" t="inlineStr">
+        <is>
+          <t>05.14</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C85" s="42" t="inlineStr">
+        <is>
+          <t>Aydınlatma linyesi NHXMH 3×1,5 mm² — spiral boru ve işçilik dâhil</t>
+        </is>
+      </c>
+      <c r="D85" s="43" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E85" s="44" t="n">
+        <v>172</v>
+      </c>
+      <c r="F85" s="29" t="n"/>
+      <c r="G85" s="45">
+        <f>E85*F85*K85</f>
+        <v/>
+      </c>
+      <c r="H85" s="46">
+        <f>18920*K85</f>
+        <v/>
+      </c>
+      <c r="I85" s="46">
+        <f>31820*K85</f>
+        <v/>
+      </c>
+      <c r="J85" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K85" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="34" t="inlineStr">
+        <is>
+          <t>05.15</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C86" s="35" t="inlineStr">
+        <is>
+          <t>Anahtar / komütatör / vaviyen — sıva altı</t>
+        </is>
+      </c>
+      <c r="D86" s="36" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E86" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="F86" s="29" t="n"/>
+      <c r="G86" s="38">
+        <f>E86*F86*K86</f>
+        <v/>
+      </c>
+      <c r="H86" s="39">
+        <f>3360*K86</f>
+        <v/>
+      </c>
+      <c r="I86" s="39">
+        <f>5740*K86</f>
+        <v/>
+      </c>
+      <c r="J86" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K86" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="41" t="inlineStr">
+        <is>
+          <t>05.16</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C87" s="42" t="inlineStr">
+        <is>
+          <t>Hareket sensörü — ıslak hacim ve geçiş</t>
+        </is>
+      </c>
+      <c r="D87" s="43" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E87" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F87" s="29" t="n"/>
+      <c r="G87" s="45">
+        <f>E87*F87*K87</f>
+        <v/>
+      </c>
+      <c r="H87" s="46">
+        <f>4350*K87</f>
+        <v/>
+      </c>
+      <c r="I87" s="46">
+        <f>7200*K87</f>
+        <v/>
+      </c>
+      <c r="J87" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K87" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="34" t="inlineStr">
+        <is>
+          <t>05.20</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C88" s="35" t="inlineStr">
+        <is>
+          <t>İkili topraklı priz — sıva altı, komple</t>
+        </is>
+      </c>
+      <c r="D88" s="36" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E88" s="37" t="n">
+        <v>22</v>
+      </c>
+      <c r="F88" s="29" t="n"/>
+      <c r="G88" s="38">
+        <f>E88*F88*K88</f>
+        <v/>
+      </c>
+      <c r="H88" s="39">
+        <f>13640*K88</f>
+        <v/>
+      </c>
+      <c r="I88" s="39">
+        <f>23100*K88</f>
+        <v/>
+      </c>
+      <c r="J88" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K88" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="41" t="inlineStr">
+        <is>
+          <t>05.21</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C89" s="42" t="inlineStr">
+        <is>
+          <t>IP44 priz — ıslak hacim</t>
+        </is>
+      </c>
+      <c r="D89" s="43" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E89" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F89" s="29" t="n"/>
+      <c r="G89" s="45">
+        <f>E89*F89*K89</f>
+        <v/>
+      </c>
+      <c r="H89" s="46">
+        <f>1900*K89</f>
+        <v/>
+      </c>
+      <c r="I89" s="46">
+        <f>3200*K89</f>
+        <v/>
+      </c>
+      <c r="J89" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K89" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="34" t="inlineStr">
+        <is>
+          <t>05.22</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C90" s="35" t="inlineStr">
+        <is>
+          <t>Priz linyesi NHXMH 3×2,5 mm² — spiral boru ve işçilik dâhil</t>
+        </is>
+      </c>
+      <c r="D90" s="36" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E90" s="37" t="n">
+        <v>193</v>
+      </c>
+      <c r="F90" s="29" t="n"/>
+      <c r="G90" s="38">
+        <f>E90*F90*K90</f>
+        <v/>
+      </c>
+      <c r="H90" s="39">
+        <f>27020*K90</f>
+        <v/>
+      </c>
+      <c r="I90" s="39">
+        <f>44390*K90</f>
+        <v/>
+      </c>
+      <c r="J90" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K90" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="41" t="inlineStr">
+        <is>
+          <t>05.23</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C91" s="42" t="inlineStr">
+        <is>
+          <t>Klima besleme hattı 3×2,5 mm² + hat sonu kesici</t>
+        </is>
+      </c>
+      <c r="D91" s="43" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E91" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="F91" s="29" t="n"/>
+      <c r="G91" s="45">
+        <f>E91*F91*K91</f>
+        <v/>
+      </c>
+      <c r="H91" s="46">
+        <f>13600*K91</f>
+        <v/>
+      </c>
+      <c r="I91" s="46">
+        <f>22800*K91</f>
+        <v/>
+      </c>
+      <c r="J91" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K91" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="34" t="inlineStr">
+        <is>
+          <t>05.24</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C92" s="35" t="inlineStr">
+        <is>
+          <t>Su ısıtıcı besleme hattı 3×4 mm² + 32 A kesici</t>
+        </is>
+      </c>
+      <c r="D92" s="36" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E92" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" s="29" t="n"/>
+      <c r="G92" s="38">
+        <f>E92*F92*K92</f>
+        <v/>
+      </c>
+      <c r="H92" s="39">
+        <f>10400*K92</f>
+        <v/>
+      </c>
+      <c r="I92" s="39">
+        <f>17600*K92</f>
+        <v/>
+      </c>
+      <c r="J92" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K92" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="41" t="inlineStr">
+        <is>
+          <t>05.25</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C93" s="42" t="inlineStr">
+        <is>
+          <t>Havalandırma fanı besleme ve hız kontrol hattı</t>
+        </is>
+      </c>
+      <c r="D93" s="43" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E93" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F93" s="29" t="n"/>
+      <c r="G93" s="45">
+        <f>E93*F93*K93</f>
+        <v/>
+      </c>
+      <c r="H93" s="46">
+        <f>7200*K93</f>
+        <v/>
+      </c>
+      <c r="I93" s="46">
+        <f>12000*K93</f>
+        <v/>
+      </c>
+      <c r="J93" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K93" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="34" t="inlineStr">
+        <is>
+          <t>05.26</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C94" s="35" t="inlineStr">
+        <is>
+          <t>Banko kuvvet + veri kutusu (gömme)</t>
+        </is>
+      </c>
+      <c r="D94" s="36" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E94" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="29" t="n"/>
+      <c r="G94" s="38">
+        <f>E94*F94*K94</f>
+        <v/>
+      </c>
+      <c r="H94" s="39">
+        <f>7500*K94</f>
+        <v/>
+      </c>
+      <c r="I94" s="39">
+        <f>12500*K94</f>
+        <v/>
+      </c>
+      <c r="J94" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K94" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="41" t="inlineStr">
+        <is>
+          <t>05.30</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C95" s="42" t="inlineStr">
+        <is>
+          <t>Cat6 veri prizi + kablolama</t>
+        </is>
+      </c>
+      <c r="D95" s="43" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E95" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F95" s="29" t="n"/>
+      <c r="G95" s="45">
+        <f>E95*F95*K95</f>
+        <v/>
+      </c>
+      <c r="H95" s="46">
+        <f>8700*K95</f>
+        <v/>
+      </c>
+      <c r="I95" s="46">
+        <f>14700*K95</f>
+        <v/>
+      </c>
+      <c r="J95" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K95" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="34" t="inlineStr">
+        <is>
+          <t>05.31</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C96" s="35" t="inlineStr">
+        <is>
+          <t>Kablosuz erişim noktası (AP) + PoE besleme</t>
+        </is>
+      </c>
+      <c r="D96" s="36" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E96" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" s="29" t="n"/>
+      <c r="G96" s="38">
+        <f>E96*F96*K96</f>
+        <v/>
+      </c>
+      <c r="H96" s="39">
+        <f>13600*K96</f>
+        <v/>
+      </c>
+      <c r="I96" s="39">
+        <f>23000*K96</f>
+        <v/>
+      </c>
+      <c r="J96" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K96" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="41" t="inlineStr">
+        <is>
+          <t>05.32</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C97" s="42" t="inlineStr">
+        <is>
+          <t>IP güvenlik kamerası — iç mekân (soyunma ve WC HARİÇ)</t>
+        </is>
+      </c>
+      <c r="D97" s="43" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E97" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="F97" s="29" t="n"/>
+      <c r="G97" s="45">
+        <f>E97*F97*K97</f>
+        <v/>
+      </c>
+      <c r="H97" s="46">
+        <f>27000*K97</f>
+        <v/>
+      </c>
+      <c r="I97" s="46">
+        <f>45000*K97</f>
+        <v/>
+      </c>
+      <c r="J97" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K97" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="34" t="inlineStr">
+        <is>
+          <t>05.33</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C98" s="35" t="inlineStr">
+        <is>
+          <t>NVR + 4 TB disk + 9U rack kabinet</t>
+        </is>
+      </c>
+      <c r="D98" s="36" t="inlineStr">
+        <is>
+          <t>takım</t>
+        </is>
+      </c>
+      <c r="E98" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="29" t="n"/>
+      <c r="G98" s="38">
+        <f>E98*F98*K98</f>
+        <v/>
+      </c>
+      <c r="H98" s="39">
+        <f>24000*K98</f>
+        <v/>
+      </c>
+      <c r="I98" s="39">
+        <f>40000*K98</f>
+        <v/>
+      </c>
+      <c r="J98" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K98" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="41" t="inlineStr">
+        <is>
+          <t>05.34</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C99" s="42" t="inlineStr">
+        <is>
+          <t>Tavan hoparlörü 6 W / 100 V hat</t>
+        </is>
+      </c>
+      <c r="D99" s="43" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E99" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F99" s="29" t="n"/>
+      <c r="G99" s="45">
+        <f>E99*F99*K99</f>
+        <v/>
+      </c>
+      <c r="H99" s="46">
+        <f>9900*K99</f>
+        <v/>
+      </c>
+      <c r="I99" s="46">
+        <f>16800*K99</f>
+        <v/>
+      </c>
+      <c r="J99" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K99" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="34" t="inlineStr">
+        <is>
+          <t>05.35</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C100" s="35" t="inlineStr">
+        <is>
+          <t>Anfi / ses matrisi 120 W + kaynak</t>
+        </is>
+      </c>
+      <c r="D100" s="36" t="inlineStr">
+        <is>
+          <t>takım</t>
+        </is>
+      </c>
+      <c r="E100" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="29" t="n"/>
+      <c r="G100" s="38">
+        <f>E100*F100*K100</f>
+        <v/>
+      </c>
+      <c r="H100" s="39">
+        <f>14000*K100</f>
+        <v/>
+      </c>
+      <c r="I100" s="39">
+        <f>24000*K100</f>
+        <v/>
+      </c>
+      <c r="J100" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K100" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="41" t="inlineStr">
+        <is>
+          <t>05.36</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C101" s="42" t="inlineStr">
+        <is>
+          <t>Geçiş kontrol — kapı okuyucu + elektrikli kilit + buton</t>
+        </is>
+      </c>
+      <c r="D101" s="43" t="inlineStr">
+        <is>
+          <t>takım</t>
+        </is>
+      </c>
+      <c r="E101" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="29" t="n"/>
+      <c r="G101" s="45">
+        <f>E101*F101*K101</f>
+        <v/>
+      </c>
+      <c r="H101" s="46">
+        <f>16500*K101</f>
+        <v/>
+      </c>
+      <c r="I101" s="46">
+        <f>28000*K101</f>
+        <v/>
+      </c>
+      <c r="J101" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K101" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="34" t="inlineStr">
+        <is>
+          <t>05.37</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C102" s="35" t="inlineStr">
+        <is>
+          <t>Yangın algılama paneli — 2 zon, aküleriyle</t>
+        </is>
+      </c>
+      <c r="D102" s="36" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E102" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="29" t="n"/>
+      <c r="G102" s="38">
+        <f>E102*F102*K102</f>
+        <v/>
+      </c>
+      <c r="H102" s="39">
+        <f>14500*K102</f>
+        <v/>
+      </c>
+      <c r="I102" s="39">
+        <f>24500*K102</f>
+        <v/>
+      </c>
+      <c r="J102" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K102" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="41" t="inlineStr">
+        <is>
+          <t>05.38</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C103" s="42" t="inlineStr">
+        <is>
+          <t>Optik duman dedektörü</t>
+        </is>
+      </c>
+      <c r="D103" s="43" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E103" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F103" s="29" t="n"/>
+      <c r="G103" s="45">
+        <f>E103*F103*K103</f>
+        <v/>
+      </c>
+      <c r="H103" s="46">
+        <f>7500*K103</f>
+        <v/>
+      </c>
+      <c r="I103" s="46">
+        <f>12600*K103</f>
+        <v/>
+      </c>
+      <c r="J103" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K103" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="34" t="inlineStr">
+        <is>
+          <t>05.39</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C104" s="35" t="inlineStr">
+        <is>
+          <t>Yangın ihbar butonu / siren + flaşör</t>
+        </is>
+      </c>
+      <c r="D104" s="36" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E104" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F104" s="29" t="n"/>
+      <c r="G104" s="38">
+        <f>E104*F104*K104</f>
+        <v/>
+      </c>
+      <c r="H104" s="39">
+        <f>5550*K104</f>
+        <v/>
+      </c>
+      <c r="I104" s="39">
+        <f>9300*K104</f>
+        <v/>
+      </c>
+      <c r="J104" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K104" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="41" t="inlineStr">
+        <is>
+          <t>05.40</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C105" s="42" t="inlineStr">
+        <is>
+          <t>Zayıf akım kablolaması (Cat6, koaksiyel, ses, algılama)</t>
+        </is>
+      </c>
+      <c r="D105" s="43" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E105" s="44" t="n">
+        <v>210</v>
+      </c>
+      <c r="F105" s="29" t="n"/>
+      <c r="G105" s="45">
+        <f>E105*F105*K105</f>
+        <v/>
+      </c>
+      <c r="H105" s="46">
+        <f>12600*K105</f>
+        <v/>
+      </c>
+      <c r="I105" s="46">
+        <f>22050*K105</f>
+        <v/>
+      </c>
+      <c r="J105" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K105" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="34" t="inlineStr">
+        <is>
+          <t>05.45</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C106" s="35" t="inlineStr">
+        <is>
+          <t>Topraklama çubuğu, bağlantı ve ölçüm kutusu</t>
+        </is>
+      </c>
+      <c r="D106" s="36" t="inlineStr">
+        <is>
+          <t>takım</t>
+        </is>
+      </c>
+      <c r="E106" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="29" t="n"/>
+      <c r="G106" s="38">
+        <f>E106*F106*K106</f>
+        <v/>
+      </c>
+      <c r="H106" s="39">
+        <f>8500*K106</f>
+        <v/>
+      </c>
+      <c r="I106" s="39">
+        <f>14500*K106</f>
+        <v/>
+      </c>
+      <c r="J106" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K106" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="41" t="inlineStr">
+        <is>
+          <t>05.46</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C107" s="42" t="inlineStr">
+        <is>
+          <t>Ana potansiyel dengeleme barası ve iletkenleri</t>
+        </is>
+      </c>
+      <c r="D107" s="43" t="inlineStr">
+        <is>
+          <t>takım</t>
+        </is>
+      </c>
+      <c r="E107" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="29" t="n"/>
+      <c r="G107" s="45">
+        <f>E107*F107*K107</f>
+        <v/>
+      </c>
+      <c r="H107" s="46">
+        <f>5200*K107</f>
+        <v/>
+      </c>
+      <c r="I107" s="46">
+        <f>8800*K107</f>
+        <v/>
+      </c>
+      <c r="J107" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K107" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="34" t="inlineStr">
+        <is>
+          <t>05.47</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C108" s="35" t="inlineStr">
+        <is>
+          <t>Islak hacim ek potansiyel dengeleme</t>
+        </is>
+      </c>
+      <c r="D108" s="36" t="inlineStr">
+        <is>
+          <t>takım</t>
+        </is>
+      </c>
+      <c r="E108" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F108" s="29" t="n"/>
+      <c r="G108" s="38">
+        <f>E108*F108*K108</f>
+        <v/>
+      </c>
+      <c r="H108" s="39">
+        <f>5600*K108</f>
+        <v/>
+      </c>
+      <c r="I108" s="39">
+        <f>9400*K108</f>
+        <v/>
+      </c>
+      <c r="J108" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K108" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="41" t="inlineStr">
+        <is>
+          <t>05.48</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C109" s="42" t="inlineStr">
+        <is>
+          <t>Topraklama direnci ölçümü, izolasyon testi ve rapor</t>
+        </is>
+      </c>
+      <c r="D109" s="43" t="inlineStr">
+        <is>
+          <t>götürü</t>
+        </is>
+      </c>
+      <c r="E109" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="29" t="n"/>
+      <c r="G109" s="45">
+        <f>E109*F109*K109</f>
+        <v/>
+      </c>
+      <c r="H109" s="46">
+        <f>7500*K109</f>
+        <v/>
+      </c>
+      <c r="I109" s="46">
+        <f>13000*K109</f>
+        <v/>
+      </c>
+      <c r="J109" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K109" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="56" t="n"/>
+      <c r="B111" s="56" t="n"/>
+      <c r="C111" s="57" t="inlineStr">
         <is>
           <t>İMALAT ARA TOPLAMI</t>
         </is>
       </c>
-      <c r="D51" s="56" t="n"/>
-      <c r="E51" s="56" t="n"/>
-      <c r="F51" s="56" t="n"/>
-      <c r="G51" s="18">
-        <f>SUM(G4:G49)</f>
-        <v/>
-      </c>
-      <c r="H51" s="18">
-        <f>SUM(H4:H49)</f>
-        <v/>
-      </c>
-      <c r="I51" s="18">
-        <f>SUM(I4:I49)</f>
-        <v/>
-      </c>
-      <c r="J51" s="56" t="n"/>
-      <c r="K51" s="56" t="n"/>
+      <c r="D111" s="56" t="n"/>
+      <c r="E111" s="56" t="n"/>
+      <c r="F111" s="56" t="n"/>
+      <c r="G111" s="18">
+        <f>SUM(G4:G109)</f>
+        <v/>
+      </c>
+      <c r="H111" s="18">
+        <f>SUM(H4:H109)</f>
+        <v/>
+      </c>
+      <c r="I111" s="18">
+        <f>SUM(I4:I109)</f>
+        <v/>
+      </c>
+      <c r="J111" s="56" t="n"/>
+      <c r="K111" s="56" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K49"/>
+  <autoFilter ref="A3:K109"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -4262,11 +7023,11 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Klima adedi</t>
+          <t>Klima iç ünite adedi</t>
         </is>
       </c>
       <c r="B16" s="61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
@@ -4275,7 +7036,7 @@
       </c>
       <c r="D16" s="59" t="inlineStr">
         <is>
-          <t>57000 BTU / 24.000</t>
+          <t>bölge bazlı · kurulu 66000 BTU</t>
         </is>
       </c>
     </row>
@@ -4306,7 +7067,7 @@
         </is>
       </c>
       <c r="B18" s="61" t="n">
-        <v>16.3</v>
+        <v>26.59</v>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>

--- a/output/Gym_Maliyet_BoQ.xlsx
+++ b/output/Gym_Maliyet_BoQ.xlsx
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="E58" s="37" t="n">
-        <v>33.5</v>
+        <v>35.8</v>
       </c>
       <c r="F58" s="29" t="n"/>
       <c r="G58" s="38">
@@ -4041,11 +4041,11 @@
         <v/>
       </c>
       <c r="H58" s="39">
-        <f>36850*K58</f>
+        <f>39380*K58</f>
         <v/>
       </c>
       <c r="I58" s="39">
-        <f>61975*K58</f>
+        <f>66230*K58</f>
         <v/>
       </c>
       <c r="J58" s="40" t="inlineStr">
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="E60" s="37" t="n">
-        <v>31.6</v>
+        <v>34.2</v>
       </c>
       <c r="F60" s="29" t="n"/>
       <c r="G60" s="38">
@@ -4133,11 +4133,11 @@
         <v/>
       </c>
       <c r="H60" s="39">
-        <f>13272*K60</f>
+        <f>14364*K60</f>
         <v/>
       </c>
       <c r="I60" s="39">
-        <f>22752*K60</f>
+        <f>24624*K60</f>
         <v/>
       </c>
       <c r="J60" s="40" t="inlineStr">

--- a/output/Gym_Maliyet_BoQ.xlsx
+++ b/output/Gym_Maliyet_BoQ.xlsx
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="E42" s="37" t="n">
-        <v>8</v>
+        <v>10.7</v>
       </c>
       <c r="F42" s="29" t="n"/>
       <c r="G42" s="38">
@@ -3303,11 +3303,11 @@
         <v/>
       </c>
       <c r="H42" s="39">
-        <f>4960*K42</f>
+        <f>6634*K42</f>
         <v/>
       </c>
       <c r="I42" s="39">
-        <f>8400*K42</f>
+        <f>11235*K42</f>
         <v/>
       </c>
       <c r="J42" s="40" t="inlineStr">
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="E88" s="37" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F88" s="29" t="n"/>
       <c r="G88" s="38">
@@ -5421,11 +5421,11 @@
         <v/>
       </c>
       <c r="H88" s="39">
-        <f>13640*K88</f>
+        <f>12400*K88</f>
         <v/>
       </c>
       <c r="I88" s="39">
-        <f>23100*K88</f>
+        <f>21000*K88</f>
         <v/>
       </c>
       <c r="J88" s="40" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C92" s="35" t="inlineStr">
         <is>
-          <t>Su ısıtıcı besleme hattı 3×4 mm² + 32 A kesici</t>
+          <t>Su ısıtıcı besleme hattı 3×6 mm² + 32 A kesici + 30 mA kaçak akım</t>
         </is>
       </c>
       <c r="D92" s="36" t="inlineStr">
@@ -5605,11 +5605,11 @@
         <v/>
       </c>
       <c r="H92" s="39">
-        <f>10400*K92</f>
+        <f>12800*K92</f>
         <v/>
       </c>
       <c r="I92" s="39">
-        <f>17600*K92</f>
+        <f>21600*K92</f>
         <v/>
       </c>
       <c r="J92" s="40" t="inlineStr">

--- a/output/Gym_Maliyet_BoQ.xlsx
+++ b/output/Gym_Maliyet_BoQ.xlsx
@@ -13,7 +13,7 @@
     <sheet name="4 · Varsayımlar" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2 · Detay metraj'!$A$3:$K$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2 · Detay metraj'!$A$3:$K$114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -287,11 +287,11 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -787,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -808,7 +808,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rev C · 13 Eylül 2026 · Eylül 2026 piyasa mertebesi · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
+          <t>Rev E · 17 Eylül 2026 · Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="11">
-        <f>IFERROR((C7+D7)/2/(($C$17+$D$17)/2),0)</f>
+        <f>IFERROR((C7+D7)/2/(($C$18+$D$18)/2),0)</f>
         <v/>
       </c>
     </row>
@@ -924,7 +924,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="16">
-        <f>IFERROR((C8+D8)/2/(($C$17+$D$17)/2),0)</f>
+        <f>IFERROR((C8+D8)/2/(($C$18+$D$18)/2),0)</f>
         <v/>
       </c>
     </row>
@@ -950,7 +950,7 @@
         <v>7</v>
       </c>
       <c r="F9" s="11">
-        <f>IFERROR((C9+D9)/2/(($C$17+$D$17)/2),0)</f>
+        <f>IFERROR((C9+D9)/2/(($C$18+$D$18)/2),0)</f>
         <v/>
       </c>
     </row>
@@ -976,7 +976,7 @@
         <v>5</v>
       </c>
       <c r="F10" s="16">
-        <f>IFERROR((C10+D10)/2/(($C$17+$D$17)/2),0)</f>
+        <f>IFERROR((C10+D10)/2/(($C$18+$D$18)/2),0)</f>
         <v/>
       </c>
     </row>
@@ -987,22 +987,22 @@
         </is>
       </c>
       <c r="B11" s="8">
-        <f>'2 · Detay metraj'!G74+'2 · Detay metraj'!G75+'2 · Detay metraj'!G76+'2 · Detay metraj'!G77+'2 · Detay metraj'!G78+'2 · Detay metraj'!G79+'2 · Detay metraj'!G80+'2 · Detay metraj'!G81+'2 · Detay metraj'!G82+'2 · Detay metraj'!G83+'2 · Detay metraj'!G84+'2 · Detay metraj'!G85+'2 · Detay metraj'!G86+'2 · Detay metraj'!G87+'2 · Detay metraj'!G88+'2 · Detay metraj'!G89+'2 · Detay metraj'!G90+'2 · Detay metraj'!G91+'2 · Detay metraj'!G92+'2 · Detay metraj'!G93+'2 · Detay metraj'!G94+'2 · Detay metraj'!G95+'2 · Detay metraj'!G96+'2 · Detay metraj'!G97+'2 · Detay metraj'!G98+'2 · Detay metraj'!G99+'2 · Detay metraj'!G100+'2 · Detay metraj'!G101+'2 · Detay metraj'!G102+'2 · Detay metraj'!G103+'2 · Detay metraj'!G104+'2 · Detay metraj'!G105+'2 · Detay metraj'!G106+'2 · Detay metraj'!G107+'2 · Detay metraj'!G108+'2 · Detay metraj'!G109</f>
+        <f>'2 · Detay metraj'!G79+'2 · Detay metraj'!G80+'2 · Detay metraj'!G81+'2 · Detay metraj'!G82+'2 · Detay metraj'!G83+'2 · Detay metraj'!G84+'2 · Detay metraj'!G85+'2 · Detay metraj'!G86+'2 · Detay metraj'!G87+'2 · Detay metraj'!G88+'2 · Detay metraj'!G89+'2 · Detay metraj'!G90+'2 · Detay metraj'!G91+'2 · Detay metraj'!G92+'2 · Detay metraj'!G93+'2 · Detay metraj'!G94+'2 · Detay metraj'!G95+'2 · Detay metraj'!G96+'2 · Detay metraj'!G97+'2 · Detay metraj'!G98+'2 · Detay metraj'!G99+'2 · Detay metraj'!G100+'2 · Detay metraj'!G101+'2 · Detay metraj'!G102+'2 · Detay metraj'!G103+'2 · Detay metraj'!G104+'2 · Detay metraj'!G105+'2 · Detay metraj'!G106+'2 · Detay metraj'!G107+'2 · Detay metraj'!G108+'2 · Detay metraj'!G109+'2 · Detay metraj'!G110+'2 · Detay metraj'!G111+'2 · Detay metraj'!G112+'2 · Detay metraj'!G113+'2 · Detay metraj'!G114</f>
         <v/>
       </c>
       <c r="C11" s="9">
-        <f>'2 · Detay metraj'!H74+'2 · Detay metraj'!H75+'2 · Detay metraj'!H76+'2 · Detay metraj'!H77+'2 · Detay metraj'!H78+'2 · Detay metraj'!H79+'2 · Detay metraj'!H80+'2 · Detay metraj'!H81+'2 · Detay metraj'!H82+'2 · Detay metraj'!H83+'2 · Detay metraj'!H84+'2 · Detay metraj'!H85+'2 · Detay metraj'!H86+'2 · Detay metraj'!H87+'2 · Detay metraj'!H88+'2 · Detay metraj'!H89+'2 · Detay metraj'!H90+'2 · Detay metraj'!H91+'2 · Detay metraj'!H92+'2 · Detay metraj'!H93+'2 · Detay metraj'!H94+'2 · Detay metraj'!H95+'2 · Detay metraj'!H96+'2 · Detay metraj'!H97+'2 · Detay metraj'!H98+'2 · Detay metraj'!H99+'2 · Detay metraj'!H100+'2 · Detay metraj'!H101+'2 · Detay metraj'!H102+'2 · Detay metraj'!H103+'2 · Detay metraj'!H104+'2 · Detay metraj'!H105+'2 · Detay metraj'!H106+'2 · Detay metraj'!H107+'2 · Detay metraj'!H108+'2 · Detay metraj'!H109</f>
+        <f>'2 · Detay metraj'!H79+'2 · Detay metraj'!H80+'2 · Detay metraj'!H81+'2 · Detay metraj'!H82+'2 · Detay metraj'!H83+'2 · Detay metraj'!H84+'2 · Detay metraj'!H85+'2 · Detay metraj'!H86+'2 · Detay metraj'!H87+'2 · Detay metraj'!H88+'2 · Detay metraj'!H89+'2 · Detay metraj'!H90+'2 · Detay metraj'!H91+'2 · Detay metraj'!H92+'2 · Detay metraj'!H93+'2 · Detay metraj'!H94+'2 · Detay metraj'!H95+'2 · Detay metraj'!H96+'2 · Detay metraj'!H97+'2 · Detay metraj'!H98+'2 · Detay metraj'!H99+'2 · Detay metraj'!H100+'2 · Detay metraj'!H101+'2 · Detay metraj'!H102+'2 · Detay metraj'!H103+'2 · Detay metraj'!H104+'2 · Detay metraj'!H105+'2 · Detay metraj'!H106+'2 · Detay metraj'!H107+'2 · Detay metraj'!H108+'2 · Detay metraj'!H109+'2 · Detay metraj'!H110+'2 · Detay metraj'!H111+'2 · Detay metraj'!H112+'2 · Detay metraj'!H113+'2 · Detay metraj'!H114</f>
         <v/>
       </c>
       <c r="D11" s="9">
-        <f>'2 · Detay metraj'!I74+'2 · Detay metraj'!I75+'2 · Detay metraj'!I76+'2 · Detay metraj'!I77+'2 · Detay metraj'!I78+'2 · Detay metraj'!I79+'2 · Detay metraj'!I80+'2 · Detay metraj'!I81+'2 · Detay metraj'!I82+'2 · Detay metraj'!I83+'2 · Detay metraj'!I84+'2 · Detay metraj'!I85+'2 · Detay metraj'!I86+'2 · Detay metraj'!I87+'2 · Detay metraj'!I88+'2 · Detay metraj'!I89+'2 · Detay metraj'!I90+'2 · Detay metraj'!I91+'2 · Detay metraj'!I92+'2 · Detay metraj'!I93+'2 · Detay metraj'!I94+'2 · Detay metraj'!I95+'2 · Detay metraj'!I96+'2 · Detay metraj'!I97+'2 · Detay metraj'!I98+'2 · Detay metraj'!I99+'2 · Detay metraj'!I100+'2 · Detay metraj'!I101+'2 · Detay metraj'!I102+'2 · Detay metraj'!I103+'2 · Detay metraj'!I104+'2 · Detay metraj'!I105+'2 · Detay metraj'!I106+'2 · Detay metraj'!I107+'2 · Detay metraj'!I108+'2 · Detay metraj'!I109</f>
+        <f>'2 · Detay metraj'!I79+'2 · Detay metraj'!I80+'2 · Detay metraj'!I81+'2 · Detay metraj'!I82+'2 · Detay metraj'!I83+'2 · Detay metraj'!I84+'2 · Detay metraj'!I85+'2 · Detay metraj'!I86+'2 · Detay metraj'!I87+'2 · Detay metraj'!I88+'2 · Detay metraj'!I89+'2 · Detay metraj'!I90+'2 · Detay metraj'!I91+'2 · Detay metraj'!I92+'2 · Detay metraj'!I93+'2 · Detay metraj'!I94+'2 · Detay metraj'!I95+'2 · Detay metraj'!I96+'2 · Detay metraj'!I97+'2 · Detay metraj'!I98+'2 · Detay metraj'!I99+'2 · Detay metraj'!I100+'2 · Detay metraj'!I101+'2 · Detay metraj'!I102+'2 · Detay metraj'!I103+'2 · Detay metraj'!I104+'2 · Detay metraj'!I105+'2 · Detay metraj'!I106+'2 · Detay metraj'!I107+'2 · Detay metraj'!I108+'2 · Detay metraj'!I109+'2 · Detay metraj'!I110+'2 · Detay metraj'!I111+'2 · Detay metraj'!I112+'2 · Detay metraj'!I113+'2 · Detay metraj'!I114</f>
         <v/>
       </c>
       <c r="E11" s="10" t="n">
         <v>36</v>
       </c>
       <c r="F11" s="11">
-        <f>IFERROR((C11+D11)/2/(($C$17+$D$17)/2),0)</f>
+        <f>IFERROR((C11+D11)/2/(($C$18+$D$18)/2),0)</f>
         <v/>
       </c>
     </row>
@@ -1013,22 +1013,22 @@
         </is>
       </c>
       <c r="B12" s="13">
-        <f>'2 · Detay metraj'!G37+'2 · Detay metraj'!G38+'2 · Detay metraj'!G39+'2 · Detay metraj'!G40+'2 · Detay metraj'!G41+'2 · Detay metraj'!G42+'2 · Detay metraj'!G43+'2 · Detay metraj'!G44+'2 · Detay metraj'!G45+'2 · Detay metraj'!G46+'2 · Detay metraj'!G47+'2 · Detay metraj'!G48+'2 · Detay metraj'!G49+'2 · Detay metraj'!G50+'2 · Detay metraj'!G51+'2 · Detay metraj'!G52+'2 · Detay metraj'!G53+'2 · Detay metraj'!G54+'2 · Detay metraj'!G55+'2 · Detay metraj'!G56+'2 · Detay metraj'!G57+'2 · Detay metraj'!G58+'2 · Detay metraj'!G59+'2 · Detay metraj'!G60+'2 · Detay metraj'!G61+'2 · Detay metraj'!G62+'2 · Detay metraj'!G63+'2 · Detay metraj'!G64+'2 · Detay metraj'!G65+'2 · Detay metraj'!G66+'2 · Detay metraj'!G67+'2 · Detay metraj'!G68+'2 · Detay metraj'!G69+'2 · Detay metraj'!G70+'2 · Detay metraj'!G71+'2 · Detay metraj'!G72+'2 · Detay metraj'!G73</f>
+        <f>'2 · Detay metraj'!G42+'2 · Detay metraj'!G43+'2 · Detay metraj'!G44+'2 · Detay metraj'!G45+'2 · Detay metraj'!G46+'2 · Detay metraj'!G47+'2 · Detay metraj'!G48+'2 · Detay metraj'!G49+'2 · Detay metraj'!G50+'2 · Detay metraj'!G51+'2 · Detay metraj'!G52+'2 · Detay metraj'!G53+'2 · Detay metraj'!G54+'2 · Detay metraj'!G55+'2 · Detay metraj'!G56+'2 · Detay metraj'!G57+'2 · Detay metraj'!G58+'2 · Detay metraj'!G59+'2 · Detay metraj'!G60+'2 · Detay metraj'!G61+'2 · Detay metraj'!G62+'2 · Detay metraj'!G63+'2 · Detay metraj'!G64+'2 · Detay metraj'!G65+'2 · Detay metraj'!G66+'2 · Detay metraj'!G67+'2 · Detay metraj'!G68+'2 · Detay metraj'!G69+'2 · Detay metraj'!G70+'2 · Detay metraj'!G71+'2 · Detay metraj'!G72+'2 · Detay metraj'!G73+'2 · Detay metraj'!G74+'2 · Detay metraj'!G75+'2 · Detay metraj'!G76+'2 · Detay metraj'!G77+'2 · Detay metraj'!G78</f>
         <v/>
       </c>
       <c r="C12" s="14">
-        <f>'2 · Detay metraj'!H37+'2 · Detay metraj'!H38+'2 · Detay metraj'!H39+'2 · Detay metraj'!H40+'2 · Detay metraj'!H41+'2 · Detay metraj'!H42+'2 · Detay metraj'!H43+'2 · Detay metraj'!H44+'2 · Detay metraj'!H45+'2 · Detay metraj'!H46+'2 · Detay metraj'!H47+'2 · Detay metraj'!H48+'2 · Detay metraj'!H49+'2 · Detay metraj'!H50+'2 · Detay metraj'!H51+'2 · Detay metraj'!H52+'2 · Detay metraj'!H53+'2 · Detay metraj'!H54+'2 · Detay metraj'!H55+'2 · Detay metraj'!H56+'2 · Detay metraj'!H57+'2 · Detay metraj'!H58+'2 · Detay metraj'!H59+'2 · Detay metraj'!H60+'2 · Detay metraj'!H61+'2 · Detay metraj'!H62+'2 · Detay metraj'!H63+'2 · Detay metraj'!H64+'2 · Detay metraj'!H65+'2 · Detay metraj'!H66+'2 · Detay metraj'!H67+'2 · Detay metraj'!H68+'2 · Detay metraj'!H69+'2 · Detay metraj'!H70+'2 · Detay metraj'!H71+'2 · Detay metraj'!H72+'2 · Detay metraj'!H73</f>
+        <f>'2 · Detay metraj'!H42+'2 · Detay metraj'!H43+'2 · Detay metraj'!H44+'2 · Detay metraj'!H45+'2 · Detay metraj'!H46+'2 · Detay metraj'!H47+'2 · Detay metraj'!H48+'2 · Detay metraj'!H49+'2 · Detay metraj'!H50+'2 · Detay metraj'!H51+'2 · Detay metraj'!H52+'2 · Detay metraj'!H53+'2 · Detay metraj'!H54+'2 · Detay metraj'!H55+'2 · Detay metraj'!H56+'2 · Detay metraj'!H57+'2 · Detay metraj'!H58+'2 · Detay metraj'!H59+'2 · Detay metraj'!H60+'2 · Detay metraj'!H61+'2 · Detay metraj'!H62+'2 · Detay metraj'!H63+'2 · Detay metraj'!H64+'2 · Detay metraj'!H65+'2 · Detay metraj'!H66+'2 · Detay metraj'!H67+'2 · Detay metraj'!H68+'2 · Detay metraj'!H69+'2 · Detay metraj'!H70+'2 · Detay metraj'!H71+'2 · Detay metraj'!H72+'2 · Detay metraj'!H73+'2 · Detay metraj'!H74+'2 · Detay metraj'!H75+'2 · Detay metraj'!H76+'2 · Detay metraj'!H77+'2 · Detay metraj'!H78</f>
         <v/>
       </c>
       <c r="D12" s="14">
-        <f>'2 · Detay metraj'!I37+'2 · Detay metraj'!I38+'2 · Detay metraj'!I39+'2 · Detay metraj'!I40+'2 · Detay metraj'!I41+'2 · Detay metraj'!I42+'2 · Detay metraj'!I43+'2 · Detay metraj'!I44+'2 · Detay metraj'!I45+'2 · Detay metraj'!I46+'2 · Detay metraj'!I47+'2 · Detay metraj'!I48+'2 · Detay metraj'!I49+'2 · Detay metraj'!I50+'2 · Detay metraj'!I51+'2 · Detay metraj'!I52+'2 · Detay metraj'!I53+'2 · Detay metraj'!I54+'2 · Detay metraj'!I55+'2 · Detay metraj'!I56+'2 · Detay metraj'!I57+'2 · Detay metraj'!I58+'2 · Detay metraj'!I59+'2 · Detay metraj'!I60+'2 · Detay metraj'!I61+'2 · Detay metraj'!I62+'2 · Detay metraj'!I63+'2 · Detay metraj'!I64+'2 · Detay metraj'!I65+'2 · Detay metraj'!I66+'2 · Detay metraj'!I67+'2 · Detay metraj'!I68+'2 · Detay metraj'!I69+'2 · Detay metraj'!I70+'2 · Detay metraj'!I71+'2 · Detay metraj'!I72+'2 · Detay metraj'!I73</f>
+        <f>'2 · Detay metraj'!I42+'2 · Detay metraj'!I43+'2 · Detay metraj'!I44+'2 · Detay metraj'!I45+'2 · Detay metraj'!I46+'2 · Detay metraj'!I47+'2 · Detay metraj'!I48+'2 · Detay metraj'!I49+'2 · Detay metraj'!I50+'2 · Detay metraj'!I51+'2 · Detay metraj'!I52+'2 · Detay metraj'!I53+'2 · Detay metraj'!I54+'2 · Detay metraj'!I55+'2 · Detay metraj'!I56+'2 · Detay metraj'!I57+'2 · Detay metraj'!I58+'2 · Detay metraj'!I59+'2 · Detay metraj'!I60+'2 · Detay metraj'!I61+'2 · Detay metraj'!I62+'2 · Detay metraj'!I63+'2 · Detay metraj'!I64+'2 · Detay metraj'!I65+'2 · Detay metraj'!I66+'2 · Detay metraj'!I67+'2 · Detay metraj'!I68+'2 · Detay metraj'!I69+'2 · Detay metraj'!I70+'2 · Detay metraj'!I71+'2 · Detay metraj'!I72+'2 · Detay metraj'!I73+'2 · Detay metraj'!I74+'2 · Detay metraj'!I75+'2 · Detay metraj'!I76+'2 · Detay metraj'!I77+'2 · Detay metraj'!I78</f>
         <v/>
       </c>
       <c r="E12" s="15" t="n">
         <v>37</v>
       </c>
       <c r="F12" s="16">
-        <f>IFERROR((C12+D12)/2/(($C$17+$D$17)/2),0)</f>
+        <f>IFERROR((C12+D12)/2/(($C$18+$D$18)/2),0)</f>
         <v/>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
         <v>4</v>
       </c>
       <c r="F13" s="11">
-        <f>IFERROR((C13+D13)/2/(($C$17+$D$17)/2),0)</f>
+        <f>IFERROR((C13+D13)/2/(($C$18+$D$18)/2),0)</f>
         <v/>
       </c>
     </row>
@@ -1080,332 +1080,358 @@
         <v>3</v>
       </c>
       <c r="F14" s="16">
-        <f>IFERROR((C14+D14)/2/(($C$17+$D$17)/2),0)</f>
+        <f>IFERROR((C14+D14)/2/(($C$18+$D$18)/2),0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>YANGIN · GÜVENLİK</t>
+          <t>DOĞRAMA</t>
         </is>
       </c>
       <c r="B15" s="8">
-        <f>'2 · Detay metraj'!G31+'2 · Detay metraj'!G32+'2 · Detay metraj'!G33+'2 · Detay metraj'!G34</f>
+        <f>'2 · Detay metraj'!G37+'2 · Detay metraj'!G38+'2 · Detay metraj'!G39+'2 · Detay metraj'!G40+'2 · Detay metraj'!G41</f>
         <v/>
       </c>
       <c r="C15" s="9">
-        <f>'2 · Detay metraj'!H31+'2 · Detay metraj'!H32+'2 · Detay metraj'!H33+'2 · Detay metraj'!H34</f>
+        <f>'2 · Detay metraj'!H37+'2 · Detay metraj'!H38+'2 · Detay metraj'!H39+'2 · Detay metraj'!H40+'2 · Detay metraj'!H41</f>
         <v/>
       </c>
       <c r="D15" s="9">
-        <f>'2 · Detay metraj'!I31+'2 · Detay metraj'!I32+'2 · Detay metraj'!I33+'2 · Detay metraj'!I34</f>
+        <f>'2 · Detay metraj'!I37+'2 · Detay metraj'!I38+'2 · Detay metraj'!I39+'2 · Detay metraj'!I40+'2 · Detay metraj'!I41</f>
         <v/>
       </c>
       <c r="E15" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F15" s="11">
-        <f>IFERROR((C15+D15)/2/(($C$17+$D$17)/2),0)</f>
+        <f>IFERROR((C15+D15)/2/(($C$18+$D$18)/2),0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
+          <t>YANGIN · GÜVENLİK</t>
+        </is>
+      </c>
+      <c r="B16" s="13">
+        <f>'2 · Detay metraj'!G31+'2 · Detay metraj'!G32+'2 · Detay metraj'!G33+'2 · Detay metraj'!G34</f>
+        <v/>
+      </c>
+      <c r="C16" s="14">
+        <f>'2 · Detay metraj'!H31+'2 · Detay metraj'!H32+'2 · Detay metraj'!H33+'2 · Detay metraj'!H34</f>
+        <v/>
+      </c>
+      <c r="D16" s="14">
+        <f>'2 · Detay metraj'!I31+'2 · Detay metraj'!I32+'2 · Detay metraj'!I33+'2 · Detay metraj'!I34</f>
+        <v/>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="16">
+        <f>IFERROR((C16+D16)/2/(($C$18+$D$18)/2),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
           <t>TABELA · DIŞ</t>
         </is>
       </c>
-      <c r="B16" s="13">
+      <c r="B17" s="8">
         <f>'2 · Detay metraj'!G35+'2 · Detay metraj'!G36</f>
         <v/>
       </c>
-      <c r="C16" s="14">
+      <c r="C17" s="9">
         <f>'2 · Detay metraj'!H35+'2 · Detay metraj'!H36</f>
         <v/>
       </c>
-      <c r="D16" s="14">
+      <c r="D17" s="9">
         <f>'2 · Detay metraj'!I35+'2 · Detay metraj'!I36</f>
         <v/>
       </c>
-      <c r="E16" s="15" t="n">
+      <c r="E17" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="16">
-        <f>IFERROR((C16+D16)/2/(($C$17+$D$17)/2),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="F17" s="11">
+        <f>IFERROR((C17+D17)/2/(($C$18+$D$18)/2),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>İMALAT ARA TOPLAMI</t>
         </is>
       </c>
-      <c r="B17" s="18">
-        <f>SUM(B7:B16)</f>
-        <v/>
-      </c>
-      <c r="C17" s="18">
-        <f>SUM(C7:C16)</f>
-        <v/>
-      </c>
-      <c r="D17" s="18">
-        <f>SUM(D7:D16)</f>
-        <v/>
-      </c>
-      <c r="E17" s="19" t="n">
-        <v>106</v>
-      </c>
-      <c r="F17" s="20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="21" t="inlineStr">
-        <is>
-          <t>Şantiye genel giderleri (%9)</t>
-        </is>
-      </c>
-      <c r="B18" s="22">
-        <f>B17*0.09</f>
-        <v/>
-      </c>
-      <c r="C18" s="23">
-        <f>C17*0.09</f>
-        <v/>
-      </c>
-      <c r="D18" s="23">
-        <f>D17*0.09</f>
-        <v/>
-      </c>
-      <c r="E18" s="24" t="n"/>
-      <c r="F18" s="24" t="n"/>
+      <c r="B18" s="18">
+        <f>SUM(B7:B17)</f>
+        <v/>
+      </c>
+      <c r="C18" s="18">
+        <f>SUM(C7:C17)</f>
+        <v/>
+      </c>
+      <c r="D18" s="18">
+        <f>SUM(D7:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>111</v>
+      </c>
+      <c r="F18" s="20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="21" t="inlineStr">
         <is>
-          <t>Beklenmedik giderler (%15)</t>
+          <t>Şantiye genel giderleri (%12)</t>
         </is>
       </c>
       <c r="B19" s="22">
-        <f>(B17+B18)*0.15</f>
+        <f>B18*0.12</f>
         <v/>
       </c>
       <c r="C19" s="23">
-        <f>(C17+C18)*0.15</f>
+        <f>C18*0.12</f>
         <v/>
       </c>
       <c r="D19" s="23">
-        <f>(D17+D18)*0.15</f>
+        <f>D18*0.12</f>
         <v/>
       </c>
       <c r="E19" s="24" t="n"/>
       <c r="F19" s="24" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>Beklenmedik giderler (%15)</t>
+        </is>
+      </c>
+      <c r="B20" s="22">
+        <f>(B18+B19)*0.15</f>
+        <v/>
+      </c>
+      <c r="C20" s="23">
+        <f>(C18+C19)*0.15</f>
+        <v/>
+      </c>
+      <c r="D20" s="23">
+        <f>(D18+D19)*0.15</f>
+        <v/>
+      </c>
+      <c r="E20" s="24" t="n"/>
+      <c r="F20" s="24" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>GENEL TOPLAM</t>
         </is>
       </c>
-      <c r="B20" s="26">
-        <f>B17+B18+B19</f>
-        <v/>
-      </c>
-      <c r="C20" s="26">
-        <f>C17+C18+C19</f>
-        <v/>
-      </c>
-      <c r="D20" s="26">
-        <f>D17+D18+D19</f>
-        <v/>
-      </c>
-      <c r="E20" s="25" t="n"/>
-      <c r="F20" s="25" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="B21" s="26">
+        <f>B18+B19+B20</f>
+        <v/>
+      </c>
+      <c r="C21" s="26">
+        <f>C18+C19+C20</f>
+        <v/>
+      </c>
+      <c r="D21" s="26">
+        <f>D18+D19+D20</f>
+        <v/>
+      </c>
+      <c r="E21" s="25" t="n"/>
+      <c r="F21" s="25" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>m² başına (net iç alan)</t>
         </is>
       </c>
-      <c r="B22" s="8">
-        <f>B20/103.78</f>
-        <v/>
-      </c>
-      <c r="C22" s="8">
-        <f>C20/103.78</f>
-        <v/>
-      </c>
-      <c r="D22" s="8">
-        <f>D20/103.78</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="27" t="inlineStr">
+      <c r="B23" s="8">
+        <f>B21/103.78</f>
+        <v/>
+      </c>
+      <c r="C23" s="8">
+        <f>C21/103.78</f>
+        <v/>
+      </c>
+      <c r="D23" s="8">
+        <f>D21/103.78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>AÇILIŞ ÖNCESİ NAKİT İHTİYACI</t>
         </is>
       </c>
-      <c r="B24" s="27" t="n"/>
-      <c r="C24" s="27" t="n"/>
-      <c r="D24" s="27" t="n"/>
-      <c r="E24" s="27" t="n"/>
-      <c r="F24" s="27" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>Tadilat (genel toplam)</t>
-        </is>
-      </c>
-      <c r="B25" s="13">
-        <f>B20</f>
-        <v/>
-      </c>
-      <c r="C25" s="14">
-        <f>C20</f>
-        <v/>
-      </c>
-      <c r="D25" s="14">
-        <f>D20</f>
-        <v/>
-      </c>
+      <c r="B25" s="27" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="27" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="28" t="inlineStr">
         <is>
+          <t>Tadilat (genel toplam)</t>
+        </is>
+      </c>
+      <c r="B26" s="13">
+        <f>B21</f>
+        <v/>
+      </c>
+      <c r="C26" s="14">
+        <f>C21</f>
+        <v/>
+      </c>
+      <c r="D26" s="14">
+        <f>D21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
           <t>Ruhsat · harç · GSİM tescil · itfaiye · sağlık raporu</t>
         </is>
       </c>
-      <c r="B26" s="29" t="n"/>
-      <c r="C26" s="14" t="n">
+      <c r="B27" s="30" t="n"/>
+      <c r="C27" s="9" t="n">
         <v>85000</v>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D27" s="9" t="n">
         <v>175000</v>
       </c>
-      <c r="E26" s="28" t="n"/>
-      <c r="F26" s="28" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="30" t="inlineStr">
-        <is>
-          <t>Proje / mimari onaylı 1/100 vaziyet planı · müşavirlik</t>
-        </is>
-      </c>
-      <c r="B27" s="29" t="n"/>
-      <c r="C27" s="9" t="n">
-        <v>45000</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>95000</v>
-      </c>
-      <c r="E27" s="30" t="n"/>
-      <c r="F27" s="30" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="29" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="28" t="inlineStr">
         <is>
-          <t>İlk 3 ay kira</t>
-        </is>
-      </c>
-      <c r="B28" s="29" t="n"/>
+          <t>Proje / mimari onaylı 1/100 vaziyet planı · müşavirlik</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="n"/>
       <c r="C28" s="14" t="n">
-        <v>84000</v>
+        <v>45000</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>156000</v>
+        <v>95000</v>
       </c>
       <c r="E28" s="28" t="n"/>
       <c r="F28" s="28" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>Depozito (3 ay)</t>
-        </is>
-      </c>
-      <c r="B29" s="29" t="n"/>
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>İlk 3 ay kira</t>
+        </is>
+      </c>
+      <c r="B29" s="30" t="n"/>
       <c r="C29" s="9" t="n">
         <v>84000</v>
       </c>
       <c r="D29" s="9" t="n">
         <v>156000</v>
       </c>
-      <c r="E29" s="30" t="n"/>
-      <c r="F29" s="30" t="n"/>
+      <c r="E29" s="29" t="n"/>
+      <c r="F29" s="29" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="28" t="inlineStr">
         <is>
-          <t>Personel (açılış öncesi 2 ay · 2 kişi)</t>
-        </is>
-      </c>
-      <c r="B30" s="29" t="n"/>
+          <t>Depozito (3 ay)</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="n"/>
       <c r="C30" s="14" t="n">
-        <v>160000</v>
+        <v>84000</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>280000</v>
+        <v>156000</v>
       </c>
       <c r="E30" s="28" t="n"/>
       <c r="F30" s="28" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="30" t="inlineStr">
-        <is>
-          <t>Pazarlama · açılış kampanyası · dijital</t>
-        </is>
-      </c>
-      <c r="B31" s="29" t="n"/>
+      <c r="A31" s="29" t="inlineStr">
+        <is>
+          <t>Personel (açılış öncesi 2 ay · 2 kişi)</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="n"/>
       <c r="C31" s="9" t="n">
-        <v>95000</v>
+        <v>160000</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>210000</v>
-      </c>
-      <c r="E31" s="30" t="n"/>
-      <c r="F31" s="30" t="n"/>
+        <v>280000</v>
+      </c>
+      <c r="E31" s="29" t="n"/>
+      <c r="F31" s="29" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="28" t="inlineStr">
         <is>
-          <t>Yazılım (üyelik/POS), sarf, ilk stok</t>
-        </is>
-      </c>
-      <c r="B32" s="29" t="n"/>
+          <t>Pazarlama · açılış kampanyası · dijital</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="n"/>
       <c r="C32" s="14" t="n">
-        <v>55000</v>
+        <v>95000</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>120000</v>
+        <v>210000</v>
       </c>
       <c r="E32" s="28" t="n"/>
       <c r="F32" s="28" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="31" t="inlineStr">
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>Yazılım (üyelik/POS), sarf, ilk stok</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="n"/>
+      <c r="C33" s="9" t="n">
+        <v>55000</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E33" s="29" t="n"/>
+      <c r="F33" s="29" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="31" t="inlineStr">
         <is>
           <t>TOPLAM AÇILIŞ ÖNCESİ NAKİT</t>
         </is>
       </c>
-      <c r="B33" s="32">
-        <f>SUM(B25:B32)</f>
-        <v/>
-      </c>
-      <c r="C33" s="32">
-        <f>SUM(C25:C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="32">
-        <f>SUM(D25:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="31" t="n"/>
-      <c r="F33" s="31" t="n"/>
+      <c r="B34" s="32">
+        <f>SUM(B26:B33)</f>
+        <v/>
+      </c>
+      <c r="C34" s="32">
+        <f>SUM(C26:C33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="32">
+        <f>SUM(D26:D33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="31" t="n"/>
+      <c r="F34" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1430,7 +1456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K111"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1456,7 +1482,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev C · 13 Eylül 2026 · Fiyat referansı: Eylül 2026 piyasa mertebesi · Net iç alan 103.78 m²</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev E · 17 Eylül 2026 · Fiyat referansı: Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Net iç alan 103.78 m²</t>
         </is>
       </c>
     </row>
@@ -1541,17 +1567,17 @@
       <c r="E4" s="37" t="n">
         <v>103.78</v>
       </c>
-      <c r="F4" s="29" t="n"/>
+      <c r="F4" s="30" t="n"/>
       <c r="G4" s="38">
         <f>E4*F4*K4</f>
         <v/>
       </c>
       <c r="H4" s="39">
-        <f>18680*K4</f>
+        <f>35285*K4</f>
         <v/>
       </c>
       <c r="I4" s="39">
-        <f>33210*K4</f>
+        <f>60192*K4</f>
         <v/>
       </c>
       <c r="J4" s="40" t="inlineStr">
@@ -1587,17 +1613,17 @@
       <c r="E5" s="44" t="n">
         <v>103.78</v>
       </c>
-      <c r="F5" s="29" t="n"/>
+      <c r="F5" s="30" t="n"/>
       <c r="G5" s="45">
         <f>E5*F5*K5</f>
         <v/>
       </c>
       <c r="H5" s="46">
-        <f>26983*K5</f>
+        <f>43588*K5</f>
         <v/>
       </c>
       <c r="I5" s="46">
-        <f>46701*K5</f>
+        <f>67457*K5</f>
         <v/>
       </c>
       <c r="J5" s="47" t="inlineStr">
@@ -1633,17 +1659,17 @@
       <c r="E6" s="37" t="n">
         <v>16.73</v>
       </c>
-      <c r="F6" s="29" t="n"/>
+      <c r="F6" s="30" t="n"/>
       <c r="G6" s="38">
         <f>E6*F6*K6</f>
         <v/>
       </c>
       <c r="H6" s="39">
-        <f>6357*K6</f>
+        <f>10373*K6</f>
         <v/>
       </c>
       <c r="I6" s="39">
-        <f>10373*K6</f>
+        <f>15894*K6</f>
         <v/>
       </c>
       <c r="J6" s="40" t="inlineStr">
@@ -1679,17 +1705,17 @@
       <c r="E7" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="29" t="n"/>
+      <c r="F7" s="30" t="n"/>
       <c r="G7" s="45">
         <f>E7*F7*K7</f>
         <v/>
       </c>
       <c r="H7" s="46">
-        <f>28000*K7</f>
+        <f>48000*K7</f>
         <v/>
       </c>
       <c r="I7" s="46">
-        <f>55000*K7</f>
+        <f>75000*K7</f>
         <v/>
       </c>
       <c r="J7" s="47" t="inlineStr">
@@ -1725,17 +1751,17 @@
       <c r="E8" s="37" t="n">
         <v>44.6</v>
       </c>
-      <c r="F8" s="29" t="n"/>
+      <c r="F8" s="30" t="n"/>
       <c r="G8" s="38">
         <f>E8*F8*K8</f>
         <v/>
       </c>
       <c r="H8" s="39">
-        <f>26760*K8</f>
+        <f>138260*K8</f>
         <v/>
       </c>
       <c r="I8" s="39">
-        <f>42370*K8</f>
+        <f>173940*K8</f>
         <v/>
       </c>
       <c r="J8" s="40" t="inlineStr">
@@ -1771,17 +1797,17 @@
       <c r="E9" s="44" t="n">
         <v>20.1</v>
       </c>
-      <c r="F9" s="29" t="n"/>
+      <c r="F9" s="30" t="n"/>
       <c r="G9" s="45">
         <f>E9*F9*K9</f>
         <v/>
       </c>
       <c r="H9" s="46">
-        <f>5226*K9</f>
+        <f>7035*K9</f>
         <v/>
       </c>
       <c r="I9" s="46">
-        <f>8442*K9</f>
+        <f>10452*K9</f>
         <v/>
       </c>
       <c r="J9" s="47" t="inlineStr">
@@ -1817,17 +1843,17 @@
       <c r="E10" s="37" t="n">
         <v>129.3</v>
       </c>
-      <c r="F10" s="29" t="n"/>
+      <c r="F10" s="30" t="n"/>
       <c r="G10" s="38">
         <f>E10*F10*K10</f>
         <v/>
       </c>
       <c r="H10" s="39">
-        <f>28446*K10</f>
+        <f>49134*K10</f>
         <v/>
       </c>
       <c r="I10" s="39">
-        <f>49134*K10</f>
+        <f>72408*K10</f>
         <v/>
       </c>
       <c r="J10" s="40" t="inlineStr">
@@ -1863,17 +1889,17 @@
       <c r="E11" s="44" t="n">
         <v>12</v>
       </c>
-      <c r="F11" s="29" t="n"/>
+      <c r="F11" s="30" t="n"/>
       <c r="G11" s="45">
         <f>E11*F11*K11</f>
         <v/>
       </c>
       <c r="H11" s="46">
-        <f>9000*K11</f>
+        <f>31200*K11</f>
         <v/>
       </c>
       <c r="I11" s="46">
-        <f>15000*K11</f>
+        <f>50400*K11</f>
         <v/>
       </c>
       <c r="J11" s="47" t="inlineStr">
@@ -1910,17 +1936,17 @@
       <c r="E12" s="37" t="n">
         <v>24.3</v>
       </c>
-      <c r="F12" s="29" t="n"/>
+      <c r="F12" s="30" t="n"/>
       <c r="G12" s="38">
         <f>E12*F12*K12</f>
         <v/>
       </c>
       <c r="H12" s="39">
-        <f>11664*K12</f>
+        <f>19440*K12</f>
         <v/>
       </c>
       <c r="I12" s="39">
-        <f>18954*K12</f>
+        <f>26730*K12</f>
         <v/>
       </c>
       <c r="J12" s="40" t="inlineStr">
@@ -1956,17 +1982,17 @@
       <c r="E13" s="44" t="n">
         <v>16.73</v>
       </c>
-      <c r="F13" s="29" t="n"/>
+      <c r="F13" s="30" t="n"/>
       <c r="G13" s="45">
         <f>E13*F13*K13</f>
         <v/>
       </c>
       <c r="H13" s="46">
-        <f>12548*K13</f>
+        <f>28943*K13</f>
         <v/>
       </c>
       <c r="I13" s="46">
-        <f>20076*K13</f>
+        <f>41825*K13</f>
         <v/>
       </c>
       <c r="J13" s="47" t="inlineStr">
@@ -2002,17 +2028,17 @@
       <c r="E14" s="37" t="n">
         <v>55.7</v>
       </c>
-      <c r="F14" s="29" t="n"/>
+      <c r="F14" s="30" t="n"/>
       <c r="G14" s="38">
         <f>E14*F14*K14</f>
         <v/>
       </c>
       <c r="H14" s="39">
-        <f>47345*K14</f>
+        <f>99982*K14</f>
         <v/>
       </c>
       <c r="I14" s="39">
-        <f>75195*K14</f>
+        <f>147605*K14</f>
         <v/>
       </c>
       <c r="J14" s="40" t="inlineStr">
@@ -2048,17 +2074,17 @@
       <c r="E15" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="29" t="n"/>
+      <c r="F15" s="30" t="n"/>
       <c r="G15" s="45">
         <f>E15*F15*K15</f>
         <v/>
       </c>
       <c r="H15" s="46">
-        <f>24000*K15</f>
+        <f>52000*K15</f>
         <v/>
       </c>
       <c r="I15" s="46">
-        <f>44000*K15</f>
+        <f>96000*K15</f>
         <v/>
       </c>
       <c r="J15" s="47" t="inlineStr">
@@ -2094,17 +2120,17 @@
       <c r="E16" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="29" t="n"/>
+      <c r="F16" s="30" t="n"/>
       <c r="G16" s="38">
         <f>E16*F16*K16</f>
         <v/>
       </c>
       <c r="H16" s="39">
-        <f>32000*K16</f>
+        <f>44000*K16</f>
         <v/>
       </c>
       <c r="I16" s="39">
-        <f>60000*K16</f>
+        <f>80000*K16</f>
         <v/>
       </c>
       <c r="J16" s="40" t="inlineStr">
@@ -2140,17 +2166,17 @@
       <c r="E17" s="52" t="n">
         <v>16.73</v>
       </c>
-      <c r="F17" s="29" t="n"/>
+      <c r="F17" s="30" t="n"/>
       <c r="G17" s="53">
         <f>E17*F17*K17</f>
         <v/>
       </c>
       <c r="H17" s="54">
-        <f>14220*K17</f>
+        <f>23422*K17</f>
         <v/>
       </c>
       <c r="I17" s="54">
-        <f>23422*K17</f>
+        <f>38479*K17</f>
         <v/>
       </c>
       <c r="J17" s="55" t="inlineStr">
@@ -2187,17 +2213,17 @@
       <c r="E18" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="29" t="n"/>
+      <c r="F18" s="30" t="n"/>
       <c r="G18" s="53">
         <f>E18*F18*K18</f>
         <v/>
       </c>
       <c r="H18" s="54">
-        <f>72000*K18</f>
+        <f>95000*K18</f>
         <v/>
       </c>
       <c r="I18" s="54">
-        <f>128000*K18</f>
+        <f>170000*K18</f>
         <v/>
       </c>
       <c r="J18" s="55" t="inlineStr">
@@ -2234,17 +2260,17 @@
       <c r="E19" s="44" t="n">
         <v>31.76</v>
       </c>
-      <c r="F19" s="29" t="n"/>
+      <c r="F19" s="30" t="n"/>
       <c r="G19" s="45">
         <f>E19*F19*K19</f>
         <v/>
       </c>
       <c r="H19" s="46">
-        <f>36524*K19</f>
+        <f>87340*K19</f>
         <v/>
       </c>
       <c r="I19" s="46">
-        <f>57168*K19</f>
+        <f>124499*K19</f>
         <v/>
       </c>
       <c r="J19" s="47" t="inlineStr">
@@ -2280,17 +2306,17 @@
       <c r="E20" s="37" t="n">
         <v>31.76</v>
       </c>
-      <c r="F20" s="29" t="n"/>
+      <c r="F20" s="30" t="n"/>
       <c r="G20" s="38">
         <f>E20*F20*K20</f>
         <v/>
       </c>
       <c r="H20" s="39">
-        <f>9528*K20</f>
+        <f>26361*K20</f>
         <v/>
       </c>
       <c r="I20" s="39">
-        <f>16515*K20</f>
+        <f>40018*K20</f>
         <v/>
       </c>
       <c r="J20" s="40" t="inlineStr">
@@ -2327,17 +2353,17 @@
       <c r="E21" s="44" t="n">
         <v>22.31</v>
       </c>
-      <c r="F21" s="29" t="n"/>
+      <c r="F21" s="30" t="n"/>
       <c r="G21" s="45">
         <f>E21*F21*K21</f>
         <v/>
       </c>
       <c r="H21" s="46">
-        <f>15617*K21</f>
+        <f>36812*K21</f>
         <v/>
       </c>
       <c r="I21" s="46">
-        <f>25656*K21</f>
+        <f>53544*K21</f>
         <v/>
       </c>
       <c r="J21" s="47" t="inlineStr">
@@ -2373,17 +2399,17 @@
       <c r="E22" s="37" t="n">
         <v>32.98</v>
       </c>
-      <c r="F22" s="29" t="n"/>
+      <c r="F22" s="30" t="n"/>
       <c r="G22" s="38">
         <f>E22*F22*K22</f>
         <v/>
       </c>
       <c r="H22" s="39">
-        <f>18139*K22</f>
+        <f>45183*K22</f>
         <v/>
       </c>
       <c r="I22" s="39">
-        <f>31331*K22</f>
+        <f>69918*K22</f>
         <v/>
       </c>
       <c r="J22" s="40" t="inlineStr">
@@ -2419,17 +2445,17 @@
       <c r="E23" s="44" t="n">
         <v>71.5</v>
       </c>
-      <c r="F23" s="29" t="n"/>
+      <c r="F23" s="30" t="n"/>
       <c r="G23" s="45">
         <f>E23*F23*K23</f>
         <v/>
       </c>
       <c r="H23" s="46">
-        <f>11440*K23</f>
+        <f>25025*K23</f>
         <v/>
       </c>
       <c r="I23" s="46">
-        <f>20735*K23</f>
+        <f>39325*K23</f>
         <v/>
       </c>
       <c r="J23" s="47" t="inlineStr">
@@ -2465,17 +2491,17 @@
       <c r="E24" s="37" t="n">
         <v>129.3</v>
       </c>
-      <c r="F24" s="29" t="n"/>
+      <c r="F24" s="30" t="n"/>
       <c r="G24" s="38">
         <f>E24*F24*K24</f>
         <v/>
       </c>
       <c r="H24" s="39">
-        <f>19395*K24</f>
+        <f>49781*K24</f>
         <v/>
       </c>
       <c r="I24" s="39">
-        <f>36204*K24</f>
+        <f>78873*K24</f>
         <v/>
       </c>
       <c r="J24" s="40" t="inlineStr">
@@ -2511,17 +2537,17 @@
       <c r="E25" s="44" t="n">
         <v>103.78</v>
       </c>
-      <c r="F25" s="29" t="n"/>
+      <c r="F25" s="30" t="n"/>
       <c r="G25" s="45">
         <f>E25*F25*K25</f>
         <v/>
       </c>
       <c r="H25" s="46">
-        <f>18680*K25</f>
+        <f>42031*K25</f>
         <v/>
       </c>
       <c r="I25" s="46">
-        <f>32172*K25</f>
+        <f>65381*K25</f>
         <v/>
       </c>
       <c r="J25" s="47" t="inlineStr">
@@ -2557,17 +2583,17 @@
       <c r="E26" s="37" t="n">
         <v>14</v>
       </c>
-      <c r="F26" s="29" t="n"/>
+      <c r="F26" s="30" t="n"/>
       <c r="G26" s="38">
         <f>E26*F26*K26</f>
         <v/>
       </c>
       <c r="H26" s="39">
-        <f>16100*K26</f>
+        <f>64400*K26</f>
         <v/>
       </c>
       <c r="I26" s="39">
-        <f>27300*K26</f>
+        <f>103600*K26</f>
         <v/>
       </c>
       <c r="J26" s="40" t="inlineStr">
@@ -2604,17 +2630,17 @@
       <c r="E27" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="29" t="n"/>
+      <c r="F27" s="30" t="n"/>
       <c r="G27" s="45">
         <f>E27*F27*K27</f>
         <v/>
       </c>
       <c r="H27" s="46">
-        <f>28000*K27</f>
+        <f>48000*K27</f>
         <v/>
       </c>
       <c r="I27" s="46">
-        <f>60000*K27</f>
+        <f>95000*K27</f>
         <v/>
       </c>
       <c r="J27" s="47" t="inlineStr">
@@ -2651,17 +2677,17 @@
       <c r="E28" s="37" t="n">
         <v>2.4</v>
       </c>
-      <c r="F28" s="29" t="n"/>
+      <c r="F28" s="30" t="n"/>
       <c r="G28" s="38">
         <f>E28*F28*K28</f>
         <v/>
       </c>
       <c r="H28" s="39">
-        <f>26400*K28</f>
+        <f>62400*K28</f>
         <v/>
       </c>
       <c r="I28" s="39">
-        <f>45600*K28</f>
+        <f>103200*K28</f>
         <v/>
       </c>
       <c r="J28" s="40" t="inlineStr">
@@ -2697,17 +2723,17 @@
       <c r="E29" s="44" t="n">
         <v>24</v>
       </c>
-      <c r="F29" s="29" t="n"/>
+      <c r="F29" s="30" t="n"/>
       <c r="G29" s="45">
         <f>E29*F29*K29</f>
         <v/>
       </c>
       <c r="H29" s="46">
-        <f>57600*K29</f>
+        <f>62400*K29</f>
         <v/>
       </c>
       <c r="I29" s="46">
-        <f>100800*K29</f>
+        <f>105600*K29</f>
         <v/>
       </c>
       <c r="J29" s="47" t="inlineStr">
@@ -2743,17 +2769,17 @@
       <c r="E30" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="29" t="n"/>
+      <c r="F30" s="30" t="n"/>
       <c r="G30" s="38">
         <f>E30*F30*K30</f>
         <v/>
       </c>
       <c r="H30" s="39">
-        <f>34000*K30</f>
+        <f>48000*K30</f>
         <v/>
       </c>
       <c r="I30" s="39">
-        <f>66000*K30</f>
+        <f>92000*K30</f>
         <v/>
       </c>
       <c r="J30" s="40" t="inlineStr">
@@ -2790,17 +2816,17 @@
       <c r="E31" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="F31" s="29" t="n"/>
+      <c r="F31" s="30" t="n"/>
       <c r="G31" s="45">
         <f>E31*F31*K31</f>
         <v/>
       </c>
       <c r="H31" s="46">
-        <f>12800*K31</f>
+        <f>18000*K31</f>
         <v/>
       </c>
       <c r="I31" s="46">
-        <f>21600*K31</f>
+        <f>30400*K31</f>
         <v/>
       </c>
       <c r="J31" s="47" t="inlineStr">
@@ -2836,17 +2862,17 @@
       <c r="E32" s="37" t="n">
         <v>18</v>
       </c>
-      <c r="F32" s="29" t="n"/>
+      <c r="F32" s="30" t="n"/>
       <c r="G32" s="38">
         <f>E32*F32*K32</f>
         <v/>
       </c>
       <c r="H32" s="39">
-        <f>15300*K32</f>
+        <f>21600*K32</f>
         <v/>
       </c>
       <c r="I32" s="39">
-        <f>27000*K32</f>
+        <f>37800*K32</f>
         <v/>
       </c>
       <c r="J32" s="40" t="inlineStr">
@@ -2882,17 +2908,17 @@
       <c r="E33" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="29" t="n"/>
+      <c r="F33" s="30" t="n"/>
       <c r="G33" s="45">
         <f>E33*F33*K33</f>
         <v/>
       </c>
       <c r="H33" s="46">
-        <f>30000*K33</f>
+        <f>42000*K33</f>
         <v/>
       </c>
       <c r="I33" s="46">
-        <f>65000*K33</f>
+        <f>90000*K33</f>
         <v/>
       </c>
       <c r="J33" s="47" t="inlineStr">
@@ -2928,17 +2954,17 @@
       <c r="E34" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="29" t="n"/>
+      <c r="F34" s="30" t="n"/>
       <c r="G34" s="38">
         <f>E34*F34*K34</f>
         <v/>
       </c>
       <c r="H34" s="39">
-        <f>24000*K34</f>
+        <f>34000*K34</f>
         <v/>
       </c>
       <c r="I34" s="39">
-        <f>45000*K34</f>
+        <f>63000*K34</f>
         <v/>
       </c>
       <c r="J34" s="40" t="inlineStr">
@@ -2974,17 +3000,17 @@
       <c r="E35" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="29" t="n"/>
+      <c r="F35" s="30" t="n"/>
       <c r="G35" s="45">
         <f>E35*F35*K35</f>
         <v/>
       </c>
       <c r="H35" s="46">
-        <f>48000*K35</f>
+        <f>68000*K35</f>
         <v/>
       </c>
       <c r="I35" s="46">
-        <f>95000*K35</f>
+        <f>135000*K35</f>
         <v/>
       </c>
       <c r="J35" s="47" t="inlineStr">
@@ -3021,17 +3047,17 @@
       <c r="E36" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="29" t="n"/>
+      <c r="F36" s="30" t="n"/>
       <c r="G36" s="38">
         <f>E36*F36*K36</f>
         <v/>
       </c>
       <c r="H36" s="39">
-        <f>26000*K36</f>
+        <f>50000*K36</f>
         <v/>
       </c>
       <c r="I36" s="39">
-        <f>50000*K36</f>
+        <f>85000*K36</f>
         <v/>
       </c>
       <c r="J36" s="40" t="inlineStr">
@@ -3046,17 +3072,17 @@
     <row r="37">
       <c r="A37" s="41" t="inlineStr">
         <is>
-          <t>06.01</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>MEKANİK</t>
+          <t>DOĞRAMA</t>
         </is>
       </c>
       <c r="C37" s="42" t="inlineStr">
         <is>
-          <t>Kanal tipi taze hava fanı — 1.000 m³/h / 250 Pa, hız kontrollü</t>
+          <t>İç kapı K03 · K04 — panel kapı 90×210, kasa, pervaz ve donanım</t>
         </is>
       </c>
       <c r="D37" s="43" t="inlineStr">
@@ -3065,19 +3091,19 @@
         </is>
       </c>
       <c r="E37" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="29" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F37" s="30" t="n"/>
       <c r="G37" s="45">
         <f>E37*F37*K37</f>
         <v/>
       </c>
       <c r="H37" s="46">
-        <f>18500*K37</f>
+        <f>37000*K37</f>
         <v/>
       </c>
       <c r="I37" s="46">
-        <f>31000*K37</f>
+        <f>58000*K37</f>
         <v/>
       </c>
       <c r="J37" s="47" t="inlineStr">
@@ -3092,17 +3118,17 @@
     <row r="38">
       <c r="A38" s="34" t="inlineStr">
         <is>
-          <t>06.02</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>MEKANİK</t>
+          <t>DOĞRAMA</t>
         </is>
       </c>
       <c r="C38" s="35" t="inlineStr">
         <is>
-          <t>Kanal tipi egzoz fanı — 760 m³/h / 200 Pa</t>
+          <t>WC kapısı K05 · K06 — tam WPC 70×200, alt menfezli</t>
         </is>
       </c>
       <c r="D38" s="36" t="inlineStr">
@@ -3111,19 +3137,19 @@
         </is>
       </c>
       <c r="E38" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="29" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F38" s="30" t="n"/>
       <c r="G38" s="38">
         <f>E38*F38*K38</f>
         <v/>
       </c>
       <c r="H38" s="39">
-        <f>14500*K38</f>
+        <f>30000*K38</f>
         <v/>
       </c>
       <c r="I38" s="39">
-        <f>24000*K38</f>
+        <f>49000*K38</f>
         <v/>
       </c>
       <c r="J38" s="40" t="inlineStr">
@@ -3138,17 +3164,17 @@
     <row r="39">
       <c r="A39" s="41" t="inlineStr">
         <is>
-          <t>06.03</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>MEKANİK</t>
+          <t>DOĞRAMA</t>
         </is>
       </c>
       <c r="C39" s="42" t="inlineStr">
         <is>
-          <t>Islak hacim egzoz fanı — 240 m³/h, sessiz tip, nem sensörlü</t>
+          <t>Duş kapağı K07 · K08 — 6 mm temperli cam 70×195</t>
         </is>
       </c>
       <c r="D39" s="43" t="inlineStr">
@@ -3157,19 +3183,19 @@
         </is>
       </c>
       <c r="E39" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="29" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F39" s="30" t="n"/>
       <c r="G39" s="45">
         <f>E39*F39*K39</f>
         <v/>
       </c>
       <c r="H39" s="46">
-        <f>6500*K39</f>
+        <f>35000*K39</f>
         <v/>
       </c>
       <c r="I39" s="46">
-        <f>11500*K39</f>
+        <f>56000*K39</f>
         <v/>
       </c>
       <c r="J39" s="47" t="inlineStr">
@@ -3184,38 +3210,38 @@
     <row r="40">
       <c r="A40" s="34" t="inlineStr">
         <is>
-          <t>06.04</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MEKANİK</t>
+          <t>DOĞRAMA</t>
         </is>
       </c>
       <c r="C40" s="35" t="inlineStr">
         <is>
-          <t>Galvaniz dikdörtgen kanal 500×150 — besleme ana hattı</t>
+          <t>Depo / teknik dolap kapağı K09 — havalandırma menfezli</t>
         </is>
       </c>
       <c r="D40" s="36" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E40" s="37" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="F40" s="29" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F40" s="30" t="n"/>
       <c r="G40" s="38">
         <f>E40*F40*K40</f>
         <v/>
       </c>
       <c r="H40" s="39">
-        <f>13905*K40</f>
+        <f>9000*K40</f>
         <v/>
       </c>
       <c r="I40" s="39">
-        <f>22660*K40</f>
+        <f>15000*K40</f>
         <v/>
       </c>
       <c r="J40" s="40" t="inlineStr">
@@ -3230,38 +3256,38 @@
     <row r="41">
       <c r="A41" s="41" t="inlineStr">
         <is>
-          <t>06.05</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>MEKANİK</t>
+          <t>DOĞRAMA</t>
         </is>
       </c>
       <c r="C41" s="42" t="inlineStr">
         <is>
-          <t>Galvaniz dikdörtgen kanal 400×150 — egzoz ana hattı</t>
+          <t>Acil çıkış kapısı K02 — panik bar (EN 1125), kapı kapatıcı</t>
         </is>
       </c>
       <c r="D41" s="43" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E41" s="44" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="F41" s="29" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F41" s="30" t="n"/>
       <c r="G41" s="45">
         <f>E41*F41*K41</f>
         <v/>
       </c>
       <c r="H41" s="46">
-        <f>10465*K41</f>
+        <f>54000*K41</f>
         <v/>
       </c>
       <c r="I41" s="46">
-        <f>17290*K41</f>
+        <f>88000*K41</f>
         <v/>
       </c>
       <c r="J41" s="47" t="inlineStr">
@@ -3276,7 +3302,7 @@
     <row r="42">
       <c r="A42" s="34" t="inlineStr">
         <is>
-          <t>06.06</t>
+          <t>06.01</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3286,28 +3312,28 @@
       </c>
       <c r="C42" s="35" t="inlineStr">
         <is>
-          <t>Spiro kanal Ø200 — menfez branşmanları</t>
+          <t>Kanal tipi taze hava fanı — 1.000 m³/h / 250 Pa, hız kontrollü</t>
         </is>
       </c>
       <c r="D42" s="36" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E42" s="37" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F42" s="29" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F42" s="30" t="n"/>
       <c r="G42" s="38">
         <f>E42*F42*K42</f>
         <v/>
       </c>
       <c r="H42" s="39">
-        <f>6634*K42</f>
+        <f>18500*K42</f>
         <v/>
       </c>
       <c r="I42" s="39">
-        <f>11235*K42</f>
+        <f>31000*K42</f>
         <v/>
       </c>
       <c r="J42" s="40" t="inlineStr">
@@ -3322,7 +3348,7 @@
     <row r="43">
       <c r="A43" s="41" t="inlineStr">
         <is>
-          <t>06.06b</t>
+          <t>06.02</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -3332,28 +3358,28 @@
       </c>
       <c r="C43" s="42" t="inlineStr">
         <is>
-          <t>Spiro kanal Ø125 — ıslak hacim valf branşmanları</t>
+          <t>Kanal tipi egzoz fanı — 760 m³/h / 200 Pa</t>
         </is>
       </c>
       <c r="D43" s="43" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E43" s="44" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F43" s="29" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F43" s="30" t="n"/>
       <c r="G43" s="45">
         <f>E43*F43*K43</f>
         <v/>
       </c>
       <c r="H43" s="46">
-        <f>1932*K43</f>
+        <f>14500*K43</f>
         <v/>
       </c>
       <c r="I43" s="46">
-        <f>3312*K43</f>
+        <f>24000*K43</f>
         <v/>
       </c>
       <c r="J43" s="47" t="inlineStr">
@@ -3368,7 +3394,7 @@
     <row r="44">
       <c r="A44" s="34" t="inlineStr">
         <is>
-          <t>06.07</t>
+          <t>06.03</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3378,28 +3404,28 @@
       </c>
       <c r="C44" s="35" t="inlineStr">
         <is>
-          <t>Spiro kanal Ø160 — ıslak hacim egzoz hattı</t>
+          <t>Islak hacim egzoz fanı — 240 m³/h, sessiz tip, nem sensörlü</t>
         </is>
       </c>
       <c r="D44" s="36" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E44" s="37" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="F44" s="29" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F44" s="30" t="n"/>
       <c r="G44" s="38">
         <f>E44*F44*K44</f>
         <v/>
       </c>
       <c r="H44" s="39">
-        <f>3996*K44</f>
+        <f>6500*K44</f>
         <v/>
       </c>
       <c r="I44" s="39">
-        <f>6660*K44</f>
+        <f>11500*K44</f>
         <v/>
       </c>
       <c r="J44" s="40" t="inlineStr">
@@ -3414,7 +3440,7 @@
     <row r="45">
       <c r="A45" s="41" t="inlineStr">
         <is>
-          <t>06.08</t>
+          <t>06.04</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -3424,28 +3450,28 @@
       </c>
       <c r="C45" s="42" t="inlineStr">
         <is>
-          <t>Çift sıra ayarlı besleme menfezi 300×150 + plenum</t>
+          <t>Galvaniz dikdörtgen kanal 500×150 — besleme ana hattı</t>
         </is>
       </c>
       <c r="D45" s="43" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E45" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="F45" s="29" t="n"/>
+        <v>10.3</v>
+      </c>
+      <c r="F45" s="30" t="n"/>
       <c r="G45" s="45">
         <f>E45*F45*K45</f>
         <v/>
       </c>
       <c r="H45" s="46">
-        <f>9600*K45</f>
+        <f>13905*K45</f>
         <v/>
       </c>
       <c r="I45" s="46">
-        <f>15600*K45</f>
+        <f>22660*K45</f>
         <v/>
       </c>
       <c r="J45" s="47" t="inlineStr">
@@ -3460,7 +3486,7 @@
     <row r="46">
       <c r="A46" s="34" t="inlineStr">
         <is>
-          <t>06.09</t>
+          <t>06.05</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3470,28 +3496,28 @@
       </c>
       <c r="C46" s="35" t="inlineStr">
         <is>
-          <t>Egzoz menfezi 300×150 + plenum</t>
+          <t>Galvaniz dikdörtgen kanal 400×150 — egzoz ana hattı</t>
         </is>
       </c>
       <c r="D46" s="36" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E46" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="F46" s="29" t="n"/>
+        <v>9.1</v>
+      </c>
+      <c r="F46" s="30" t="n"/>
       <c r="G46" s="38">
         <f>E46*F46*K46</f>
         <v/>
       </c>
       <c r="H46" s="39">
-        <f>6300*K46</f>
+        <f>10465*K46</f>
         <v/>
       </c>
       <c r="I46" s="39">
-        <f>10200*K46</f>
+        <f>17290*K46</f>
         <v/>
       </c>
       <c r="J46" s="40" t="inlineStr">
@@ -3506,7 +3532,7 @@
     <row r="47">
       <c r="A47" s="41" t="inlineStr">
         <is>
-          <t>06.10</t>
+          <t>06.06</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -3516,28 +3542,28 @@
       </c>
       <c r="C47" s="42" t="inlineStr">
         <is>
-          <t>Tavan egzoz valfi Ø160 (duş / WC)</t>
+          <t>Spiro kanal Ø200 — menfez branşmanları</t>
         </is>
       </c>
       <c r="D47" s="43" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E47" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="F47" s="29" t="n"/>
+        <v>10.7</v>
+      </c>
+      <c r="F47" s="30" t="n"/>
       <c r="G47" s="45">
         <f>E47*F47*K47</f>
         <v/>
       </c>
       <c r="H47" s="46">
-        <f>3800*K47</f>
+        <f>6634*K47</f>
         <v/>
       </c>
       <c r="I47" s="46">
-        <f>6400*K47</f>
+        <f>11235*K47</f>
         <v/>
       </c>
       <c r="J47" s="47" t="inlineStr">
@@ -3552,7 +3578,7 @@
     <row r="48">
       <c r="A48" s="34" t="inlineStr">
         <is>
-          <t>06.11</t>
+          <t>06.06b</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3562,28 +3588,28 @@
       </c>
       <c r="C48" s="35" t="inlineStr">
         <is>
-          <t>Debi ayar damperi (branşman başı)</t>
+          <t>Spiro kanal Ø125 — ıslak hacim valf branşmanları</t>
         </is>
       </c>
       <c r="D48" s="36" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E48" s="37" t="n">
-        <v>7</v>
-      </c>
-      <c r="F48" s="29" t="n"/>
+        <v>4.6</v>
+      </c>
+      <c r="F48" s="30" t="n"/>
       <c r="G48" s="38">
         <f>E48*F48*K48</f>
         <v/>
       </c>
       <c r="H48" s="39">
-        <f>8050*K48</f>
+        <f>1932*K48</f>
         <v/>
       </c>
       <c r="I48" s="39">
-        <f>13300*K48</f>
+        <f>3312*K48</f>
         <v/>
       </c>
       <c r="J48" s="40" t="inlineStr">
@@ -3598,7 +3624,7 @@
     <row r="49">
       <c r="A49" s="41" t="inlineStr">
         <is>
-          <t>06.12</t>
+          <t>06.07</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -3608,28 +3634,28 @@
       </c>
       <c r="C49" s="42" t="inlineStr">
         <is>
-          <t>Kanal susturucusu 1.000 mm — besleme ve egzoz</t>
+          <t>Spiro kanal Ø160 — ıslak hacim egzoz hattı</t>
         </is>
       </c>
       <c r="D49" s="43" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E49" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="F49" s="29" t="n"/>
+        <v>7.4</v>
+      </c>
+      <c r="F49" s="30" t="n"/>
       <c r="G49" s="45">
         <f>E49*F49*K49</f>
         <v/>
       </c>
       <c r="H49" s="46">
-        <f>13600*K49</f>
+        <f>3996*K49</f>
         <v/>
       </c>
       <c r="I49" s="46">
-        <f>23000*K49</f>
+        <f>6660*K49</f>
         <v/>
       </c>
       <c r="J49" s="47" t="inlineStr">
@@ -3644,7 +3670,7 @@
     <row r="50">
       <c r="A50" s="34" t="inlineStr">
         <is>
-          <t>06.13</t>
+          <t>06.08</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3654,7 +3680,7 @@
       </c>
       <c r="C50" s="35" t="inlineStr">
         <is>
-          <t>Dış hava / egzoz panjuru + kuş teli</t>
+          <t>Çift sıra ayarlı besleme menfezi 300×150 + plenum</t>
         </is>
       </c>
       <c r="D50" s="36" t="inlineStr">
@@ -3663,9 +3689,9 @@
         </is>
       </c>
       <c r="E50" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="F50" s="29" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="F50" s="30" t="n"/>
       <c r="G50" s="38">
         <f>E50*F50*K50</f>
         <v/>
@@ -3675,7 +3701,7 @@
         <v/>
       </c>
       <c r="I50" s="39">
-        <f>16200*K50</f>
+        <f>15600*K50</f>
         <v/>
       </c>
       <c r="J50" s="40" t="inlineStr">
@@ -3690,7 +3716,7 @@
     <row r="51">
       <c r="A51" s="41" t="inlineStr">
         <is>
-          <t>06.14</t>
+          <t>06.09</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -3700,28 +3726,28 @@
       </c>
       <c r="C51" s="42" t="inlineStr">
         <is>
-          <t>Kanal izolasyonu — 19 mm elastomerik kauçuk</t>
+          <t>Egzoz menfezi 300×150 + plenum</t>
         </is>
       </c>
       <c r="D51" s="43" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E51" s="44" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="F51" s="29" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="F51" s="30" t="n"/>
       <c r="G51" s="45">
         <f>E51*F51*K51</f>
         <v/>
       </c>
       <c r="H51" s="46">
-        <f>19656*K51</f>
+        <f>6300*K51</f>
         <v/>
       </c>
       <c r="I51" s="46">
-        <f>32760*K51</f>
+        <f>10200*K51</f>
         <v/>
       </c>
       <c r="J51" s="47" t="inlineStr">
@@ -3736,7 +3762,7 @@
     <row r="52">
       <c r="A52" s="34" t="inlineStr">
         <is>
-          <t>06.15</t>
+          <t>06.10</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3746,28 +3772,28 @@
       </c>
       <c r="C52" s="35" t="inlineStr">
         <is>
-          <t>Kanal askı, taşıyıcı ve titreşim takozu</t>
+          <t>Tavan egzoz valfi Ø160 (duş / WC)</t>
         </is>
       </c>
       <c r="D52" s="36" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E52" s="37" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="F52" s="29" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="F52" s="30" t="n"/>
       <c r="G52" s="38">
         <f>E52*F52*K52</f>
         <v/>
       </c>
       <c r="H52" s="39">
-        <f>8576*K52</f>
+        <f>3800*K52</f>
         <v/>
       </c>
       <c r="I52" s="39">
-        <f>14472*K52</f>
+        <f>6400*K52</f>
         <v/>
       </c>
       <c r="J52" s="40" t="inlineStr">
@@ -3782,7 +3808,7 @@
     <row r="53">
       <c r="A53" s="41" t="inlineStr">
         <is>
-          <t>06.16</t>
+          <t>06.11</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -3792,28 +3818,28 @@
       </c>
       <c r="C53" s="42" t="inlineStr">
         <is>
-          <t>Hava debisi ölçümü, balanslama ve test raporu</t>
+          <t>Debi ayar damperi (branşman başı)</t>
         </is>
       </c>
       <c r="D53" s="43" t="inlineStr">
         <is>
-          <t>götürü</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E53" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="29" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="F53" s="30" t="n"/>
       <c r="G53" s="45">
         <f>E53*F53*K53</f>
         <v/>
       </c>
       <c r="H53" s="46">
-        <f>12000*K53</f>
+        <f>8050*K53</f>
         <v/>
       </c>
       <c r="I53" s="46">
-        <f>22000*K53</f>
+        <f>13300*K53</f>
         <v/>
       </c>
       <c r="J53" s="47" t="inlineStr">
@@ -3826,57 +3852,55 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="48" t="inlineStr">
-        <is>
-          <t>06.17</t>
-        </is>
-      </c>
-      <c r="B54" s="49" t="inlineStr">
+      <c r="A54" s="34" t="inlineStr">
+        <is>
+          <t>06.12</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>MEKANİK</t>
         </is>
       </c>
-      <c r="C54" s="50" t="inlineStr">
-        <is>
-          <t>SEÇENEK — ısı geri kazanımlı taze hava ünitesi 1.000 m³/h (%75 verim)</t>
-        </is>
-      </c>
-      <c r="D54" s="51" t="inlineStr">
+      <c r="C54" s="35" t="inlineStr">
+        <is>
+          <t>Kanal susturucusu 1.000 mm — besleme ve egzoz</t>
+        </is>
+      </c>
+      <c r="D54" s="36" t="inlineStr">
         <is>
           <t>adet</t>
         </is>
       </c>
-      <c r="E54" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="29" t="n"/>
-      <c r="G54" s="53">
+      <c r="E54" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" s="30" t="n"/>
+      <c r="G54" s="38">
         <f>E54*F54*K54</f>
         <v/>
       </c>
-      <c r="H54" s="54">
-        <f>95000*K54</f>
-        <v/>
-      </c>
-      <c r="I54" s="54">
-        <f>165000*K54</f>
-        <v/>
-      </c>
-      <c r="J54" s="55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K54" s="55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H54" s="39">
+        <f>13600*K54</f>
+        <v/>
+      </c>
+      <c r="I54" s="39">
+        <f>23000*K54</f>
+        <v/>
+      </c>
+      <c r="J54" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K54" s="40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="41" t="inlineStr">
         <is>
-          <t>06.20</t>
+          <t>06.13</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -3886,7 +3910,7 @@
       </c>
       <c r="C55" s="42" t="inlineStr">
         <is>
-          <t>Duvar tipi inverter split klima 24.000 BTU (iç + dış ünite)</t>
+          <t>Dış hava / egzoz panjuru + kuş teli</t>
         </is>
       </c>
       <c r="D55" s="43" t="inlineStr">
@@ -3895,19 +3919,19 @@
         </is>
       </c>
       <c r="E55" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="29" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="F55" s="30" t="n"/>
       <c r="G55" s="45">
         <f>E55*F55*K55</f>
         <v/>
       </c>
       <c r="H55" s="46">
-        <f>34000*K55</f>
+        <f>9600*K55</f>
         <v/>
       </c>
       <c r="I55" s="46">
-        <f>55000*K55</f>
+        <f>16200*K55</f>
         <v/>
       </c>
       <c r="J55" s="47" t="inlineStr">
@@ -3922,7 +3946,7 @@
     <row r="56">
       <c r="A56" s="34" t="inlineStr">
         <is>
-          <t>06.21</t>
+          <t>06.14</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3932,28 +3956,28 @@
       </c>
       <c r="C56" s="35" t="inlineStr">
         <is>
-          <t>Duvar tipi inverter split klima 18.000 BTU (iç + dış ünite)</t>
+          <t>Kanal izolasyonu — 19 mm elastomerik kauçuk</t>
         </is>
       </c>
       <c r="D56" s="36" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E56" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" s="29" t="n"/>
+        <v>25.2</v>
+      </c>
+      <c r="F56" s="30" t="n"/>
       <c r="G56" s="38">
         <f>E56*F56*K56</f>
         <v/>
       </c>
       <c r="H56" s="39">
-        <f>27000*K56</f>
+        <f>19656*K56</f>
         <v/>
       </c>
       <c r="I56" s="39">
-        <f>44000*K56</f>
+        <f>32760*K56</f>
         <v/>
       </c>
       <c r="J56" s="40" t="inlineStr">
@@ -3968,7 +3992,7 @@
     <row r="57">
       <c r="A57" s="41" t="inlineStr">
         <is>
-          <t>06.22</t>
+          <t>06.15</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -3978,28 +4002,28 @@
       </c>
       <c r="C57" s="42" t="inlineStr">
         <is>
-          <t>Duvar tipi inverter split klima 12.000 BTU (iç + dış ünite)</t>
+          <t>Kanal askı, taşıyıcı ve titreşim takozu</t>
         </is>
       </c>
       <c r="D57" s="43" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E57" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="F57" s="29" t="n"/>
+        <v>26.8</v>
+      </c>
+      <c r="F57" s="30" t="n"/>
       <c r="G57" s="45">
         <f>E57*F57*K57</f>
         <v/>
       </c>
       <c r="H57" s="46">
-        <f>39000*K57</f>
+        <f>8576*K57</f>
         <v/>
       </c>
       <c r="I57" s="46">
-        <f>64000*K57</f>
+        <f>14472*K57</f>
         <v/>
       </c>
       <c r="J57" s="47" t="inlineStr">
@@ -4014,7 +4038,7 @@
     <row r="58">
       <c r="A58" s="34" t="inlineStr">
         <is>
-          <t>06.23</t>
+          <t>06.16</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4024,28 +4048,28 @@
       </c>
       <c r="C58" s="35" t="inlineStr">
         <is>
-          <t>Bakır boru seti (1/4"–5/8") + izolasyon + bağlantı kablosu</t>
+          <t>Hava debisi ölçümü, balanslama ve test raporu</t>
         </is>
       </c>
       <c r="D58" s="36" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>götürü</t>
         </is>
       </c>
       <c r="E58" s="37" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="F58" s="29" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F58" s="30" t="n"/>
       <c r="G58" s="38">
         <f>E58*F58*K58</f>
         <v/>
       </c>
       <c r="H58" s="39">
-        <f>39380*K58</f>
+        <f>12000*K58</f>
         <v/>
       </c>
       <c r="I58" s="39">
-        <f>66230*K58</f>
+        <f>22000*K58</f>
         <v/>
       </c>
       <c r="J58" s="40" t="inlineStr">
@@ -4058,55 +4082,57 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="41" t="inlineStr">
-        <is>
-          <t>06.24</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="A59" s="48" t="inlineStr">
+        <is>
+          <t>06.17</t>
+        </is>
+      </c>
+      <c r="B59" s="49" t="inlineStr">
         <is>
           <t>MEKANİK</t>
         </is>
       </c>
-      <c r="C59" s="42" t="inlineStr">
-        <is>
-          <t>Dış ünite galvaniz montaj konsolu ve titreşim takozu</t>
-        </is>
-      </c>
-      <c r="D59" s="43" t="inlineStr">
+      <c r="C59" s="50" t="inlineStr">
+        <is>
+          <t>SEÇENEK — ısı geri kazanımlı taze hava ünitesi 1.000 m³/h (%75 verim)</t>
+        </is>
+      </c>
+      <c r="D59" s="51" t="inlineStr">
         <is>
           <t>adet</t>
         </is>
       </c>
-      <c r="E59" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="F59" s="29" t="n"/>
-      <c r="G59" s="45">
+      <c r="E59" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="30" t="n"/>
+      <c r="G59" s="53">
         <f>E59*F59*K59</f>
         <v/>
       </c>
-      <c r="H59" s="46">
-        <f>15200*K59</f>
-        <v/>
-      </c>
-      <c r="I59" s="46">
-        <f>24800*K59</f>
-        <v/>
-      </c>
-      <c r="J59" s="47" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="K59" s="47" t="n">
-        <v>1</v>
+      <c r="H59" s="54">
+        <f>95000*K59</f>
+        <v/>
+      </c>
+      <c r="I59" s="54">
+        <f>165000*K59</f>
+        <v/>
+      </c>
+      <c r="J59" s="55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K59" s="55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="34" t="inlineStr">
         <is>
-          <t>06.25</t>
+          <t>06.20</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4116,28 +4142,28 @@
       </c>
       <c r="C60" s="35" t="inlineStr">
         <is>
-          <t>Drenaj hattı PPRC Ø25 + izolasyon</t>
+          <t>Duvar tipi inverter split klima 24.000 BTU (iç + dış ünite)</t>
         </is>
       </c>
       <c r="D60" s="36" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E60" s="37" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="F60" s="29" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F60" s="30" t="n"/>
       <c r="G60" s="38">
         <f>E60*F60*K60</f>
         <v/>
       </c>
       <c r="H60" s="39">
-        <f>14364*K60</f>
+        <f>34000*K60</f>
         <v/>
       </c>
       <c r="I60" s="39">
-        <f>24624*K60</f>
+        <f>55000*K60</f>
         <v/>
       </c>
       <c r="J60" s="40" t="inlineStr">
@@ -4152,7 +4178,7 @@
     <row r="61">
       <c r="A61" s="41" t="inlineStr">
         <is>
-          <t>06.26</t>
+          <t>06.21</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -4162,7 +4188,7 @@
       </c>
       <c r="C61" s="42" t="inlineStr">
         <is>
-          <t>Vakum, gaz şarjı, devreye alma ve test</t>
+          <t>Duvar tipi inverter split klima 18.000 BTU (iç + dış ünite)</t>
         </is>
       </c>
       <c r="D61" s="43" t="inlineStr">
@@ -4171,19 +4197,19 @@
         </is>
       </c>
       <c r="E61" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="F61" s="29" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F61" s="30" t="n"/>
       <c r="G61" s="45">
         <f>E61*F61*K61</f>
         <v/>
       </c>
       <c r="H61" s="46">
-        <f>12800*K61</f>
+        <f>27000*K61</f>
         <v/>
       </c>
       <c r="I61" s="46">
-        <f>21600*K61</f>
+        <f>44000*K61</f>
         <v/>
       </c>
       <c r="J61" s="47" t="inlineStr">
@@ -4198,7 +4224,7 @@
     <row r="62">
       <c r="A62" s="34" t="inlineStr">
         <is>
-          <t>06.30</t>
+          <t>06.22</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4208,28 +4234,28 @@
       </c>
       <c r="C62" s="35" t="inlineStr">
         <is>
-          <t>PPRC temiz su borusu Ø25 (ek parça ve montaj dahil)</t>
+          <t>Duvar tipi inverter split klima 12.000 BTU (iç + dış ünite)</t>
         </is>
       </c>
       <c r="D62" s="36" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E62" s="37" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="F62" s="29" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F62" s="30" t="n"/>
       <c r="G62" s="38">
         <f>E62*F62*K62</f>
         <v/>
       </c>
       <c r="H62" s="39">
-        <f>4278*K62</f>
+        <f>39000*K62</f>
         <v/>
       </c>
       <c r="I62" s="39">
-        <f>7245*K62</f>
+        <f>64000*K62</f>
         <v/>
       </c>
       <c r="J62" s="40" t="inlineStr">
@@ -4244,7 +4270,7 @@
     <row r="63">
       <c r="A63" s="41" t="inlineStr">
         <is>
-          <t>06.31</t>
+          <t>06.23</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -4254,7 +4280,7 @@
       </c>
       <c r="C63" s="42" t="inlineStr">
         <is>
-          <t>PPRC temiz su borusu Ø20 (ek parça ve montaj dahil)</t>
+          <t>Bakır boru seti (1/4"–5/8") + izolasyon + bağlantı kablosu</t>
         </is>
       </c>
       <c r="D63" s="43" t="inlineStr">
@@ -4263,19 +4289,19 @@
         </is>
       </c>
       <c r="E63" s="44" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F63" s="29" t="n"/>
+        <v>35.8</v>
+      </c>
+      <c r="F63" s="30" t="n"/>
       <c r="G63" s="45">
         <f>E63*F63*K63</f>
         <v/>
       </c>
       <c r="H63" s="46">
-        <f>1612*K63</f>
+        <f>39380*K63</f>
         <v/>
       </c>
       <c r="I63" s="46">
-        <f>2728*K63</f>
+        <f>66230*K63</f>
         <v/>
       </c>
       <c r="J63" s="47" t="inlineStr">
@@ -4290,7 +4316,7 @@
     <row r="64">
       <c r="A64" s="34" t="inlineStr">
         <is>
-          <t>06.32</t>
+          <t>06.24</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4300,28 +4326,28 @@
       </c>
       <c r="C64" s="35" t="inlineStr">
         <is>
-          <t>PPRC sıcak su hattı Ø20 + boru izolasyonu</t>
+          <t>Dış ünite galvaniz montaj konsolu ve titreşim takozu</t>
         </is>
       </c>
       <c r="D64" s="36" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E64" s="37" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F64" s="29" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="F64" s="30" t="n"/>
       <c r="G64" s="38">
         <f>E64*F64*K64</f>
         <v/>
       </c>
       <c r="H64" s="39">
-        <f>2856*K64</f>
+        <f>15200*K64</f>
         <v/>
       </c>
       <c r="I64" s="39">
-        <f>4830*K64</f>
+        <f>24800*K64</f>
         <v/>
       </c>
       <c r="J64" s="40" t="inlineStr">
@@ -4336,7 +4362,7 @@
     <row r="65">
       <c r="A65" s="41" t="inlineStr">
         <is>
-          <t>06.33</t>
+          <t>06.25</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -4346,7 +4372,7 @@
       </c>
       <c r="C65" s="42" t="inlineStr">
         <is>
-          <t>PVC pis su borusu Ø100 (%2 eğimli, askılı)</t>
+          <t>Drenaj hattı PPRC Ø25 + izolasyon</t>
         </is>
       </c>
       <c r="D65" s="43" t="inlineStr">
@@ -4355,19 +4381,19 @@
         </is>
       </c>
       <c r="E65" s="44" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="F65" s="29" t="n"/>
+        <v>34.2</v>
+      </c>
+      <c r="F65" s="30" t="n"/>
       <c r="G65" s="45">
         <f>E65*F65*K65</f>
         <v/>
       </c>
       <c r="H65" s="46">
-        <f>5772*K65</f>
+        <f>14364*K65</f>
         <v/>
       </c>
       <c r="I65" s="46">
-        <f>9620*K65</f>
+        <f>24624*K65</f>
         <v/>
       </c>
       <c r="J65" s="47" t="inlineStr">
@@ -4382,7 +4408,7 @@
     <row r="66">
       <c r="A66" s="34" t="inlineStr">
         <is>
-          <t>06.34</t>
+          <t>06.26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4392,28 +4418,28 @@
       </c>
       <c r="C66" s="35" t="inlineStr">
         <is>
-          <t>PVC pis su borusu Ø70</t>
+          <t>Vakum, gaz şarjı, devreye alma ve test</t>
         </is>
       </c>
       <c r="D66" s="36" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E66" s="37" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F66" s="29" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="F66" s="30" t="n"/>
       <c r="G66" s="38">
         <f>E66*F66*K66</f>
         <v/>
       </c>
       <c r="H66" s="39">
-        <f>168*K66</f>
+        <f>12800*K66</f>
         <v/>
       </c>
       <c r="I66" s="39">
-        <f>285*K66</f>
+        <f>21600*K66</f>
         <v/>
       </c>
       <c r="J66" s="40" t="inlineStr">
@@ -4428,7 +4454,7 @@
     <row r="67">
       <c r="A67" s="41" t="inlineStr">
         <is>
-          <t>06.35</t>
+          <t>06.30</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -4438,7 +4464,7 @@
       </c>
       <c r="C67" s="42" t="inlineStr">
         <is>
-          <t>PVC pis su borusu Ø50</t>
+          <t>PPRC temiz su borusu Ø25 (ek parça ve montaj dahil)</t>
         </is>
       </c>
       <c r="D67" s="43" t="inlineStr">
@@ -4447,19 +4473,19 @@
         </is>
       </c>
       <c r="E67" s="44" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F67" s="29" t="n"/>
+        <v>6.9</v>
+      </c>
+      <c r="F67" s="30" t="n"/>
       <c r="G67" s="45">
         <f>E67*F67*K67</f>
         <v/>
       </c>
       <c r="H67" s="46">
-        <f>1849*K67</f>
+        <f>4278*K67</f>
         <v/>
       </c>
       <c r="I67" s="46">
-        <f>3182*K67</f>
+        <f>7245*K67</f>
         <v/>
       </c>
       <c r="J67" s="47" t="inlineStr">
@@ -4474,7 +4500,7 @@
     <row r="68">
       <c r="A68" s="34" t="inlineStr">
         <is>
-          <t>06.36</t>
+          <t>06.31</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4484,7 +4510,7 @@
       </c>
       <c r="C68" s="35" t="inlineStr">
         <is>
-          <t>Pis su havalandırma bacası Ø70 — çatı kotuna kadar</t>
+          <t>PPRC temiz su borusu Ø20 (ek parça ve montaj dahil)</t>
         </is>
       </c>
       <c r="D68" s="36" t="inlineStr">
@@ -4493,19 +4519,19 @@
         </is>
       </c>
       <c r="E68" s="37" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F68" s="29" t="n"/>
+        <v>3.1</v>
+      </c>
+      <c r="F68" s="30" t="n"/>
       <c r="G68" s="38">
         <f>E68*F68*K68</f>
         <v/>
       </c>
       <c r="H68" s="39">
-        <f>5890*K68</f>
+        <f>1612*K68</f>
         <v/>
       </c>
       <c r="I68" s="39">
-        <f>9975*K68</f>
+        <f>2728*K68</f>
         <v/>
       </c>
       <c r="J68" s="40" t="inlineStr">
@@ -4520,7 +4546,7 @@
     <row r="69">
       <c r="A69" s="41" t="inlineStr">
         <is>
-          <t>06.37</t>
+          <t>06.32</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -4530,28 +4556,28 @@
       </c>
       <c r="C69" s="42" t="inlineStr">
         <is>
-          <t>Paslanmaz sifonlu yer süzgeci 15×15</t>
+          <t>PPRC sıcak su hattı Ø20 + boru izolasyonu</t>
         </is>
       </c>
       <c r="D69" s="43" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E69" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="F69" s="29" t="n"/>
+        <v>4.2</v>
+      </c>
+      <c r="F69" s="30" t="n"/>
       <c r="G69" s="45">
         <f>E69*F69*K69</f>
         <v/>
       </c>
       <c r="H69" s="46">
-        <f>5800*K69</f>
+        <f>2856*K69</f>
         <v/>
       </c>
       <c r="I69" s="46">
-        <f>9600*K69</f>
+        <f>4830*K69</f>
         <v/>
       </c>
       <c r="J69" s="47" t="inlineStr">
@@ -4566,7 +4592,7 @@
     <row r="70">
       <c r="A70" s="34" t="inlineStr">
         <is>
-          <t>06.38</t>
+          <t>06.33</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4576,28 +4602,28 @@
       </c>
       <c r="C70" s="35" t="inlineStr">
         <is>
-          <t>Küresel vana Ø25 / Ø20 (kolon ve branşman kesme)</t>
+          <t>PVC pis su borusu Ø100 (%2 eğimli, askılı)</t>
         </is>
       </c>
       <c r="D70" s="36" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E70" s="37" t="n">
-        <v>8</v>
-      </c>
-      <c r="F70" s="29" t="n"/>
+        <v>7.4</v>
+      </c>
+      <c r="F70" s="30" t="n"/>
       <c r="G70" s="38">
         <f>E70*F70*K70</f>
         <v/>
       </c>
       <c r="H70" s="39">
-        <f>6240*K70</f>
+        <f>5772*K70</f>
         <v/>
       </c>
       <c r="I70" s="39">
-        <f>10400*K70</f>
+        <f>9620*K70</f>
         <v/>
       </c>
       <c r="J70" s="40" t="inlineStr">
@@ -4612,7 +4638,7 @@
     <row r="71">
       <c r="A71" s="41" t="inlineStr">
         <is>
-          <t>06.39</t>
+          <t>06.34</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -4622,28 +4648,28 @@
       </c>
       <c r="C71" s="42" t="inlineStr">
         <is>
-          <t>Sayaç sonrası ana kesme vanası + pislik tutucu filtre</t>
+          <t>PVC pis su borusu Ø70</t>
         </is>
       </c>
       <c r="D71" s="43" t="inlineStr">
         <is>
-          <t>takım</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E71" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" s="29" t="n"/>
+        <v>0.3</v>
+      </c>
+      <c r="F71" s="30" t="n"/>
       <c r="G71" s="45">
         <f>E71*F71*K71</f>
         <v/>
       </c>
       <c r="H71" s="46">
-        <f>6500*K71</f>
+        <f>168*K71</f>
         <v/>
       </c>
       <c r="I71" s="46">
-        <f>11000*K71</f>
+        <f>285*K71</f>
         <v/>
       </c>
       <c r="J71" s="47" t="inlineStr">
@@ -4658,7 +4684,7 @@
     <row r="72">
       <c r="A72" s="34" t="inlineStr">
         <is>
-          <t>06.40</t>
+          <t>06.35</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4668,28 +4694,28 @@
       </c>
       <c r="C72" s="35" t="inlineStr">
         <is>
-          <t>Elektrikli ani su ısıtıcı 6 kW (blok başına)</t>
+          <t>PVC pis su borusu Ø50</t>
         </is>
       </c>
       <c r="D72" s="36" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E72" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="F72" s="29" t="n"/>
+        <v>4.3</v>
+      </c>
+      <c r="F72" s="30" t="n"/>
       <c r="G72" s="38">
         <f>E72*F72*K72</f>
         <v/>
       </c>
       <c r="H72" s="39">
-        <f>19600*K72</f>
+        <f>1849*K72</f>
         <v/>
       </c>
       <c r="I72" s="39">
-        <f>34000*K72</f>
+        <f>3182*K72</f>
         <v/>
       </c>
       <c r="J72" s="40" t="inlineStr">
@@ -4704,7 +4730,7 @@
     <row r="73">
       <c r="A73" s="41" t="inlineStr">
         <is>
-          <t>06.41</t>
+          <t>06.36</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -4714,28 +4740,28 @@
       </c>
       <c r="C73" s="42" t="inlineStr">
         <is>
-          <t>Tesisat basınç testi, dezenfeksiyon ve teslim raporu</t>
+          <t>Pis su havalandırma bacası Ø70 — çatı kotuna kadar</t>
         </is>
       </c>
       <c r="D73" s="43" t="inlineStr">
         <is>
-          <t>götürü</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E73" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" s="29" t="n"/>
+        <v>9.5</v>
+      </c>
+      <c r="F73" s="30" t="n"/>
       <c r="G73" s="45">
         <f>E73*F73*K73</f>
         <v/>
       </c>
       <c r="H73" s="46">
-        <f>9500*K73</f>
+        <f>5890*K73</f>
         <v/>
       </c>
       <c r="I73" s="46">
-        <f>17000*K73</f>
+        <f>9975*K73</f>
         <v/>
       </c>
       <c r="J73" s="47" t="inlineStr">
@@ -4750,17 +4776,17 @@
     <row r="74">
       <c r="A74" s="34" t="inlineStr">
         <is>
-          <t>05.01</t>
+          <t>06.37</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>ELEKTRİK</t>
+          <t>MEKANİK</t>
         </is>
       </c>
       <c r="C74" s="35" t="inlineStr">
         <is>
-          <t>Ana dağıtım panosu — sıva üstü metal, 36 modül, montajlı</t>
+          <t>Paslanmaz sifonlu yer süzgeci 15×15</t>
         </is>
       </c>
       <c r="D74" s="36" t="inlineStr">
@@ -4769,19 +4795,19 @@
         </is>
       </c>
       <c r="E74" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" s="29" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="F74" s="30" t="n"/>
       <c r="G74" s="38">
         <f>E74*F74*K74</f>
         <v/>
       </c>
       <c r="H74" s="39">
-        <f>22000*K74</f>
+        <f>5800*K74</f>
         <v/>
       </c>
       <c r="I74" s="39">
-        <f>37000*K74</f>
+        <f>9600*K74</f>
         <v/>
       </c>
       <c r="J74" s="40" t="inlineStr">
@@ -4796,17 +4822,17 @@
     <row r="75">
       <c r="A75" s="41" t="inlineStr">
         <is>
-          <t>05.02</t>
+          <t>06.38</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>ELEKTRİK</t>
+          <t>MEKANİK</t>
         </is>
       </c>
       <c r="C75" s="42" t="inlineStr">
         <is>
-          <t>Ana kesici 3×40 A, C eğrisi</t>
+          <t>Küresel vana Ø25 / Ø20 (kolon ve branşman kesme)</t>
         </is>
       </c>
       <c r="D75" s="43" t="inlineStr">
@@ -4815,19 +4841,19 @@
         </is>
       </c>
       <c r="E75" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" s="29" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="F75" s="30" t="n"/>
       <c r="G75" s="45">
         <f>E75*F75*K75</f>
         <v/>
       </c>
       <c r="H75" s="46">
-        <f>3200*K75</f>
+        <f>6240*K75</f>
         <v/>
       </c>
       <c r="I75" s="46">
-        <f>5400*K75</f>
+        <f>10400*K75</f>
         <v/>
       </c>
       <c r="J75" s="47" t="inlineStr">
@@ -4842,38 +4868,38 @@
     <row r="76">
       <c r="A76" s="34" t="inlineStr">
         <is>
-          <t>05.03</t>
+          <t>06.39</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>ELEKTRİK</t>
+          <t>MEKANİK</t>
         </is>
       </c>
       <c r="C76" s="35" t="inlineStr">
         <is>
-          <t>Kaçak akım rölesi 4×40 A / 30 mA (genel + ıslak hacim ayrı)</t>
+          <t>Sayaç sonrası ana kesme vanası + pislik tutucu filtre</t>
         </is>
       </c>
       <c r="D76" s="36" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>takım</t>
         </is>
       </c>
       <c r="E76" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="F76" s="29" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F76" s="30" t="n"/>
       <c r="G76" s="38">
         <f>E76*F76*K76</f>
         <v/>
       </c>
       <c r="H76" s="39">
-        <f>8400*K76</f>
+        <f>6500*K76</f>
         <v/>
       </c>
       <c r="I76" s="39">
-        <f>14000*K76</f>
+        <f>11000*K76</f>
         <v/>
       </c>
       <c r="J76" s="40" t="inlineStr">
@@ -4888,17 +4914,17 @@
     <row r="77">
       <c r="A77" s="41" t="inlineStr">
         <is>
-          <t>05.04</t>
+          <t>06.40</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>ELEKTRİK</t>
+          <t>MEKANİK</t>
         </is>
       </c>
       <c r="C77" s="42" t="inlineStr">
         <is>
-          <t>Otomatik sigorta (1×6 / 1×10 / 1×16 / 1×32 A)</t>
+          <t>Elektrikli ani su ısıtıcı 6 kW (blok başına)</t>
         </is>
       </c>
       <c r="D77" s="43" t="inlineStr">
@@ -4907,19 +4933,19 @@
         </is>
       </c>
       <c r="E77" s="44" t="n">
-        <v>21</v>
-      </c>
-      <c r="F77" s="29" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F77" s="30" t="n"/>
       <c r="G77" s="45">
         <f>E77*F77*K77</f>
         <v/>
       </c>
       <c r="H77" s="46">
-        <f>13020*K77</f>
+        <f>19600*K77</f>
         <v/>
       </c>
       <c r="I77" s="46">
-        <f>22050*K77</f>
+        <f>34000*K77</f>
         <v/>
       </c>
       <c r="J77" s="47" t="inlineStr">
@@ -4934,38 +4960,38 @@
     <row r="78">
       <c r="A78" s="34" t="inlineStr">
         <is>
-          <t>05.05</t>
+          <t>06.41</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>ELEKTRİK</t>
+          <t>MEKANİK</t>
         </is>
       </c>
       <c r="C78" s="35" t="inlineStr">
         <is>
-          <t>Parafudr Tip 2 (aşırı gerilim koruma)</t>
+          <t>Tesisat basınç testi, dezenfeksiyon ve teslim raporu</t>
         </is>
       </c>
       <c r="D78" s="36" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>götürü</t>
         </is>
       </c>
       <c r="E78" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="F78" s="29" t="n"/>
+      <c r="F78" s="30" t="n"/>
       <c r="G78" s="38">
         <f>E78*F78*K78</f>
         <v/>
       </c>
       <c r="H78" s="39">
-        <f>6800*K78</f>
+        <f>9500*K78</f>
         <v/>
       </c>
       <c r="I78" s="39">
-        <f>11500*K78</f>
+        <f>17000*K78</f>
         <v/>
       </c>
       <c r="J78" s="40" t="inlineStr">
@@ -4980,7 +5006,7 @@
     <row r="79">
       <c r="A79" s="41" t="inlineStr">
         <is>
-          <t>05.06</t>
+          <t>05.01</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -4990,28 +5016,28 @@
       </c>
       <c r="C79" s="42" t="inlineStr">
         <is>
-          <t>NYY kolon hattı 5×10 mm² — sayaçtan panoya</t>
+          <t>Ana dağıtım panosu — sıva üstü metal, 36 modül, montajlı</t>
         </is>
       </c>
       <c r="D79" s="43" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E79" s="44" t="n">
-        <v>22</v>
-      </c>
-      <c r="F79" s="29" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F79" s="30" t="n"/>
       <c r="G79" s="45">
         <f>E79*F79*K79</f>
         <v/>
       </c>
       <c r="H79" s="46">
-        <f>17160*K79</f>
+        <f>22000*K79</f>
         <v/>
       </c>
       <c r="I79" s="46">
-        <f>28600*K79</f>
+        <f>37000*K79</f>
         <v/>
       </c>
       <c r="J79" s="47" t="inlineStr">
@@ -5026,7 +5052,7 @@
     <row r="80">
       <c r="A80" s="34" t="inlineStr">
         <is>
-          <t>05.07</t>
+          <t>05.02</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -5036,28 +5062,28 @@
       </c>
       <c r="C80" s="35" t="inlineStr">
         <is>
-          <t>Pano etiketleme, tek hat şeması çerçevesi ve fonksiyon testi</t>
+          <t>Ana kesici 3×40 A, C eğrisi</t>
         </is>
       </c>
       <c r="D80" s="36" t="inlineStr">
         <is>
-          <t>götürü</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E80" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="F80" s="29" t="n"/>
+      <c r="F80" s="30" t="n"/>
       <c r="G80" s="38">
         <f>E80*F80*K80</f>
         <v/>
       </c>
       <c r="H80" s="39">
-        <f>6500*K80</f>
+        <f>3200*K80</f>
         <v/>
       </c>
       <c r="I80" s="39">
-        <f>11000*K80</f>
+        <f>5400*K80</f>
         <v/>
       </c>
       <c r="J80" s="40" t="inlineStr">
@@ -5072,7 +5098,7 @@
     <row r="81">
       <c r="A81" s="41" t="inlineStr">
         <is>
-          <t>05.10</t>
+          <t>05.03</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -5082,7 +5108,7 @@
       </c>
       <c r="C81" s="42" t="inlineStr">
         <is>
-          <t>Lineer LED armatür 40 W / 4400 lm, 1.200 mm (montaj dahil)</t>
+          <t>Kaçak akım rölesi 4×40 A / 30 mA (genel + ıslak hacim ayrı)</t>
         </is>
       </c>
       <c r="D81" s="43" t="inlineStr">
@@ -5091,19 +5117,19 @@
         </is>
       </c>
       <c r="E81" s="44" t="n">
-        <v>15</v>
-      </c>
-      <c r="F81" s="29" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F81" s="30" t="n"/>
       <c r="G81" s="45">
         <f>E81*F81*K81</f>
         <v/>
       </c>
       <c r="H81" s="46">
-        <f>21000*K81</f>
+        <f>8400*K81</f>
         <v/>
       </c>
       <c r="I81" s="46">
-        <f>39000*K81</f>
+        <f>14000*K81</f>
         <v/>
       </c>
       <c r="J81" s="47" t="inlineStr">
@@ -5118,7 +5144,7 @@
     <row r="82">
       <c r="A82" s="34" t="inlineStr">
         <is>
-          <t>05.11</t>
+          <t>05.04</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5128,7 +5154,7 @@
       </c>
       <c r="C82" s="35" t="inlineStr">
         <is>
-          <t>IP44 downlight 18 W / 1800 lm — ıslak hacim ve soyunma</t>
+          <t>Otomatik sigorta (1×6 / 1×10 / 1×16 / 1×32 A)</t>
         </is>
       </c>
       <c r="D82" s="36" t="inlineStr">
@@ -5137,19 +5163,19 @@
         </is>
       </c>
       <c r="E82" s="37" t="n">
-        <v>6</v>
-      </c>
-      <c r="F82" s="29" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="F82" s="30" t="n"/>
       <c r="G82" s="38">
         <f>E82*F82*K82</f>
         <v/>
       </c>
       <c r="H82" s="39">
-        <f>5100*K82</f>
+        <f>13020*K82</f>
         <v/>
       </c>
       <c r="I82" s="39">
-        <f>9300*K82</f>
+        <f>22050*K82</f>
         <v/>
       </c>
       <c r="J82" s="40" t="inlineStr">
@@ -5164,7 +5190,7 @@
     <row r="83">
       <c r="A83" s="41" t="inlineStr">
         <is>
-          <t>05.12</t>
+          <t>05.05</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
@@ -5174,7 +5200,7 @@
       </c>
       <c r="C83" s="42" t="inlineStr">
         <is>
-          <t>Acil aydınlatma armatürü — 3 saat bataryalı</t>
+          <t>Parafudr Tip 2 (aşırı gerilim koruma)</t>
         </is>
       </c>
       <c r="D83" s="43" t="inlineStr">
@@ -5183,19 +5209,19 @@
         </is>
       </c>
       <c r="E83" s="44" t="n">
-        <v>5</v>
-      </c>
-      <c r="F83" s="29" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F83" s="30" t="n"/>
       <c r="G83" s="45">
         <f>E83*F83*K83</f>
         <v/>
       </c>
       <c r="H83" s="46">
-        <f>6250*K83</f>
+        <f>6800*K83</f>
         <v/>
       </c>
       <c r="I83" s="46">
-        <f>11000*K83</f>
+        <f>11500*K83</f>
         <v/>
       </c>
       <c r="J83" s="47" t="inlineStr">
@@ -5210,7 +5236,7 @@
     <row r="84">
       <c r="A84" s="34" t="inlineStr">
         <is>
-          <t>05.13</t>
+          <t>05.06</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5220,28 +5246,28 @@
       </c>
       <c r="C84" s="35" t="inlineStr">
         <is>
-          <t>Acil çıkış yönlendirme armatürü</t>
+          <t>NYY kolon hattı 5×10 mm² — sayaçtan panoya</t>
         </is>
       </c>
       <c r="D84" s="36" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E84" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="F84" s="29" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="F84" s="30" t="n"/>
       <c r="G84" s="38">
         <f>E84*F84*K84</f>
         <v/>
       </c>
       <c r="H84" s="39">
-        <f>3450*K84</f>
+        <f>17160*K84</f>
         <v/>
       </c>
       <c r="I84" s="39">
-        <f>5850*K84</f>
+        <f>28600*K84</f>
         <v/>
       </c>
       <c r="J84" s="40" t="inlineStr">
@@ -5256,7 +5282,7 @@
     <row r="85">
       <c r="A85" s="41" t="inlineStr">
         <is>
-          <t>05.14</t>
+          <t>05.07</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
@@ -5266,28 +5292,28 @@
       </c>
       <c r="C85" s="42" t="inlineStr">
         <is>
-          <t>Aydınlatma linyesi NHXMH 3×1,5 mm² — spiral boru ve işçilik dâhil</t>
+          <t>Pano etiketleme, tek hat şeması çerçevesi ve fonksiyon testi</t>
         </is>
       </c>
       <c r="D85" s="43" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>götürü</t>
         </is>
       </c>
       <c r="E85" s="44" t="n">
-        <v>172</v>
-      </c>
-      <c r="F85" s="29" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F85" s="30" t="n"/>
       <c r="G85" s="45">
         <f>E85*F85*K85</f>
         <v/>
       </c>
       <c r="H85" s="46">
-        <f>18920*K85</f>
+        <f>6500*K85</f>
         <v/>
       </c>
       <c r="I85" s="46">
-        <f>31820*K85</f>
+        <f>11000*K85</f>
         <v/>
       </c>
       <c r="J85" s="47" t="inlineStr">
@@ -5302,7 +5328,7 @@
     <row r="86">
       <c r="A86" s="34" t="inlineStr">
         <is>
-          <t>05.15</t>
+          <t>05.10</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5312,7 +5338,7 @@
       </c>
       <c r="C86" s="35" t="inlineStr">
         <is>
-          <t>Anahtar / komütatör / vaviyen — sıva altı</t>
+          <t>Lineer LED armatür 40 W / 4400 lm, 1.200 mm (montaj dahil)</t>
         </is>
       </c>
       <c r="D86" s="36" t="inlineStr">
@@ -5321,19 +5347,19 @@
         </is>
       </c>
       <c r="E86" s="37" t="n">
-        <v>7</v>
-      </c>
-      <c r="F86" s="29" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="F86" s="30" t="n"/>
       <c r="G86" s="38">
         <f>E86*F86*K86</f>
         <v/>
       </c>
       <c r="H86" s="39">
-        <f>3360*K86</f>
+        <f>21000*K86</f>
         <v/>
       </c>
       <c r="I86" s="39">
-        <f>5740*K86</f>
+        <f>39000*K86</f>
         <v/>
       </c>
       <c r="J86" s="40" t="inlineStr">
@@ -5348,7 +5374,7 @@
     <row r="87">
       <c r="A87" s="41" t="inlineStr">
         <is>
-          <t>05.16</t>
+          <t>05.11</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
@@ -5358,7 +5384,7 @@
       </c>
       <c r="C87" s="42" t="inlineStr">
         <is>
-          <t>Hareket sensörü — ıslak hacim ve geçiş</t>
+          <t>IP44 downlight 18 W / 1800 lm — ıslak hacim ve soyunma</t>
         </is>
       </c>
       <c r="D87" s="43" t="inlineStr">
@@ -5367,19 +5393,19 @@
         </is>
       </c>
       <c r="E87" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="F87" s="29" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="F87" s="30" t="n"/>
       <c r="G87" s="45">
         <f>E87*F87*K87</f>
         <v/>
       </c>
       <c r="H87" s="46">
-        <f>4350*K87</f>
+        <f>5100*K87</f>
         <v/>
       </c>
       <c r="I87" s="46">
-        <f>7200*K87</f>
+        <f>9300*K87</f>
         <v/>
       </c>
       <c r="J87" s="47" t="inlineStr">
@@ -5394,7 +5420,7 @@
     <row r="88">
       <c r="A88" s="34" t="inlineStr">
         <is>
-          <t>05.20</t>
+          <t>05.12</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5404,7 +5430,7 @@
       </c>
       <c r="C88" s="35" t="inlineStr">
         <is>
-          <t>İkili topraklı priz — sıva altı, komple</t>
+          <t>Acil aydınlatma armatürü — 3 saat bataryalı</t>
         </is>
       </c>
       <c r="D88" s="36" t="inlineStr">
@@ -5413,19 +5439,19 @@
         </is>
       </c>
       <c r="E88" s="37" t="n">
-        <v>20</v>
-      </c>
-      <c r="F88" s="29" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="F88" s="30" t="n"/>
       <c r="G88" s="38">
         <f>E88*F88*K88</f>
         <v/>
       </c>
       <c r="H88" s="39">
-        <f>12400*K88</f>
+        <f>6250*K88</f>
         <v/>
       </c>
       <c r="I88" s="39">
-        <f>21000*K88</f>
+        <f>11000*K88</f>
         <v/>
       </c>
       <c r="J88" s="40" t="inlineStr">
@@ -5440,7 +5466,7 @@
     <row r="89">
       <c r="A89" s="41" t="inlineStr">
         <is>
-          <t>05.21</t>
+          <t>05.13</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
@@ -5450,7 +5476,7 @@
       </c>
       <c r="C89" s="42" t="inlineStr">
         <is>
-          <t>IP44 priz — ıslak hacim</t>
+          <t>Acil çıkış yönlendirme armatürü</t>
         </is>
       </c>
       <c r="D89" s="43" t="inlineStr">
@@ -5459,19 +5485,19 @@
         </is>
       </c>
       <c r="E89" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="F89" s="29" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="F89" s="30" t="n"/>
       <c r="G89" s="45">
         <f>E89*F89*K89</f>
         <v/>
       </c>
       <c r="H89" s="46">
-        <f>1900*K89</f>
+        <f>3450*K89</f>
         <v/>
       </c>
       <c r="I89" s="46">
-        <f>3200*K89</f>
+        <f>5850*K89</f>
         <v/>
       </c>
       <c r="J89" s="47" t="inlineStr">
@@ -5486,7 +5512,7 @@
     <row r="90">
       <c r="A90" s="34" t="inlineStr">
         <is>
-          <t>05.22</t>
+          <t>05.14</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5496,7 +5522,7 @@
       </c>
       <c r="C90" s="35" t="inlineStr">
         <is>
-          <t>Priz linyesi NHXMH 3×2,5 mm² — spiral boru ve işçilik dâhil</t>
+          <t>Aydınlatma linyesi NHXMH 3×1,5 mm² — spiral boru ve işçilik dâhil</t>
         </is>
       </c>
       <c r="D90" s="36" t="inlineStr">
@@ -5505,19 +5531,19 @@
         </is>
       </c>
       <c r="E90" s="37" t="n">
-        <v>193</v>
-      </c>
-      <c r="F90" s="29" t="n"/>
+        <v>172</v>
+      </c>
+      <c r="F90" s="30" t="n"/>
       <c r="G90" s="38">
         <f>E90*F90*K90</f>
         <v/>
       </c>
       <c r="H90" s="39">
-        <f>27020*K90</f>
+        <f>18920*K90</f>
         <v/>
       </c>
       <c r="I90" s="39">
-        <f>44390*K90</f>
+        <f>31820*K90</f>
         <v/>
       </c>
       <c r="J90" s="40" t="inlineStr">
@@ -5532,7 +5558,7 @@
     <row r="91">
       <c r="A91" s="41" t="inlineStr">
         <is>
-          <t>05.23</t>
+          <t>05.15</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -5542,7 +5568,7 @@
       </c>
       <c r="C91" s="42" t="inlineStr">
         <is>
-          <t>Klima besleme hattı 3×2,5 mm² + hat sonu kesici</t>
+          <t>Anahtar / komütatör / vaviyen — sıva altı</t>
         </is>
       </c>
       <c r="D91" s="43" t="inlineStr">
@@ -5551,19 +5577,19 @@
         </is>
       </c>
       <c r="E91" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="F91" s="29" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="F91" s="30" t="n"/>
       <c r="G91" s="45">
         <f>E91*F91*K91</f>
         <v/>
       </c>
       <c r="H91" s="46">
-        <f>13600*K91</f>
+        <f>3360*K91</f>
         <v/>
       </c>
       <c r="I91" s="46">
-        <f>22800*K91</f>
+        <f>5740*K91</f>
         <v/>
       </c>
       <c r="J91" s="47" t="inlineStr">
@@ -5578,7 +5604,7 @@
     <row r="92">
       <c r="A92" s="34" t="inlineStr">
         <is>
-          <t>05.24</t>
+          <t>05.16</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -5588,7 +5614,7 @@
       </c>
       <c r="C92" s="35" t="inlineStr">
         <is>
-          <t>Su ısıtıcı besleme hattı 3×6 mm² + 32 A kesici + 30 mA kaçak akım</t>
+          <t>Hareket sensörü — ıslak hacim ve geçiş</t>
         </is>
       </c>
       <c r="D92" s="36" t="inlineStr">
@@ -5597,19 +5623,19 @@
         </is>
       </c>
       <c r="E92" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="F92" s="29" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="F92" s="30" t="n"/>
       <c r="G92" s="38">
         <f>E92*F92*K92</f>
         <v/>
       </c>
       <c r="H92" s="39">
-        <f>12800*K92</f>
+        <f>4350*K92</f>
         <v/>
       </c>
       <c r="I92" s="39">
-        <f>21600*K92</f>
+        <f>7200*K92</f>
         <v/>
       </c>
       <c r="J92" s="40" t="inlineStr">
@@ -5624,7 +5650,7 @@
     <row r="93">
       <c r="A93" s="41" t="inlineStr">
         <is>
-          <t>05.25</t>
+          <t>05.20</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -5634,7 +5660,7 @@
       </c>
       <c r="C93" s="42" t="inlineStr">
         <is>
-          <t>Havalandırma fanı besleme ve hız kontrol hattı</t>
+          <t>İkili topraklı priz — sıva altı, komple</t>
         </is>
       </c>
       <c r="D93" s="43" t="inlineStr">
@@ -5643,19 +5669,19 @@
         </is>
       </c>
       <c r="E93" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="F93" s="29" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="F93" s="30" t="n"/>
       <c r="G93" s="45">
         <f>E93*F93*K93</f>
         <v/>
       </c>
       <c r="H93" s="46">
-        <f>7200*K93</f>
+        <f>12400*K93</f>
         <v/>
       </c>
       <c r="I93" s="46">
-        <f>12000*K93</f>
+        <f>21000*K93</f>
         <v/>
       </c>
       <c r="J93" s="47" t="inlineStr">
@@ -5670,7 +5696,7 @@
     <row r="94">
       <c r="A94" s="34" t="inlineStr">
         <is>
-          <t>05.26</t>
+          <t>05.21</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -5680,7 +5706,7 @@
       </c>
       <c r="C94" s="35" t="inlineStr">
         <is>
-          <t>Banko kuvvet + veri kutusu (gömme)</t>
+          <t>IP44 priz — ıslak hacim</t>
         </is>
       </c>
       <c r="D94" s="36" t="inlineStr">
@@ -5689,19 +5715,19 @@
         </is>
       </c>
       <c r="E94" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F94" s="29" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F94" s="30" t="n"/>
       <c r="G94" s="38">
         <f>E94*F94*K94</f>
         <v/>
       </c>
       <c r="H94" s="39">
-        <f>7500*K94</f>
+        <f>1900*K94</f>
         <v/>
       </c>
       <c r="I94" s="39">
-        <f>12500*K94</f>
+        <f>3200*K94</f>
         <v/>
       </c>
       <c r="J94" s="40" t="inlineStr">
@@ -5716,7 +5742,7 @@
     <row r="95">
       <c r="A95" s="41" t="inlineStr">
         <is>
-          <t>05.30</t>
+          <t>05.22</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
@@ -5726,28 +5752,28 @@
       </c>
       <c r="C95" s="42" t="inlineStr">
         <is>
-          <t>Cat6 veri prizi + kablolama</t>
+          <t>Priz linyesi NHXMH 3×2,5 mm² — spiral boru ve işçilik dâhil</t>
         </is>
       </c>
       <c r="D95" s="43" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E95" s="44" t="n">
-        <v>6</v>
-      </c>
-      <c r="F95" s="29" t="n"/>
+        <v>193</v>
+      </c>
+      <c r="F95" s="30" t="n"/>
       <c r="G95" s="45">
         <f>E95*F95*K95</f>
         <v/>
       </c>
       <c r="H95" s="46">
-        <f>8700*K95</f>
+        <f>27020*K95</f>
         <v/>
       </c>
       <c r="I95" s="46">
-        <f>14700*K95</f>
+        <f>44390*K95</f>
         <v/>
       </c>
       <c r="J95" s="47" t="inlineStr">
@@ -5762,7 +5788,7 @@
     <row r="96">
       <c r="A96" s="34" t="inlineStr">
         <is>
-          <t>05.31</t>
+          <t>05.23</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5772,7 +5798,7 @@
       </c>
       <c r="C96" s="35" t="inlineStr">
         <is>
-          <t>Kablosuz erişim noktası (AP) + PoE besleme</t>
+          <t>Klima besleme hattı 3×2,5 mm² + hat sonu kesici</t>
         </is>
       </c>
       <c r="D96" s="36" t="inlineStr">
@@ -5781,9 +5807,9 @@
         </is>
       </c>
       <c r="E96" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="F96" s="29" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="F96" s="30" t="n"/>
       <c r="G96" s="38">
         <f>E96*F96*K96</f>
         <v/>
@@ -5793,7 +5819,7 @@
         <v/>
       </c>
       <c r="I96" s="39">
-        <f>23000*K96</f>
+        <f>22800*K96</f>
         <v/>
       </c>
       <c r="J96" s="40" t="inlineStr">
@@ -5808,7 +5834,7 @@
     <row r="97">
       <c r="A97" s="41" t="inlineStr">
         <is>
-          <t>05.32</t>
+          <t>05.24</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
@@ -5818,7 +5844,7 @@
       </c>
       <c r="C97" s="42" t="inlineStr">
         <is>
-          <t>IP güvenlik kamerası — iç mekân (soyunma ve WC HARİÇ)</t>
+          <t>Su ısıtıcı besleme hattı 3×6 mm² + 32 A kesici + 30 mA kaçak akım</t>
         </is>
       </c>
       <c r="D97" s="43" t="inlineStr">
@@ -5827,19 +5853,19 @@
         </is>
       </c>
       <c r="E97" s="44" t="n">
-        <v>5</v>
-      </c>
-      <c r="F97" s="29" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F97" s="30" t="n"/>
       <c r="G97" s="45">
         <f>E97*F97*K97</f>
         <v/>
       </c>
       <c r="H97" s="46">
-        <f>27000*K97</f>
+        <f>12800*K97</f>
         <v/>
       </c>
       <c r="I97" s="46">
-        <f>45000*K97</f>
+        <f>21600*K97</f>
         <v/>
       </c>
       <c r="J97" s="47" t="inlineStr">
@@ -5854,7 +5880,7 @@
     <row r="98">
       <c r="A98" s="34" t="inlineStr">
         <is>
-          <t>05.33</t>
+          <t>05.25</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5864,28 +5890,28 @@
       </c>
       <c r="C98" s="35" t="inlineStr">
         <is>
-          <t>NVR + 4 TB disk + 9U rack kabinet</t>
+          <t>Havalandırma fanı besleme ve hız kontrol hattı</t>
         </is>
       </c>
       <c r="D98" s="36" t="inlineStr">
         <is>
-          <t>takım</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E98" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F98" s="29" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="F98" s="30" t="n"/>
       <c r="G98" s="38">
         <f>E98*F98*K98</f>
         <v/>
       </c>
       <c r="H98" s="39">
-        <f>24000*K98</f>
+        <f>7200*K98</f>
         <v/>
       </c>
       <c r="I98" s="39">
-        <f>40000*K98</f>
+        <f>12000*K98</f>
         <v/>
       </c>
       <c r="J98" s="40" t="inlineStr">
@@ -5900,7 +5926,7 @@
     <row r="99">
       <c r="A99" s="41" t="inlineStr">
         <is>
-          <t>05.34</t>
+          <t>05.26</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
@@ -5910,7 +5936,7 @@
       </c>
       <c r="C99" s="42" t="inlineStr">
         <is>
-          <t>Tavan hoparlörü 6 W / 100 V hat</t>
+          <t>Banko kuvvet + veri kutusu (gömme)</t>
         </is>
       </c>
       <c r="D99" s="43" t="inlineStr">
@@ -5919,19 +5945,19 @@
         </is>
       </c>
       <c r="E99" s="44" t="n">
-        <v>6</v>
-      </c>
-      <c r="F99" s="29" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F99" s="30" t="n"/>
       <c r="G99" s="45">
         <f>E99*F99*K99</f>
         <v/>
       </c>
       <c r="H99" s="46">
-        <f>9900*K99</f>
+        <f>7500*K99</f>
         <v/>
       </c>
       <c r="I99" s="46">
-        <f>16800*K99</f>
+        <f>12500*K99</f>
         <v/>
       </c>
       <c r="J99" s="47" t="inlineStr">
@@ -5946,7 +5972,7 @@
     <row r="100">
       <c r="A100" s="34" t="inlineStr">
         <is>
-          <t>05.35</t>
+          <t>05.30</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5956,28 +5982,28 @@
       </c>
       <c r="C100" s="35" t="inlineStr">
         <is>
-          <t>Anfi / ses matrisi 120 W + kaynak</t>
+          <t>Cat6 veri prizi + kablolama</t>
         </is>
       </c>
       <c r="D100" s="36" t="inlineStr">
         <is>
-          <t>takım</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E100" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F100" s="29" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="F100" s="30" t="n"/>
       <c r="G100" s="38">
         <f>E100*F100*K100</f>
         <v/>
       </c>
       <c r="H100" s="39">
-        <f>14000*K100</f>
+        <f>8700*K100</f>
         <v/>
       </c>
       <c r="I100" s="39">
-        <f>24000*K100</f>
+        <f>14700*K100</f>
         <v/>
       </c>
       <c r="J100" s="40" t="inlineStr">
@@ -5992,7 +6018,7 @@
     <row r="101">
       <c r="A101" s="41" t="inlineStr">
         <is>
-          <t>05.36</t>
+          <t>05.31</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
@@ -6002,28 +6028,28 @@
       </c>
       <c r="C101" s="42" t="inlineStr">
         <is>
-          <t>Geçiş kontrol — kapı okuyucu + elektrikli kilit + buton</t>
+          <t>Kablosuz erişim noktası (AP) + PoE besleme</t>
         </is>
       </c>
       <c r="D101" s="43" t="inlineStr">
         <is>
-          <t>takım</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E101" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F101" s="29" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F101" s="30" t="n"/>
       <c r="G101" s="45">
         <f>E101*F101*K101</f>
         <v/>
       </c>
       <c r="H101" s="46">
-        <f>16500*K101</f>
+        <f>13600*K101</f>
         <v/>
       </c>
       <c r="I101" s="46">
-        <f>28000*K101</f>
+        <f>23000*K101</f>
         <v/>
       </c>
       <c r="J101" s="47" t="inlineStr">
@@ -6038,7 +6064,7 @@
     <row r="102">
       <c r="A102" s="34" t="inlineStr">
         <is>
-          <t>05.37</t>
+          <t>05.32</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -6048,7 +6074,7 @@
       </c>
       <c r="C102" s="35" t="inlineStr">
         <is>
-          <t>Yangın algılama paneli — 2 zon, aküleriyle</t>
+          <t>IP güvenlik kamerası — iç mekân (soyunma ve WC HARİÇ)</t>
         </is>
       </c>
       <c r="D102" s="36" t="inlineStr">
@@ -6057,19 +6083,19 @@
         </is>
       </c>
       <c r="E102" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F102" s="29" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="F102" s="30" t="n"/>
       <c r="G102" s="38">
         <f>E102*F102*K102</f>
         <v/>
       </c>
       <c r="H102" s="39">
-        <f>14500*K102</f>
+        <f>27000*K102</f>
         <v/>
       </c>
       <c r="I102" s="39">
-        <f>24500*K102</f>
+        <f>45000*K102</f>
         <v/>
       </c>
       <c r="J102" s="40" t="inlineStr">
@@ -6084,7 +6110,7 @@
     <row r="103">
       <c r="A103" s="41" t="inlineStr">
         <is>
-          <t>05.38</t>
+          <t>05.33</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
@@ -6094,28 +6120,28 @@
       </c>
       <c r="C103" s="42" t="inlineStr">
         <is>
-          <t>Optik duman dedektörü</t>
+          <t>NVR + 4 TB disk + 9U rack kabinet</t>
         </is>
       </c>
       <c r="D103" s="43" t="inlineStr">
         <is>
-          <t>adet</t>
+          <t>takım</t>
         </is>
       </c>
       <c r="E103" s="44" t="n">
-        <v>6</v>
-      </c>
-      <c r="F103" s="29" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F103" s="30" t="n"/>
       <c r="G103" s="45">
         <f>E103*F103*K103</f>
         <v/>
       </c>
       <c r="H103" s="46">
-        <f>7500*K103</f>
+        <f>24000*K103</f>
         <v/>
       </c>
       <c r="I103" s="46">
-        <f>12600*K103</f>
+        <f>40000*K103</f>
         <v/>
       </c>
       <c r="J103" s="47" t="inlineStr">
@@ -6130,7 +6156,7 @@
     <row r="104">
       <c r="A104" s="34" t="inlineStr">
         <is>
-          <t>05.39</t>
+          <t>05.34</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -6140,7 +6166,7 @@
       </c>
       <c r="C104" s="35" t="inlineStr">
         <is>
-          <t>Yangın ihbar butonu / siren + flaşör</t>
+          <t>Tavan hoparlörü 6 W / 100 V hat</t>
         </is>
       </c>
       <c r="D104" s="36" t="inlineStr">
@@ -6149,19 +6175,19 @@
         </is>
       </c>
       <c r="E104" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="F104" s="29" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="F104" s="30" t="n"/>
       <c r="G104" s="38">
         <f>E104*F104*K104</f>
         <v/>
       </c>
       <c r="H104" s="39">
-        <f>5550*K104</f>
+        <f>9900*K104</f>
         <v/>
       </c>
       <c r="I104" s="39">
-        <f>9300*K104</f>
+        <f>16800*K104</f>
         <v/>
       </c>
       <c r="J104" s="40" t="inlineStr">
@@ -6176,7 +6202,7 @@
     <row r="105">
       <c r="A105" s="41" t="inlineStr">
         <is>
-          <t>05.40</t>
+          <t>05.35</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
@@ -6186,28 +6212,28 @@
       </c>
       <c r="C105" s="42" t="inlineStr">
         <is>
-          <t>Zayıf akım kablolaması (Cat6, koaksiyel, ses, algılama)</t>
+          <t>Anfi / ses matrisi 120 W + kaynak</t>
         </is>
       </c>
       <c r="D105" s="43" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>takım</t>
         </is>
       </c>
       <c r="E105" s="44" t="n">
-        <v>210</v>
-      </c>
-      <c r="F105" s="29" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F105" s="30" t="n"/>
       <c r="G105" s="45">
         <f>E105*F105*K105</f>
         <v/>
       </c>
       <c r="H105" s="46">
-        <f>12600*K105</f>
+        <f>14000*K105</f>
         <v/>
       </c>
       <c r="I105" s="46">
-        <f>22050*K105</f>
+        <f>24000*K105</f>
         <v/>
       </c>
       <c r="J105" s="47" t="inlineStr">
@@ -6222,7 +6248,7 @@
     <row r="106">
       <c r="A106" s="34" t="inlineStr">
         <is>
-          <t>05.45</t>
+          <t>05.36</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -6232,7 +6258,7 @@
       </c>
       <c r="C106" s="35" t="inlineStr">
         <is>
-          <t>Topraklama çubuğu, bağlantı ve ölçüm kutusu</t>
+          <t>Geçiş kontrol — kapı okuyucu + elektrikli kilit + buton</t>
         </is>
       </c>
       <c r="D106" s="36" t="inlineStr">
@@ -6243,17 +6269,17 @@
       <c r="E106" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="F106" s="29" t="n"/>
+      <c r="F106" s="30" t="n"/>
       <c r="G106" s="38">
         <f>E106*F106*K106</f>
         <v/>
       </c>
       <c r="H106" s="39">
-        <f>8500*K106</f>
+        <f>16500*K106</f>
         <v/>
       </c>
       <c r="I106" s="39">
-        <f>14500*K106</f>
+        <f>28000*K106</f>
         <v/>
       </c>
       <c r="J106" s="40" t="inlineStr">
@@ -6268,7 +6294,7 @@
     <row r="107">
       <c r="A107" s="41" t="inlineStr">
         <is>
-          <t>05.46</t>
+          <t>05.37</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
@@ -6278,28 +6304,28 @@
       </c>
       <c r="C107" s="42" t="inlineStr">
         <is>
-          <t>Ana potansiyel dengeleme barası ve iletkenleri</t>
+          <t>Yangın algılama paneli — 2 zon, aküleriyle</t>
         </is>
       </c>
       <c r="D107" s="43" t="inlineStr">
         <is>
-          <t>takım</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E107" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F107" s="29" t="n"/>
+      <c r="F107" s="30" t="n"/>
       <c r="G107" s="45">
         <f>E107*F107*K107</f>
         <v/>
       </c>
       <c r="H107" s="46">
-        <f>5200*K107</f>
+        <f>14500*K107</f>
         <v/>
       </c>
       <c r="I107" s="46">
-        <f>8800*K107</f>
+        <f>24500*K107</f>
         <v/>
       </c>
       <c r="J107" s="47" t="inlineStr">
@@ -6314,7 +6340,7 @@
     <row r="108">
       <c r="A108" s="34" t="inlineStr">
         <is>
-          <t>05.47</t>
+          <t>05.38</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -6324,28 +6350,28 @@
       </c>
       <c r="C108" s="35" t="inlineStr">
         <is>
-          <t>Islak hacim ek potansiyel dengeleme</t>
+          <t>Optik duman dedektörü</t>
         </is>
       </c>
       <c r="D108" s="36" t="inlineStr">
         <is>
-          <t>takım</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E108" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="F108" s="29" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="F108" s="30" t="n"/>
       <c r="G108" s="38">
         <f>E108*F108*K108</f>
         <v/>
       </c>
       <c r="H108" s="39">
-        <f>5600*K108</f>
+        <f>7500*K108</f>
         <v/>
       </c>
       <c r="I108" s="39">
-        <f>9400*K108</f>
+        <f>12600*K108</f>
         <v/>
       </c>
       <c r="J108" s="40" t="inlineStr">
@@ -6360,7 +6386,7 @@
     <row r="109">
       <c r="A109" s="41" t="inlineStr">
         <is>
-          <t>05.48</t>
+          <t>05.39</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
@@ -6370,28 +6396,28 @@
       </c>
       <c r="C109" s="42" t="inlineStr">
         <is>
-          <t>Topraklama direnci ölçümü, izolasyon testi ve rapor</t>
+          <t>Yangın ihbar butonu / siren + flaşör</t>
         </is>
       </c>
       <c r="D109" s="43" t="inlineStr">
         <is>
-          <t>götürü</t>
+          <t>adet</t>
         </is>
       </c>
       <c r="E109" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F109" s="29" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="F109" s="30" t="n"/>
       <c r="G109" s="45">
         <f>E109*F109*K109</f>
         <v/>
       </c>
       <c r="H109" s="46">
-        <f>7500*K109</f>
+        <f>5550*K109</f>
         <v/>
       </c>
       <c r="I109" s="46">
-        <f>13000*K109</f>
+        <f>9300*K109</f>
         <v/>
       </c>
       <c r="J109" s="47" t="inlineStr">
@@ -6403,34 +6429,264 @@
         <v>1</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="34" t="inlineStr">
+        <is>
+          <t>05.40</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C110" s="35" t="inlineStr">
+        <is>
+          <t>Zayıf akım kablolaması (Cat6, koaksiyel, ses, algılama)</t>
+        </is>
+      </c>
+      <c r="D110" s="36" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E110" s="37" t="n">
+        <v>210</v>
+      </c>
+      <c r="F110" s="30" t="n"/>
+      <c r="G110" s="38">
+        <f>E110*F110*K110</f>
+        <v/>
+      </c>
+      <c r="H110" s="39">
+        <f>12600*K110</f>
+        <v/>
+      </c>
+      <c r="I110" s="39">
+        <f>22050*K110</f>
+        <v/>
+      </c>
+      <c r="J110" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K110" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="111">
-      <c r="A111" s="56" t="n"/>
-      <c r="B111" s="56" t="n"/>
-      <c r="C111" s="57" t="inlineStr">
+      <c r="A111" s="41" t="inlineStr">
+        <is>
+          <t>05.45</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C111" s="42" t="inlineStr">
+        <is>
+          <t>Topraklama çubuğu, bağlantı ve ölçüm kutusu</t>
+        </is>
+      </c>
+      <c r="D111" s="43" t="inlineStr">
+        <is>
+          <t>takım</t>
+        </is>
+      </c>
+      <c r="E111" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="30" t="n"/>
+      <c r="G111" s="45">
+        <f>E111*F111*K111</f>
+        <v/>
+      </c>
+      <c r="H111" s="46">
+        <f>8500*K111</f>
+        <v/>
+      </c>
+      <c r="I111" s="46">
+        <f>14500*K111</f>
+        <v/>
+      </c>
+      <c r="J111" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K111" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="34" t="inlineStr">
+        <is>
+          <t>05.46</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C112" s="35" t="inlineStr">
+        <is>
+          <t>Ana potansiyel dengeleme barası ve iletkenleri</t>
+        </is>
+      </c>
+      <c r="D112" s="36" t="inlineStr">
+        <is>
+          <t>takım</t>
+        </is>
+      </c>
+      <c r="E112" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="30" t="n"/>
+      <c r="G112" s="38">
+        <f>E112*F112*K112</f>
+        <v/>
+      </c>
+      <c r="H112" s="39">
+        <f>5200*K112</f>
+        <v/>
+      </c>
+      <c r="I112" s="39">
+        <f>8800*K112</f>
+        <v/>
+      </c>
+      <c r="J112" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K112" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="41" t="inlineStr">
+        <is>
+          <t>05.47</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C113" s="42" t="inlineStr">
+        <is>
+          <t>Islak hacim ek potansiyel dengeleme</t>
+        </is>
+      </c>
+      <c r="D113" s="43" t="inlineStr">
+        <is>
+          <t>takım</t>
+        </is>
+      </c>
+      <c r="E113" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F113" s="30" t="n"/>
+      <c r="G113" s="45">
+        <f>E113*F113*K113</f>
+        <v/>
+      </c>
+      <c r="H113" s="46">
+        <f>5600*K113</f>
+        <v/>
+      </c>
+      <c r="I113" s="46">
+        <f>9400*K113</f>
+        <v/>
+      </c>
+      <c r="J113" s="47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K113" s="47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="34" t="inlineStr">
+        <is>
+          <t>05.48</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>ELEKTRİK</t>
+        </is>
+      </c>
+      <c r="C114" s="35" t="inlineStr">
+        <is>
+          <t>Topraklama direnci ölçümü, izolasyon testi ve rapor</t>
+        </is>
+      </c>
+      <c r="D114" s="36" t="inlineStr">
+        <is>
+          <t>götürü</t>
+        </is>
+      </c>
+      <c r="E114" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="30" t="n"/>
+      <c r="G114" s="38">
+        <f>E114*F114*K114</f>
+        <v/>
+      </c>
+      <c r="H114" s="39">
+        <f>7500*K114</f>
+        <v/>
+      </c>
+      <c r="I114" s="39">
+        <f>13000*K114</f>
+        <v/>
+      </c>
+      <c r="J114" s="40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K114" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="56" t="n"/>
+      <c r="B116" s="56" t="n"/>
+      <c r="C116" s="57" t="inlineStr">
         <is>
           <t>İMALAT ARA TOPLAMI</t>
         </is>
       </c>
-      <c r="D111" s="56" t="n"/>
-      <c r="E111" s="56" t="n"/>
-      <c r="F111" s="56" t="n"/>
-      <c r="G111" s="18">
-        <f>SUM(G4:G109)</f>
-        <v/>
-      </c>
-      <c r="H111" s="18">
-        <f>SUM(H4:H109)</f>
-        <v/>
-      </c>
-      <c r="I111" s="18">
-        <f>SUM(I4:I109)</f>
-        <v/>
-      </c>
-      <c r="J111" s="56" t="n"/>
-      <c r="K111" s="56" t="n"/>
+      <c r="D116" s="56" t="n"/>
+      <c r="E116" s="56" t="n"/>
+      <c r="F116" s="56" t="n"/>
+      <c r="G116" s="18">
+        <f>SUM(G4:G114)</f>
+        <v/>
+      </c>
+      <c r="H116" s="18">
+        <f>SUM(H4:H114)</f>
+        <v/>
+      </c>
+      <c r="I116" s="18">
+        <f>SUM(I4:I114)</f>
+        <v/>
+      </c>
+      <c r="J116" s="56" t="n"/>
+      <c r="K116" s="56" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K109"/>
+  <autoFilter ref="A3:K114"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -6707,7 +6963,7 @@
       <c r="H10" s="17" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>Salon brüt alanı</t>
         </is>
@@ -6717,7 +6973,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Serbest sirkülasyon / çalışma alanı</t>
         </is>
@@ -7087,7 +7343,7 @@
         </is>
       </c>
       <c r="B19" s="67" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>

--- a/output/Gym_Maliyet_BoQ.xlsx
+++ b/output/Gym_Maliyet_BoQ.xlsx
@@ -808,7 +808,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rev E · 17 Eylül 2026 · Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
+          <t>Rev F · 17 Eylül 2026 · Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev E · 17 Eylül 2026 · Fiyat referansı: Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Net iç alan 103.78 m²</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev F · 17 Eylül 2026 · Fiyat referansı: Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Net iç alan 103.78 m²</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="E45" s="44" t="n">
-        <v>10.3</v>
+        <v>16.8</v>
       </c>
       <c r="F45" s="30" t="n"/>
       <c r="G45" s="45">
@@ -3467,11 +3467,11 @@
         <v/>
       </c>
       <c r="H45" s="46">
-        <f>13905*K45</f>
+        <f>22680*K45</f>
         <v/>
       </c>
       <c r="I45" s="46">
-        <f>22660*K45</f>
+        <f>36960*K45</f>
         <v/>
       </c>
       <c r="J45" s="47" t="inlineStr">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="E46" s="37" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="F46" s="30" t="n"/>
       <c r="G46" s="38">
@@ -3513,11 +3513,11 @@
         <v/>
       </c>
       <c r="H46" s="39">
-        <f>10465*K46</f>
+        <f>12075*K46</f>
         <v/>
       </c>
       <c r="I46" s="39">
-        <f>17290*K46</f>
+        <f>19950*K46</f>
         <v/>
       </c>
       <c r="J46" s="40" t="inlineStr">
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="E47" s="44" t="n">
-        <v>10.7</v>
+        <v>4.4</v>
       </c>
       <c r="F47" s="30" t="n"/>
       <c r="G47" s="45">
@@ -3559,11 +3559,11 @@
         <v/>
       </c>
       <c r="H47" s="46">
-        <f>6634*K47</f>
+        <f>2728*K47</f>
         <v/>
       </c>
       <c r="I47" s="46">
-        <f>11235*K47</f>
+        <f>4620*K47</f>
         <v/>
       </c>
       <c r="J47" s="47" t="inlineStr">
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="E48" s="37" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="F48" s="30" t="n"/>
       <c r="G48" s="38">
@@ -3605,11 +3605,11 @@
         <v/>
       </c>
       <c r="H48" s="39">
-        <f>1932*K48</f>
+        <f>1260*K48</f>
         <v/>
       </c>
       <c r="I48" s="39">
-        <f>3312*K48</f>
+        <f>2160*K48</f>
         <v/>
       </c>
       <c r="J48" s="40" t="inlineStr">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E49" s="44" t="n">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="F49" s="30" t="n"/>
       <c r="G49" s="45">
@@ -3651,11 +3651,11 @@
         <v/>
       </c>
       <c r="H49" s="46">
-        <f>3996*K49</f>
+        <f>8100*K49</f>
         <v/>
       </c>
       <c r="I49" s="46">
-        <f>6660*K49</f>
+        <f>13500*K49</f>
         <v/>
       </c>
       <c r="J49" s="47" t="inlineStr">
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="E56" s="37" t="n">
-        <v>25.2</v>
+        <v>35.5</v>
       </c>
       <c r="F56" s="30" t="n"/>
       <c r="G56" s="38">
@@ -3973,11 +3973,11 @@
         <v/>
       </c>
       <c r="H56" s="39">
-        <f>19656*K56</f>
+        <f>27690*K56</f>
         <v/>
       </c>
       <c r="I56" s="39">
-        <f>32760*K56</f>
+        <f>46150*K56</f>
         <v/>
       </c>
       <c r="J56" s="40" t="inlineStr">
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="E57" s="44" t="n">
-        <v>26.8</v>
+        <v>42.3</v>
       </c>
       <c r="F57" s="30" t="n"/>
       <c r="G57" s="45">
@@ -4019,11 +4019,11 @@
         <v/>
       </c>
       <c r="H57" s="46">
-        <f>8576*K57</f>
+        <f>13536*K57</f>
         <v/>
       </c>
       <c r="I57" s="46">
-        <f>14472*K57</f>
+        <f>22842*K57</f>
         <v/>
       </c>
       <c r="J57" s="47" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="C77" s="42" t="inlineStr">
         <is>
-          <t>Elektrikli ani su ısıtıcı 6 kW (blok başına)</t>
+          <t>Depolu elektrikli boyler 100 L / 3 kW, emaye kaplı, magnezyum anotlu (blok başına)</t>
         </is>
       </c>
       <c r="D77" s="43" t="inlineStr">
@@ -4941,11 +4941,11 @@
         <v/>
       </c>
       <c r="H77" s="46">
-        <f>19600*K77</f>
+        <f>23000*K77</f>
         <v/>
       </c>
       <c r="I77" s="46">
-        <f>34000*K77</f>
+        <f>39000*K77</f>
         <v/>
       </c>
       <c r="J77" s="47" t="inlineStr">
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="E82" s="37" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F82" s="30" t="n"/>
       <c r="G82" s="38">
@@ -5171,11 +5171,11 @@
         <v/>
       </c>
       <c r="H82" s="39">
-        <f>13020*K82</f>
+        <f>13640*K82</f>
         <v/>
       </c>
       <c r="I82" s="39">
-        <f>22050*K82</f>
+        <f>23100*K82</f>
         <v/>
       </c>
       <c r="J82" s="40" t="inlineStr">
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="E90" s="37" t="n">
-        <v>172</v>
+        <v>42</v>
       </c>
       <c r="F90" s="30" t="n"/>
       <c r="G90" s="38">
@@ -5539,11 +5539,11 @@
         <v/>
       </c>
       <c r="H90" s="39">
-        <f>18920*K90</f>
+        <f>4620*K90</f>
         <v/>
       </c>
       <c r="I90" s="39">
-        <f>31820*K90</f>
+        <f>7770*K90</f>
         <v/>
       </c>
       <c r="J90" s="40" t="inlineStr">
@@ -5761,7 +5761,7 @@
         </is>
       </c>
       <c r="E95" s="44" t="n">
-        <v>193</v>
+        <v>391</v>
       </c>
       <c r="F95" s="30" t="n"/>
       <c r="G95" s="45">
@@ -5769,11 +5769,11 @@
         <v/>
       </c>
       <c r="H95" s="46">
-        <f>27020*K95</f>
+        <f>54740*K95</f>
         <v/>
       </c>
       <c r="I95" s="46">
-        <f>44390*K95</f>
+        <f>89930*K95</f>
         <v/>
       </c>
       <c r="J95" s="47" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="C97" s="42" t="inlineStr">
         <is>
-          <t>Su ısıtıcı besleme hattı 3×6 mm² + 32 A kesici + 30 mA kaçak akım</t>
+          <t>Boyler besleme hattı 3×2,5 mm² + 20 A kesici + 30 mA kaçak akım</t>
         </is>
       </c>
       <c r="D97" s="43" t="inlineStr">
@@ -5861,11 +5861,11 @@
         <v/>
       </c>
       <c r="H97" s="46">
-        <f>12800*K97</f>
+        <f>8400*K97</f>
         <v/>
       </c>
       <c r="I97" s="46">
-        <f>21600*K97</f>
+        <f>14600*K97</f>
         <v/>
       </c>
       <c r="J97" s="47" t="inlineStr">
@@ -7323,7 +7323,7 @@
         </is>
       </c>
       <c r="B18" s="61" t="n">
-        <v>26.59</v>
+        <v>20.59</v>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>

--- a/output/Gym_Maliyet_BoQ.xlsx
+++ b/output/Gym_Maliyet_BoQ.xlsx
@@ -808,7 +808,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rev G · 17 Eylül 2026 · Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
+          <t>Rev H · 17 Eylül 2026 · Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev G · 17 Eylül 2026 · Fiyat referansı: Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Net iç alan 103.78 m²</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev H · 17 Eylül 2026 · Fiyat referansı: Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Net iç alan 103.78 m²</t>
         </is>
       </c>
     </row>

--- a/output/Gym_Maliyet_BoQ.xlsx
+++ b/output/Gym_Maliyet_BoQ.xlsx
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="E8" s="37" t="n">
-        <v>44.6</v>
+        <v>45.1</v>
       </c>
       <c r="F8" s="30" t="n"/>
       <c r="G8" s="38">
@@ -1757,11 +1757,11 @@
         <v/>
       </c>
       <c r="H8" s="39">
-        <f>138260*K8</f>
+        <f>139810*K8</f>
         <v/>
       </c>
       <c r="I8" s="39">
-        <f>173940*K8</f>
+        <f>175890*K8</f>
         <v/>
       </c>
       <c r="J8" s="40" t="inlineStr">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="E9" s="44" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="F9" s="30" t="n"/>
       <c r="G9" s="45">
@@ -1803,11 +1803,11 @@
         <v/>
       </c>
       <c r="H9" s="46">
-        <f>7035*K9</f>
+        <f>7105*K9</f>
         <v/>
       </c>
       <c r="I9" s="46">
-        <f>10452*K9</f>
+        <f>10556*K9</f>
         <v/>
       </c>
       <c r="J9" s="47" t="inlineStr">
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="E10" s="37" t="n">
-        <v>129.3</v>
+        <v>131.8</v>
       </c>
       <c r="F10" s="30" t="n"/>
       <c r="G10" s="38">
@@ -1849,11 +1849,11 @@
         <v/>
       </c>
       <c r="H10" s="39">
-        <f>49134*K10</f>
+        <f>50084*K10</f>
         <v/>
       </c>
       <c r="I10" s="39">
-        <f>72408*K10</f>
+        <f>73808*K10</f>
         <v/>
       </c>
       <c r="J10" s="40" t="inlineStr">
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="E12" s="37" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="F12" s="30" t="n"/>
       <c r="G12" s="38">
@@ -1942,11 +1942,11 @@
         <v/>
       </c>
       <c r="H12" s="39">
-        <f>19440*K12</f>
+        <f>19520*K12</f>
         <v/>
       </c>
       <c r="I12" s="39">
-        <f>26730*K12</f>
+        <f>26840*K12</f>
         <v/>
       </c>
       <c r="J12" s="40" t="inlineStr">
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="E14" s="37" t="n">
-        <v>55.7</v>
+        <v>56.4</v>
       </c>
       <c r="F14" s="30" t="n"/>
       <c r="G14" s="38">
@@ -2034,11 +2034,11 @@
         <v/>
       </c>
       <c r="H14" s="39">
-        <f>99982*K14</f>
+        <f>101238*K14</f>
         <v/>
       </c>
       <c r="I14" s="39">
-        <f>147605*K14</f>
+        <f>149460*K14</f>
         <v/>
       </c>
       <c r="J14" s="40" t="inlineStr">
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="E19" s="44" t="n">
-        <v>31.76</v>
+        <v>31.94</v>
       </c>
       <c r="F19" s="30" t="n"/>
       <c r="G19" s="45">
@@ -2266,11 +2266,11 @@
         <v/>
       </c>
       <c r="H19" s="46">
-        <f>87340*K19</f>
+        <f>87835*K19</f>
         <v/>
       </c>
       <c r="I19" s="46">
-        <f>124499*K19</f>
+        <f>125205*K19</f>
         <v/>
       </c>
       <c r="J19" s="47" t="inlineStr">
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="E20" s="37" t="n">
-        <v>31.76</v>
+        <v>31.94</v>
       </c>
       <c r="F20" s="30" t="n"/>
       <c r="G20" s="38">
@@ -2312,11 +2312,11 @@
         <v/>
       </c>
       <c r="H20" s="39">
-        <f>26361*K20</f>
+        <f>26510*K20</f>
         <v/>
       </c>
       <c r="I20" s="39">
-        <f>40018*K20</f>
+        <f>40244*K20</f>
         <v/>
       </c>
       <c r="J20" s="40" t="inlineStr">
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="E21" s="44" t="n">
-        <v>22.31</v>
+        <v>22.34</v>
       </c>
       <c r="F21" s="30" t="n"/>
       <c r="G21" s="45">
@@ -2359,11 +2359,11 @@
         <v/>
       </c>
       <c r="H21" s="46">
-        <f>36812*K21</f>
+        <f>36861*K21</f>
         <v/>
       </c>
       <c r="I21" s="46">
-        <f>53544*K21</f>
+        <f>53616*K21</f>
         <v/>
       </c>
       <c r="J21" s="47" t="inlineStr">
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="E22" s="37" t="n">
-        <v>32.98</v>
+        <v>32.77</v>
       </c>
       <c r="F22" s="30" t="n"/>
       <c r="G22" s="38">
@@ -2405,11 +2405,11 @@
         <v/>
       </c>
       <c r="H22" s="39">
-        <f>45183*K22</f>
+        <f>44895*K22</f>
         <v/>
       </c>
       <c r="I22" s="39">
-        <f>69918*K22</f>
+        <f>69472*K22</f>
         <v/>
       </c>
       <c r="J22" s="40" t="inlineStr">
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="E23" s="44" t="n">
-        <v>71.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F23" s="30" t="n"/>
       <c r="G23" s="45">
@@ -2451,11 +2451,11 @@
         <v/>
       </c>
       <c r="H23" s="46">
-        <f>25025*K23</f>
+        <f>25410*K23</f>
         <v/>
       </c>
       <c r="I23" s="46">
-        <f>39325*K23</f>
+        <f>39930*K23</f>
         <v/>
       </c>
       <c r="J23" s="47" t="inlineStr">
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="E24" s="37" t="n">
-        <v>129.3</v>
+        <v>131.8</v>
       </c>
       <c r="F24" s="30" t="n"/>
       <c r="G24" s="38">
@@ -2497,11 +2497,11 @@
         <v/>
       </c>
       <c r="H24" s="39">
-        <f>49781*K24</f>
+        <f>50743*K24</f>
         <v/>
       </c>
       <c r="I24" s="39">
-        <f>78873*K24</f>
+        <f>80398*K24</f>
         <v/>
       </c>
       <c r="J24" s="40" t="inlineStr">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="E46" s="37" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="F46" s="30" t="n"/>
       <c r="G46" s="38">
@@ -3513,11 +3513,11 @@
         <v/>
       </c>
       <c r="H46" s="39">
-        <f>12075*K46</f>
+        <f>12190*K46</f>
         <v/>
       </c>
       <c r="I46" s="39">
-        <f>19950*K46</f>
+        <f>20140*K46</f>
         <v/>
       </c>
       <c r="J46" s="40" t="inlineStr">
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="E47" s="44" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="F47" s="30" t="n"/>
       <c r="G47" s="45">
@@ -3559,11 +3559,11 @@
         <v/>
       </c>
       <c r="H47" s="46">
-        <f>2728*K47</f>
+        <f>3162*K47</f>
         <v/>
       </c>
       <c r="I47" s="46">
-        <f>4620*K47</f>
+        <f>5355*K47</f>
         <v/>
       </c>
       <c r="J47" s="47" t="inlineStr">
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="E48" s="37" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="F48" s="30" t="n"/>
       <c r="G48" s="38">
@@ -3605,11 +3605,11 @@
         <v/>
       </c>
       <c r="H48" s="39">
-        <f>1260*K48</f>
+        <f>1050*K48</f>
         <v/>
       </c>
       <c r="I48" s="39">
-        <f>2160*K48</f>
+        <f>1800*K48</f>
         <v/>
       </c>
       <c r="J48" s="40" t="inlineStr">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E49" s="44" t="n">
-        <v>15</v>
+        <v>16.7</v>
       </c>
       <c r="F49" s="30" t="n"/>
       <c r="G49" s="45">
@@ -3651,11 +3651,11 @@
         <v/>
       </c>
       <c r="H49" s="46">
-        <f>8100*K49</f>
+        <f>9018*K49</f>
         <v/>
       </c>
       <c r="I49" s="46">
-        <f>13500*K49</f>
+        <f>15030*K49</f>
         <v/>
       </c>
       <c r="J49" s="47" t="inlineStr">
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="E56" s="37" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="F56" s="30" t="n"/>
       <c r="G56" s="38">
@@ -3973,11 +3973,11 @@
         <v/>
       </c>
       <c r="H56" s="39">
-        <f>27690*K56</f>
+        <f>27768*K56</f>
         <v/>
       </c>
       <c r="I56" s="39">
-        <f>46150*K56</f>
+        <f>46280*K56</f>
         <v/>
       </c>
       <c r="J56" s="40" t="inlineStr">
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="E57" s="44" t="n">
-        <v>42.3</v>
+        <v>44.1</v>
       </c>
       <c r="F57" s="30" t="n"/>
       <c r="G57" s="45">
@@ -4019,11 +4019,11 @@
         <v/>
       </c>
       <c r="H57" s="46">
-        <f>13536*K57</f>
+        <f>14112*K57</f>
         <v/>
       </c>
       <c r="I57" s="46">
-        <f>22842*K57</f>
+        <f>23814*K57</f>
         <v/>
       </c>
       <c r="J57" s="47" t="inlineStr">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="E63" s="44" t="n">
-        <v>35.8</v>
+        <v>34</v>
       </c>
       <c r="F63" s="30" t="n"/>
       <c r="G63" s="45">
@@ -4297,11 +4297,11 @@
         <v/>
       </c>
       <c r="H63" s="46">
-        <f>39380*K63</f>
+        <f>37400*K63</f>
         <v/>
       </c>
       <c r="I63" s="46">
-        <f>66230*K63</f>
+        <f>62900*K63</f>
         <v/>
       </c>
       <c r="J63" s="47" t="inlineStr">
@@ -4381,7 +4381,7 @@
         </is>
       </c>
       <c r="E65" s="44" t="n">
-        <v>34.2</v>
+        <v>31.9</v>
       </c>
       <c r="F65" s="30" t="n"/>
       <c r="G65" s="45">
@@ -4389,11 +4389,11 @@
         <v/>
       </c>
       <c r="H65" s="46">
-        <f>14364*K65</f>
+        <f>13398*K65</f>
         <v/>
       </c>
       <c r="I65" s="46">
-        <f>24624*K65</f>
+        <f>22968*K65</f>
         <v/>
       </c>
       <c r="J65" s="47" t="inlineStr">
@@ -6451,7 +6451,7 @@
         </is>
       </c>
       <c r="E110" s="37" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F110" s="30" t="n"/>
       <c r="G110" s="38">
@@ -6459,11 +6459,11 @@
         <v/>
       </c>
       <c r="H110" s="39">
-        <f>12600*K110</f>
+        <f>12720*K110</f>
         <v/>
       </c>
       <c r="I110" s="39">
-        <f>22050*K110</f>
+        <f>22260*K110</f>
         <v/>
       </c>
       <c r="J110" s="40" t="inlineStr">
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="B10" s="61" t="n">
-        <v>46.15</v>
+        <v>46.91</v>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="B11" s="67" t="n">
-        <v>25.32</v>
+        <v>25.65</v>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="B12" s="61" t="n">
-        <v>129.3</v>
+        <v>131.8</v>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="B13" s="67" t="n">
-        <v>55.7</v>
+        <v>56.4</v>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="B14" s="61" t="n">
-        <v>44.6</v>
+        <v>45.1</v>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>

--- a/output/Gym_Maliyet_BoQ.xlsx
+++ b/output/Gym_Maliyet_BoQ.xlsx
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="E48" s="37" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="F48" s="30" t="n"/>
       <c r="G48" s="38">
@@ -3605,11 +3605,11 @@
         <v/>
       </c>
       <c r="H48" s="39">
-        <f>1050*K48</f>
+        <f>1260*K48</f>
         <v/>
       </c>
       <c r="I48" s="39">
-        <f>1800*K48</f>
+        <f>2160*K48</f>
         <v/>
       </c>
       <c r="J48" s="40" t="inlineStr">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E49" s="44" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="F49" s="30" t="n"/>
       <c r="G49" s="45">
@@ -3651,11 +3651,11 @@
         <v/>
       </c>
       <c r="H49" s="46">
-        <f>9018*K49</f>
+        <f>7506*K49</f>
         <v/>
       </c>
       <c r="I49" s="46">
-        <f>15030*K49</f>
+        <f>12510*K49</f>
         <v/>
       </c>
       <c r="J49" s="47" t="inlineStr">
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="E57" s="44" t="n">
-        <v>44.1</v>
+        <v>41.3</v>
       </c>
       <c r="F57" s="30" t="n"/>
       <c r="G57" s="45">
@@ -4019,11 +4019,11 @@
         <v/>
       </c>
       <c r="H57" s="46">
-        <f>14112*K57</f>
+        <f>13216*K57</f>
         <v/>
       </c>
       <c r="I57" s="46">
-        <f>23814*K57</f>
+        <f>22302*K57</f>
         <v/>
       </c>
       <c r="J57" s="47" t="inlineStr">
